--- a/Serie A 26-27.xlsx
+++ b/Serie A 26-27.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kuba\Desktop\analityczka\26-27\Serie A 26-27\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kuba\Desktop\analityczka\26-27\Ekstraklasa 26-27\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D0618169-1BA8-4930-8AF2-6780CD474366}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{BB41553A-87C8-4431-B461-01ABBB5BB2A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="408" xr2:uid="{1DB53276-41DA-4D3A-8911-B22B4D34B4C3}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="637" uniqueCount="147">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="670" uniqueCount="150">
   <si>
     <t>date</t>
   </si>
@@ -481,6 +481,15 @@
   <si>
     <t>Fri 18 September, 20:45</t>
   </si>
+  <si>
+    <t>Sat 10 October, 15:00</t>
+  </si>
+  <si>
+    <t>Sat 10 October, 18:00</t>
+  </si>
+  <si>
+    <t>Sat 10 October, 20:45</t>
+  </si>
 </sst>
 </file>
 
@@ -878,7 +887,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{830FE08A-34EB-4CC3-870F-27849C4CD8BD}">
-  <dimension ref="A1:CJ51"/>
+  <dimension ref="A1:CJ54"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="19.5703125" bestFit="1" customWidth="1"/>
@@ -1202,7 +1211,7 @@
         <v>70</v>
       </c>
       <c r="H2">
-        <f t="shared" ref="H2:H51" si="0">100-G2</f>
+        <f t="shared" ref="H2:H54" si="0">100-G2</f>
         <v>30</v>
       </c>
       <c r="I2">
@@ -14418,6 +14427,798 @@
         <v>0</v>
       </c>
       <c r="CJ51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="2:88" x14ac:dyDescent="0.25">
+      <c r="B52" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="C52" t="s">
+        <v>94</v>
+      </c>
+      <c r="D52" t="s">
+        <v>113</v>
+      </c>
+      <c r="E52">
+        <v>2</v>
+      </c>
+      <c r="F52">
+        <v>1</v>
+      </c>
+      <c r="G52">
+        <v>37</v>
+      </c>
+      <c r="H52">
+        <f t="shared" si="0"/>
+        <v>63</v>
+      </c>
+      <c r="I52">
+        <v>1.46</v>
+      </c>
+      <c r="J52">
+        <v>0.82</v>
+      </c>
+      <c r="K52">
+        <v>10</v>
+      </c>
+      <c r="L52">
+        <v>13</v>
+      </c>
+      <c r="M52">
+        <v>4</v>
+      </c>
+      <c r="N52">
+        <v>3</v>
+      </c>
+      <c r="O52">
+        <v>3</v>
+      </c>
+      <c r="P52">
+        <v>0</v>
+      </c>
+      <c r="Q52">
+        <v>1</v>
+      </c>
+      <c r="R52">
+        <v>0</v>
+      </c>
+      <c r="S52">
+        <v>209</v>
+      </c>
+      <c r="T52">
+        <v>405</v>
+      </c>
+      <c r="U52">
+        <v>11</v>
+      </c>
+      <c r="V52">
+        <v>10</v>
+      </c>
+      <c r="W52">
+        <v>3</v>
+      </c>
+      <c r="X52">
+        <v>4</v>
+      </c>
+      <c r="Y52" t="s">
+        <v>90</v>
+      </c>
+      <c r="Z52" t="s">
+        <v>90</v>
+      </c>
+      <c r="AA52">
+        <v>5</v>
+      </c>
+      <c r="AB52">
+        <v>6</v>
+      </c>
+      <c r="AC52">
+        <v>1</v>
+      </c>
+      <c r="AD52">
+        <v>4</v>
+      </c>
+      <c r="AE52">
+        <v>0</v>
+      </c>
+      <c r="AF52">
+        <v>1</v>
+      </c>
+      <c r="AG52">
+        <v>7</v>
+      </c>
+      <c r="AH52">
+        <v>10</v>
+      </c>
+      <c r="AI52">
+        <v>3</v>
+      </c>
+      <c r="AJ52">
+        <v>3</v>
+      </c>
+      <c r="AK52">
+        <v>1.38</v>
+      </c>
+      <c r="AL52">
+        <v>0.74</v>
+      </c>
+      <c r="AM52">
+        <v>0.08</v>
+      </c>
+      <c r="AN52">
+        <v>0.08</v>
+      </c>
+      <c r="AO52">
+        <v>1.46</v>
+      </c>
+      <c r="AP52">
+        <v>0.82</v>
+      </c>
+      <c r="AQ52">
+        <v>1.91</v>
+      </c>
+      <c r="AR52">
+        <v>0.62</v>
+      </c>
+      <c r="AS52">
+        <v>276</v>
+      </c>
+      <c r="AT52">
+        <v>473</v>
+      </c>
+      <c r="AU52">
+        <v>130</v>
+      </c>
+      <c r="AV52">
+        <v>167</v>
+      </c>
+      <c r="AW52">
+        <v>79</v>
+      </c>
+      <c r="AX52">
+        <v>238</v>
+      </c>
+      <c r="AY52">
+        <v>21</v>
+      </c>
+      <c r="AZ52">
+        <v>17</v>
+      </c>
+      <c r="BA52">
+        <v>3</v>
+      </c>
+      <c r="BB52">
+        <v>4</v>
+      </c>
+      <c r="BC52">
+        <v>15</v>
+      </c>
+      <c r="BD52">
+        <v>25</v>
+      </c>
+      <c r="BE52">
+        <v>21</v>
+      </c>
+      <c r="BF52">
+        <v>44</v>
+      </c>
+      <c r="BG52">
+        <v>2</v>
+      </c>
+      <c r="BH52">
+        <v>2</v>
+      </c>
+      <c r="BI52" t="s">
+        <v>90</v>
+      </c>
+      <c r="BJ52" t="s">
+        <v>90</v>
+      </c>
+      <c r="BK52">
+        <v>22</v>
+      </c>
+      <c r="BL52">
+        <v>19</v>
+      </c>
+      <c r="BM52">
+        <v>8</v>
+      </c>
+      <c r="BN52">
+        <v>3</v>
+      </c>
+      <c r="BO52">
+        <v>3</v>
+      </c>
+      <c r="BP52">
+        <v>1</v>
+      </c>
+      <c r="BQ52">
+        <v>33</v>
+      </c>
+      <c r="BR52">
+        <v>21</v>
+      </c>
+      <c r="BS52">
+        <v>3</v>
+      </c>
+      <c r="BT52">
+        <v>2</v>
+      </c>
+      <c r="BU52" t="s">
+        <v>90</v>
+      </c>
+      <c r="BV52" t="s">
+        <v>90</v>
+      </c>
+      <c r="BW52">
+        <v>46</v>
+      </c>
+      <c r="BX52">
+        <v>51</v>
+      </c>
+      <c r="BY52">
+        <v>35</v>
+      </c>
+      <c r="BZ52">
+        <v>39</v>
+      </c>
+      <c r="CA52">
+        <v>11</v>
+      </c>
+      <c r="CB52">
+        <v>12</v>
+      </c>
+      <c r="CC52">
+        <v>5</v>
+      </c>
+      <c r="CD52">
+        <v>10</v>
+      </c>
+      <c r="CE52" t="s">
+        <v>90</v>
+      </c>
+      <c r="CF52" t="s">
+        <v>90</v>
+      </c>
+      <c r="CG52">
+        <v>5</v>
+      </c>
+      <c r="CH52">
+        <v>3</v>
+      </c>
+      <c r="CI52">
+        <v>0</v>
+      </c>
+      <c r="CJ52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="2:88" x14ac:dyDescent="0.25">
+      <c r="B53" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="C53" t="s">
+        <v>88</v>
+      </c>
+      <c r="D53" t="s">
+        <v>96</v>
+      </c>
+      <c r="E53">
+        <v>3</v>
+      </c>
+      <c r="F53">
+        <v>0</v>
+      </c>
+      <c r="G53">
+        <v>59</v>
+      </c>
+      <c r="H53">
+        <f t="shared" si="0"/>
+        <v>41</v>
+      </c>
+      <c r="I53">
+        <v>2.42</v>
+      </c>
+      <c r="J53">
+        <v>0.46</v>
+      </c>
+      <c r="K53">
+        <v>19</v>
+      </c>
+      <c r="L53">
+        <v>9</v>
+      </c>
+      <c r="M53">
+        <v>6</v>
+      </c>
+      <c r="N53">
+        <v>2</v>
+      </c>
+      <c r="O53">
+        <v>4</v>
+      </c>
+      <c r="P53">
+        <v>0</v>
+      </c>
+      <c r="Q53">
+        <v>1</v>
+      </c>
+      <c r="R53">
+        <v>0</v>
+      </c>
+      <c r="S53">
+        <v>574</v>
+      </c>
+      <c r="T53">
+        <v>367</v>
+      </c>
+      <c r="U53">
+        <v>13</v>
+      </c>
+      <c r="V53">
+        <v>9</v>
+      </c>
+      <c r="W53">
+        <v>3</v>
+      </c>
+      <c r="X53">
+        <v>1</v>
+      </c>
+      <c r="Y53" t="s">
+        <v>90</v>
+      </c>
+      <c r="Z53" t="s">
+        <v>90</v>
+      </c>
+      <c r="AA53">
+        <v>9</v>
+      </c>
+      <c r="AB53">
+        <v>6</v>
+      </c>
+      <c r="AC53">
+        <v>4</v>
+      </c>
+      <c r="AD53">
+        <v>1</v>
+      </c>
+      <c r="AE53">
+        <v>0</v>
+      </c>
+      <c r="AF53">
+        <v>0</v>
+      </c>
+      <c r="AG53">
+        <v>13</v>
+      </c>
+      <c r="AH53">
+        <v>7</v>
+      </c>
+      <c r="AI53">
+        <v>6</v>
+      </c>
+      <c r="AJ53">
+        <v>2</v>
+      </c>
+      <c r="AK53">
+        <v>1.62</v>
+      </c>
+      <c r="AL53">
+        <v>0.41</v>
+      </c>
+      <c r="AM53">
+        <v>0.01</v>
+      </c>
+      <c r="AN53">
+        <v>0.05</v>
+      </c>
+      <c r="AO53">
+        <v>1.63</v>
+      </c>
+      <c r="AP53">
+        <v>0.46</v>
+      </c>
+      <c r="AQ53">
+        <v>1.96</v>
+      </c>
+      <c r="AR53">
+        <v>0.08</v>
+      </c>
+      <c r="AS53">
+        <v>634</v>
+      </c>
+      <c r="AT53">
+        <v>433</v>
+      </c>
+      <c r="AU53">
+        <v>265</v>
+      </c>
+      <c r="AV53">
+        <v>243</v>
+      </c>
+      <c r="AW53">
+        <v>309</v>
+      </c>
+      <c r="AX53">
+        <v>124</v>
+      </c>
+      <c r="AY53">
+        <v>31</v>
+      </c>
+      <c r="AZ53">
+        <v>23</v>
+      </c>
+      <c r="BA53">
+        <v>3</v>
+      </c>
+      <c r="BB53">
+        <v>0</v>
+      </c>
+      <c r="BC53">
+        <v>9</v>
+      </c>
+      <c r="BD53">
+        <v>18</v>
+      </c>
+      <c r="BE53">
+        <v>40</v>
+      </c>
+      <c r="BF53">
+        <v>16</v>
+      </c>
+      <c r="BG53">
+        <v>6</v>
+      </c>
+      <c r="BH53">
+        <v>2</v>
+      </c>
+      <c r="BI53" t="s">
+        <v>90</v>
+      </c>
+      <c r="BJ53" t="s">
+        <v>90</v>
+      </c>
+      <c r="BK53">
+        <v>20</v>
+      </c>
+      <c r="BL53">
+        <v>16</v>
+      </c>
+      <c r="BM53">
+        <v>12</v>
+      </c>
+      <c r="BN53">
+        <v>8</v>
+      </c>
+      <c r="BO53">
+        <v>1</v>
+      </c>
+      <c r="BP53">
+        <v>4</v>
+      </c>
+      <c r="BQ53">
+        <v>17</v>
+      </c>
+      <c r="BR53">
+        <v>16</v>
+      </c>
+      <c r="BS53">
+        <v>2</v>
+      </c>
+      <c r="BT53">
+        <v>4</v>
+      </c>
+      <c r="BU53" t="s">
+        <v>90</v>
+      </c>
+      <c r="BV53" t="s">
+        <v>90</v>
+      </c>
+      <c r="BW53">
+        <v>47</v>
+      </c>
+      <c r="BX53">
+        <v>39</v>
+      </c>
+      <c r="BY53">
+        <v>33</v>
+      </c>
+      <c r="BZ53">
+        <v>34</v>
+      </c>
+      <c r="CA53">
+        <v>14</v>
+      </c>
+      <c r="CB53">
+        <v>5</v>
+      </c>
+      <c r="CC53">
+        <v>5</v>
+      </c>
+      <c r="CD53">
+        <v>5</v>
+      </c>
+      <c r="CE53" t="s">
+        <v>90</v>
+      </c>
+      <c r="CF53" t="s">
+        <v>90</v>
+      </c>
+      <c r="CG53">
+        <v>0</v>
+      </c>
+      <c r="CH53">
+        <v>0</v>
+      </c>
+      <c r="CI53">
+        <v>0</v>
+      </c>
+      <c r="CJ53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="2:88" x14ac:dyDescent="0.25">
+      <c r="B54" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="C54" t="s">
+        <v>95</v>
+      </c>
+      <c r="D54" t="s">
+        <v>99</v>
+      </c>
+      <c r="E54">
+        <v>3</v>
+      </c>
+      <c r="F54">
+        <v>0</v>
+      </c>
+      <c r="G54">
+        <v>51</v>
+      </c>
+      <c r="H54">
+        <f t="shared" si="0"/>
+        <v>49</v>
+      </c>
+      <c r="I54">
+        <v>3.12</v>
+      </c>
+      <c r="J54">
+        <v>1.01</v>
+      </c>
+      <c r="K54">
+        <v>19</v>
+      </c>
+      <c r="L54">
+        <v>17</v>
+      </c>
+      <c r="M54">
+        <v>8</v>
+      </c>
+      <c r="N54">
+        <v>1</v>
+      </c>
+      <c r="O54">
+        <v>4</v>
+      </c>
+      <c r="P54">
+        <v>0</v>
+      </c>
+      <c r="Q54">
+        <v>1</v>
+      </c>
+      <c r="R54">
+        <v>0</v>
+      </c>
+      <c r="S54">
+        <v>364</v>
+      </c>
+      <c r="T54">
+        <v>355</v>
+      </c>
+      <c r="U54">
+        <v>8</v>
+      </c>
+      <c r="V54">
+        <v>12</v>
+      </c>
+      <c r="W54">
+        <v>6</v>
+      </c>
+      <c r="X54">
+        <v>4</v>
+      </c>
+      <c r="Y54" t="s">
+        <v>90</v>
+      </c>
+      <c r="Z54" t="s">
+        <v>90</v>
+      </c>
+      <c r="AA54">
+        <v>9</v>
+      </c>
+      <c r="AB54">
+        <v>14</v>
+      </c>
+      <c r="AC54">
+        <v>2</v>
+      </c>
+      <c r="AD54">
+        <v>2</v>
+      </c>
+      <c r="AE54">
+        <v>1</v>
+      </c>
+      <c r="AF54">
+        <v>0</v>
+      </c>
+      <c r="AG54">
+        <v>13</v>
+      </c>
+      <c r="AH54">
+        <v>9</v>
+      </c>
+      <c r="AI54">
+        <v>6</v>
+      </c>
+      <c r="AJ54">
+        <v>8</v>
+      </c>
+      <c r="AK54">
+        <v>2.21</v>
+      </c>
+      <c r="AL54">
+        <v>0.76</v>
+      </c>
+      <c r="AM54">
+        <v>0.12</v>
+      </c>
+      <c r="AN54">
+        <v>0.25</v>
+      </c>
+      <c r="AO54">
+        <v>2.33</v>
+      </c>
+      <c r="AP54">
+        <v>1.01</v>
+      </c>
+      <c r="AQ54">
+        <v>3.38</v>
+      </c>
+      <c r="AR54">
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="AS54">
+        <v>456</v>
+      </c>
+      <c r="AT54">
+        <v>425</v>
+      </c>
+      <c r="AU54">
+        <v>176</v>
+      </c>
+      <c r="AV54">
+        <v>152</v>
+      </c>
+      <c r="AW54">
+        <v>188</v>
+      </c>
+      <c r="AX54">
+        <v>203</v>
+      </c>
+      <c r="AY54">
+        <v>27</v>
+      </c>
+      <c r="AZ54">
+        <v>16</v>
+      </c>
+      <c r="BA54">
+        <v>5</v>
+      </c>
+      <c r="BB54">
+        <v>7</v>
+      </c>
+      <c r="BC54">
+        <v>24</v>
+      </c>
+      <c r="BD54">
+        <v>8</v>
+      </c>
+      <c r="BE54">
+        <v>32</v>
+      </c>
+      <c r="BF54">
+        <v>34</v>
+      </c>
+      <c r="BG54">
+        <v>1</v>
+      </c>
+      <c r="BH54">
+        <v>2</v>
+      </c>
+      <c r="BI54" t="s">
+        <v>90</v>
+      </c>
+      <c r="BJ54" t="s">
+        <v>90</v>
+      </c>
+      <c r="BK54">
+        <v>9</v>
+      </c>
+      <c r="BL54">
+        <v>18</v>
+      </c>
+      <c r="BM54">
+        <v>10</v>
+      </c>
+      <c r="BN54">
+        <v>14</v>
+      </c>
+      <c r="BO54">
+        <v>2</v>
+      </c>
+      <c r="BP54">
+        <v>2</v>
+      </c>
+      <c r="BQ54">
+        <v>24</v>
+      </c>
+      <c r="BR54">
+        <v>20</v>
+      </c>
+      <c r="BS54">
+        <v>1</v>
+      </c>
+      <c r="BT54">
+        <v>5</v>
+      </c>
+      <c r="BU54" t="s">
+        <v>90</v>
+      </c>
+      <c r="BV54" t="s">
+        <v>90</v>
+      </c>
+      <c r="BW54">
+        <v>43</v>
+      </c>
+      <c r="BX54">
+        <v>49</v>
+      </c>
+      <c r="BY54">
+        <v>25</v>
+      </c>
+      <c r="BZ54">
+        <v>35</v>
+      </c>
+      <c r="CA54">
+        <v>18</v>
+      </c>
+      <c r="CB54">
+        <v>14</v>
+      </c>
+      <c r="CC54">
+        <v>5</v>
+      </c>
+      <c r="CD54">
+        <v>9</v>
+      </c>
+      <c r="CE54" t="s">
+        <v>90</v>
+      </c>
+      <c r="CF54" t="s">
+        <v>90</v>
+      </c>
+      <c r="CG54">
+        <v>2</v>
+      </c>
+      <c r="CH54">
+        <v>0</v>
+      </c>
+      <c r="CI54">
+        <v>0</v>
+      </c>
+      <c r="CJ54">
         <v>0</v>
       </c>
     </row>

--- a/Serie A 26-27.xlsx
+++ b/Serie A 26-27.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kuba\Desktop\analityczka\26-27\Ekstraklasa 26-27\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{BB41553A-87C8-4431-B461-01ABBB5BB2A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{666383AD-F874-457C-9658-D14464C98B2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="408" xr2:uid="{1DB53276-41DA-4D3A-8911-B22B4D34B4C3}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="670" uniqueCount="150">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="747" uniqueCount="156">
   <si>
     <t>date</t>
   </si>
@@ -490,12 +490,30 @@
   <si>
     <t>Sat 10 October, 20:45</t>
   </si>
+  <si>
+    <t>Sun 11 October, 12:30</t>
+  </si>
+  <si>
+    <t>Sun 11 October, 15:00</t>
+  </si>
+  <si>
+    <t>Sun 11 October, 18:00</t>
+  </si>
+  <si>
+    <t>Sun 11 October, 20:45</t>
+  </si>
+  <si>
+    <t>Mon 12 October, 18:30</t>
+  </si>
+  <si>
+    <t>Mon 12 October, 20:45</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -518,6 +536,11 @@
       <family val="2"/>
       <charset val="238"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Inherit"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -539,7 +562,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
@@ -552,6 +575,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" indent="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -887,8 +916,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{830FE08A-34EB-4CC3-870F-27849C4CD8BD}">
-  <dimension ref="A1:CJ54"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:CJ61"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="19.5703125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="13.140625" customWidth="1"/>
@@ -925,7 +954,7 @@
     <col min="84" max="85" width="12.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:88" ht="69" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:88" ht="69" customHeight="1">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1188,7 +1217,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="2" spans="1:88" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:88" ht="27.75" customHeight="1">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1211,7 +1240,7 @@
         <v>70</v>
       </c>
       <c r="H2">
-        <f t="shared" ref="H2:H54" si="0">100-G2</f>
+        <f t="shared" ref="H2:H61" si="0">100-G2</f>
         <v>30</v>
       </c>
       <c r="I2">
@@ -1455,7 +1484,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:88" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:88" ht="25.5" customHeight="1">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1722,7 +1751,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:88" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:88" ht="26.25" customHeight="1">
       <c r="A4">
         <v>3</v>
       </c>
@@ -1989,7 +2018,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:88" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:88" ht="28.5" customHeight="1">
       <c r="A5">
         <v>4</v>
       </c>
@@ -2256,7 +2285,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:88" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:88" ht="24.75" customHeight="1">
       <c r="A6">
         <v>5</v>
       </c>
@@ -2523,7 +2552,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:88" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:88" ht="28.5" customHeight="1">
       <c r="A7">
         <v>6</v>
       </c>
@@ -2790,7 +2819,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:88" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:88" ht="28.5" customHeight="1">
       <c r="A8">
         <v>7</v>
       </c>
@@ -3057,7 +3086,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:88" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:88" ht="25.5" customHeight="1">
       <c r="A9">
         <v>8</v>
       </c>
@@ -3324,7 +3353,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:88" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:88" ht="26.25" customHeight="1">
       <c r="A10">
         <v>9</v>
       </c>
@@ -3591,7 +3620,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:88" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:88" ht="24.75" customHeight="1">
       <c r="A11">
         <v>10</v>
       </c>
@@ -3858,7 +3887,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:88" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:88" ht="25.5" customHeight="1">
       <c r="A12">
         <v>11</v>
       </c>
@@ -4125,7 +4154,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:88" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:88" ht="27.75" customHeight="1">
       <c r="A13">
         <v>12</v>
       </c>
@@ -4392,7 +4421,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:88" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:88" ht="26.25" customHeight="1">
       <c r="A14">
         <v>13</v>
       </c>
@@ -4659,7 +4688,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:88" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:88" ht="25.5" customHeight="1">
       <c r="A15">
         <v>14</v>
       </c>
@@ -4926,7 +4955,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:88" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:88" ht="25.5" customHeight="1">
       <c r="B16" s="2" t="s">
         <v>116</v>
       </c>
@@ -5190,7 +5219,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="2:88" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:88" ht="26.25" customHeight="1">
       <c r="B17" s="2" t="s">
         <v>117</v>
       </c>
@@ -5454,7 +5483,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="2:88" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:88" ht="27" customHeight="1">
       <c r="B18" s="2" t="s">
         <v>118</v>
       </c>
@@ -5718,7 +5747,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="2:88" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:88" ht="26.25" customHeight="1">
       <c r="B19" s="2" t="s">
         <v>118</v>
       </c>
@@ -5982,7 +6011,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="2:88" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:88" ht="29.25" customHeight="1">
       <c r="B20" s="2" t="s">
         <v>119</v>
       </c>
@@ -6246,7 +6275,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="2:88" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:88" ht="27" customHeight="1">
       <c r="B21" s="2" t="s">
         <v>120</v>
       </c>
@@ -6510,7 +6539,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="2:88" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:88" ht="30" customHeight="1">
       <c r="B22" s="2" t="s">
         <v>121</v>
       </c>
@@ -6774,7 +6803,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="2:88" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:88" ht="27" customHeight="1">
       <c r="B23" s="2" t="s">
         <v>122</v>
       </c>
@@ -7038,7 +7067,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="2:88" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:88" ht="25.5" customHeight="1">
       <c r="B24" s="2" t="s">
         <v>123</v>
       </c>
@@ -7302,7 +7331,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="2:88" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:88" ht="27" customHeight="1">
       <c r="B25" s="2" t="s">
         <v>124</v>
       </c>
@@ -7566,7 +7595,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="2:88" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:88" ht="27.75" customHeight="1">
       <c r="B26" s="2" t="s">
         <v>125</v>
       </c>
@@ -7830,7 +7859,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="2:88" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:88" ht="28.5" customHeight="1">
       <c r="B27" s="2" t="s">
         <v>125</v>
       </c>
@@ -8094,7 +8123,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="2:88" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:88" ht="25.5">
       <c r="B28" s="2" t="s">
         <v>126</v>
       </c>
@@ -8358,7 +8387,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="2:88" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:88" ht="25.5">
       <c r="B29" s="2" t="s">
         <v>127</v>
       </c>
@@ -8622,7 +8651,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="2:88" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:88" ht="25.5">
       <c r="B30" s="2" t="s">
         <v>128</v>
       </c>
@@ -8886,7 +8915,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="2:88" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:88" ht="25.5">
       <c r="B31" s="2" t="s">
         <v>129</v>
       </c>
@@ -9150,7 +9179,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="2:88" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:88" ht="25.5">
       <c r="B32" s="2" t="s">
         <v>130</v>
       </c>
@@ -9414,7 +9443,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="2:88" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:88" ht="25.5">
       <c r="B33" s="2" t="s">
         <v>131</v>
       </c>
@@ -9678,7 +9707,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="2:88" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:88" ht="25.5">
       <c r="B34" s="2" t="s">
         <v>132</v>
       </c>
@@ -9942,7 +9971,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="2:88" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:88" ht="25.5">
       <c r="B35" s="2" t="s">
         <v>133</v>
       </c>
@@ -10206,7 +10235,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="2:88" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:88" ht="25.5">
       <c r="B36" s="2" t="s">
         <v>134</v>
       </c>
@@ -10470,7 +10499,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="2:88" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:88" ht="25.5">
       <c r="B37" s="2" t="s">
         <v>135</v>
       </c>
@@ -10734,7 +10763,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="2:88" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:88" ht="25.5">
       <c r="B38" s="2" t="s">
         <v>136</v>
       </c>
@@ -10998,7 +11027,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="2:88" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:88" ht="25.5">
       <c r="B39" s="3" t="s">
         <v>137</v>
       </c>
@@ -11262,7 +11291,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="2:88" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:88" ht="25.5">
       <c r="B40" s="3" t="s">
         <v>137</v>
       </c>
@@ -11526,7 +11555,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="2:88" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:88" ht="25.5">
       <c r="B41" s="3" t="s">
         <v>138</v>
       </c>
@@ -11790,7 +11819,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="2:88" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:88" ht="25.5">
       <c r="B42" s="3" t="s">
         <v>146</v>
       </c>
@@ -12054,7 +12083,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="2:88" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="43" spans="2:88" ht="25.5">
       <c r="B43" s="2" t="s">
         <v>139</v>
       </c>
@@ -12318,7 +12347,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="2:88" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:88" ht="25.5">
       <c r="B44" s="2" t="s">
         <v>139</v>
       </c>
@@ -12582,7 +12611,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="2:88" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="45" spans="2:88" ht="25.5">
       <c r="B45" s="2" t="s">
         <v>140</v>
       </c>
@@ -12846,7 +12875,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="2:88" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="46" spans="2:88" ht="25.5">
       <c r="B46" s="2" t="s">
         <v>141</v>
       </c>
@@ -13110,7 +13139,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="2:88" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="47" spans="2:88" ht="25.5">
       <c r="B47" s="3" t="s">
         <v>142</v>
       </c>
@@ -13374,7 +13403,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="2:88" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="48" spans="2:88" ht="25.5">
       <c r="B48" s="3" t="s">
         <v>143</v>
       </c>
@@ -13638,7 +13667,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="2:88" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="49" spans="2:88" ht="25.5">
       <c r="B49" s="3" t="s">
         <v>143</v>
       </c>
@@ -13902,7 +13931,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="2:88" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="50" spans="2:88" ht="25.5">
       <c r="B50" s="3" t="s">
         <v>144</v>
       </c>
@@ -14166,7 +14195,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="2:88" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="51" spans="2:88" ht="25.5">
       <c r="B51" s="3" t="s">
         <v>145</v>
       </c>
@@ -14430,7 +14459,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="2:88" x14ac:dyDescent="0.25">
+    <row r="52" spans="2:88">
       <c r="B52" s="2" t="s">
         <v>147</v>
       </c>
@@ -14694,7 +14723,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="2:88" x14ac:dyDescent="0.25">
+    <row r="53" spans="2:88">
       <c r="B53" s="2" t="s">
         <v>148</v>
       </c>
@@ -14958,7 +14987,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="2:88" x14ac:dyDescent="0.25">
+    <row r="54" spans="2:88">
       <c r="B54" s="2" t="s">
         <v>149</v>
       </c>
@@ -15219,6 +15248,1854 @@
         <v>0</v>
       </c>
       <c r="CJ54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="2:88">
+      <c r="B55" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="C55" t="s">
+        <v>92</v>
+      </c>
+      <c r="D55" t="s">
+        <v>112</v>
+      </c>
+      <c r="E55">
+        <v>0</v>
+      </c>
+      <c r="F55">
+        <v>0</v>
+      </c>
+      <c r="G55">
+        <v>66</v>
+      </c>
+      <c r="H55">
+        <f t="shared" si="0"/>
+        <v>34</v>
+      </c>
+      <c r="I55">
+        <v>1.35</v>
+      </c>
+      <c r="J55">
+        <v>1.08</v>
+      </c>
+      <c r="K55">
+        <v>19</v>
+      </c>
+      <c r="L55">
+        <v>9</v>
+      </c>
+      <c r="M55">
+        <v>4</v>
+      </c>
+      <c r="N55">
+        <v>2</v>
+      </c>
+      <c r="O55">
+        <v>4</v>
+      </c>
+      <c r="P55">
+        <v>2</v>
+      </c>
+      <c r="Q55">
+        <v>4</v>
+      </c>
+      <c r="R55">
+        <v>2</v>
+      </c>
+      <c r="S55">
+        <v>616</v>
+      </c>
+      <c r="T55">
+        <v>270</v>
+      </c>
+      <c r="U55">
+        <v>9</v>
+      </c>
+      <c r="V55">
+        <v>9</v>
+      </c>
+      <c r="W55">
+        <v>6</v>
+      </c>
+      <c r="X55">
+        <v>2</v>
+      </c>
+      <c r="Y55" t="s">
+        <v>90</v>
+      </c>
+      <c r="Z55" t="s">
+        <v>90</v>
+      </c>
+      <c r="AA55">
+        <v>10</v>
+      </c>
+      <c r="AB55">
+        <v>5</v>
+      </c>
+      <c r="AC55">
+        <v>5</v>
+      </c>
+      <c r="AD55">
+        <v>2</v>
+      </c>
+      <c r="AE55">
+        <v>0</v>
+      </c>
+      <c r="AF55">
+        <v>1</v>
+      </c>
+      <c r="AG55">
+        <v>9</v>
+      </c>
+      <c r="AH55">
+        <v>4</v>
+      </c>
+      <c r="AI55">
+        <v>10</v>
+      </c>
+      <c r="AJ55">
+        <v>5</v>
+      </c>
+      <c r="AK55">
+        <v>1.1599999999999999</v>
+      </c>
+      <c r="AL55">
+        <v>1.05</v>
+      </c>
+      <c r="AM55">
+        <v>0.18</v>
+      </c>
+      <c r="AN55">
+        <v>0.03</v>
+      </c>
+      <c r="AO55">
+        <v>1.35</v>
+      </c>
+      <c r="AP55">
+        <v>1.08</v>
+      </c>
+      <c r="AQ55">
+        <v>1.25</v>
+      </c>
+      <c r="AR55">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="AS55">
+        <v>674</v>
+      </c>
+      <c r="AT55">
+        <v>344</v>
+      </c>
+      <c r="AU55">
+        <v>254</v>
+      </c>
+      <c r="AV55">
+        <v>170</v>
+      </c>
+      <c r="AW55">
+        <v>362</v>
+      </c>
+      <c r="AX55">
+        <v>100</v>
+      </c>
+      <c r="AY55">
+        <v>21</v>
+      </c>
+      <c r="AZ55">
+        <v>17</v>
+      </c>
+      <c r="BA55">
+        <v>3</v>
+      </c>
+      <c r="BB55">
+        <v>2</v>
+      </c>
+      <c r="BC55">
+        <v>23</v>
+      </c>
+      <c r="BD55">
+        <v>25</v>
+      </c>
+      <c r="BE55">
+        <v>29</v>
+      </c>
+      <c r="BF55">
+        <v>11</v>
+      </c>
+      <c r="BG55">
+        <v>0</v>
+      </c>
+      <c r="BH55">
+        <v>3</v>
+      </c>
+      <c r="BI55" t="s">
+        <v>90</v>
+      </c>
+      <c r="BJ55" t="s">
+        <v>90</v>
+      </c>
+      <c r="BK55">
+        <v>18</v>
+      </c>
+      <c r="BL55">
+        <v>16</v>
+      </c>
+      <c r="BM55">
+        <v>12</v>
+      </c>
+      <c r="BN55">
+        <v>7</v>
+      </c>
+      <c r="BO55">
+        <v>2</v>
+      </c>
+      <c r="BP55">
+        <v>5</v>
+      </c>
+      <c r="BQ55">
+        <v>14</v>
+      </c>
+      <c r="BR55">
+        <v>18</v>
+      </c>
+      <c r="BS55">
+        <v>2</v>
+      </c>
+      <c r="BT55">
+        <v>4</v>
+      </c>
+      <c r="BU55" t="s">
+        <v>90</v>
+      </c>
+      <c r="BV55" t="s">
+        <v>90</v>
+      </c>
+      <c r="BW55">
+        <v>47</v>
+      </c>
+      <c r="BX55">
+        <v>46</v>
+      </c>
+      <c r="BY55">
+        <v>38</v>
+      </c>
+      <c r="BZ55">
+        <v>32</v>
+      </c>
+      <c r="CA55">
+        <v>9</v>
+      </c>
+      <c r="CB55">
+        <v>14</v>
+      </c>
+      <c r="CC55">
+        <v>11</v>
+      </c>
+      <c r="CD55">
+        <v>7</v>
+      </c>
+      <c r="CE55" t="s">
+        <v>90</v>
+      </c>
+      <c r="CF55" t="s">
+        <v>90</v>
+      </c>
+      <c r="CG55">
+        <v>2</v>
+      </c>
+      <c r="CH55">
+        <v>3</v>
+      </c>
+      <c r="CI55">
+        <v>0</v>
+      </c>
+      <c r="CJ55">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56" spans="2:88">
+      <c r="B56" s="5" t="s">
+        <v>151</v>
+      </c>
+      <c r="C56" t="s">
+        <v>110</v>
+      </c>
+      <c r="D56" t="s">
+        <v>89</v>
+      </c>
+      <c r="E56">
+        <v>3</v>
+      </c>
+      <c r="F56">
+        <v>1</v>
+      </c>
+      <c r="G56">
+        <v>65</v>
+      </c>
+      <c r="H56">
+        <f t="shared" si="0"/>
+        <v>35</v>
+      </c>
+      <c r="I56">
+        <v>1.84</v>
+      </c>
+      <c r="J56">
+        <v>1.76</v>
+      </c>
+      <c r="K56">
+        <v>17</v>
+      </c>
+      <c r="L56">
+        <v>14</v>
+      </c>
+      <c r="M56">
+        <v>7</v>
+      </c>
+      <c r="N56">
+        <v>6</v>
+      </c>
+      <c r="O56">
+        <v>4</v>
+      </c>
+      <c r="P56">
+        <v>4</v>
+      </c>
+      <c r="Q56">
+        <v>3</v>
+      </c>
+      <c r="R56">
+        <v>3</v>
+      </c>
+      <c r="S56">
+        <v>517</v>
+      </c>
+      <c r="T56">
+        <v>225</v>
+      </c>
+      <c r="U56">
+        <v>10</v>
+      </c>
+      <c r="V56">
+        <v>9</v>
+      </c>
+      <c r="W56">
+        <v>7</v>
+      </c>
+      <c r="X56">
+        <v>6</v>
+      </c>
+      <c r="Y56" t="s">
+        <v>90</v>
+      </c>
+      <c r="Z56" t="s">
+        <v>90</v>
+      </c>
+      <c r="AA56">
+        <v>8</v>
+      </c>
+      <c r="AB56">
+        <v>3</v>
+      </c>
+      <c r="AC56">
+        <v>2</v>
+      </c>
+      <c r="AD56">
+        <v>5</v>
+      </c>
+      <c r="AE56">
+        <v>1</v>
+      </c>
+      <c r="AF56">
+        <v>0</v>
+      </c>
+      <c r="AG56">
+        <v>8</v>
+      </c>
+      <c r="AH56">
+        <v>10</v>
+      </c>
+      <c r="AI56">
+        <v>9</v>
+      </c>
+      <c r="AJ56">
+        <v>4</v>
+      </c>
+      <c r="AK56">
+        <v>1.77</v>
+      </c>
+      <c r="AL56">
+        <v>0.84</v>
+      </c>
+      <c r="AM56">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="AN56">
+        <v>0.92</v>
+      </c>
+      <c r="AO56">
+        <v>1.84</v>
+      </c>
+      <c r="AP56">
+        <v>1.76</v>
+      </c>
+      <c r="AQ56">
+        <v>2.16</v>
+      </c>
+      <c r="AR56">
+        <v>1.93</v>
+      </c>
+      <c r="AS56">
+        <v>596</v>
+      </c>
+      <c r="AT56">
+        <v>300</v>
+      </c>
+      <c r="AU56">
+        <v>211</v>
+      </c>
+      <c r="AV56">
+        <v>132</v>
+      </c>
+      <c r="AW56">
+        <v>306</v>
+      </c>
+      <c r="AX56">
+        <v>93</v>
+      </c>
+      <c r="AY56">
+        <v>30</v>
+      </c>
+      <c r="AZ56">
+        <v>21</v>
+      </c>
+      <c r="BA56">
+        <v>3</v>
+      </c>
+      <c r="BB56">
+        <v>7</v>
+      </c>
+      <c r="BC56">
+        <v>18</v>
+      </c>
+      <c r="BD56">
+        <v>14</v>
+      </c>
+      <c r="BE56">
+        <v>28</v>
+      </c>
+      <c r="BF56">
+        <v>24</v>
+      </c>
+      <c r="BG56">
+        <v>0</v>
+      </c>
+      <c r="BH56">
+        <v>2</v>
+      </c>
+      <c r="BI56" t="s">
+        <v>90</v>
+      </c>
+      <c r="BJ56" t="s">
+        <v>90</v>
+      </c>
+      <c r="BK56">
+        <v>13</v>
+      </c>
+      <c r="BL56">
+        <v>13</v>
+      </c>
+      <c r="BM56">
+        <v>7</v>
+      </c>
+      <c r="BN56">
+        <v>12</v>
+      </c>
+      <c r="BO56">
+        <v>5</v>
+      </c>
+      <c r="BP56">
+        <v>2</v>
+      </c>
+      <c r="BQ56">
+        <v>26</v>
+      </c>
+      <c r="BR56">
+        <v>25</v>
+      </c>
+      <c r="BS56">
+        <v>5</v>
+      </c>
+      <c r="BT56">
+        <v>4</v>
+      </c>
+      <c r="BU56" t="s">
+        <v>90</v>
+      </c>
+      <c r="BV56" t="s">
+        <v>90</v>
+      </c>
+      <c r="BW56">
+        <v>41</v>
+      </c>
+      <c r="BX56">
+        <v>47</v>
+      </c>
+      <c r="BY56">
+        <v>25</v>
+      </c>
+      <c r="BZ56">
+        <v>32</v>
+      </c>
+      <c r="CA56">
+        <v>16</v>
+      </c>
+      <c r="CB56">
+        <v>15</v>
+      </c>
+      <c r="CC56">
+        <v>4</v>
+      </c>
+      <c r="CD56">
+        <v>10</v>
+      </c>
+      <c r="CE56" t="s">
+        <v>90</v>
+      </c>
+      <c r="CF56" t="s">
+        <v>90</v>
+      </c>
+      <c r="CG56">
+        <v>3</v>
+      </c>
+      <c r="CH56">
+        <v>1</v>
+      </c>
+      <c r="CI56">
+        <v>0</v>
+      </c>
+      <c r="CJ56">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57" spans="2:88">
+      <c r="B57" s="5" t="s">
+        <v>151</v>
+      </c>
+      <c r="C57" t="s">
+        <v>102</v>
+      </c>
+      <c r="D57" t="s">
+        <v>109</v>
+      </c>
+      <c r="E57">
+        <v>1</v>
+      </c>
+      <c r="F57">
+        <v>2</v>
+      </c>
+      <c r="G57">
+        <v>57</v>
+      </c>
+      <c r="H57">
+        <f t="shared" si="0"/>
+        <v>43</v>
+      </c>
+      <c r="I57">
+        <v>1.49</v>
+      </c>
+      <c r="J57">
+        <v>1.98</v>
+      </c>
+      <c r="K57">
+        <v>19</v>
+      </c>
+      <c r="L57">
+        <v>9</v>
+      </c>
+      <c r="M57">
+        <v>5</v>
+      </c>
+      <c r="N57">
+        <v>5</v>
+      </c>
+      <c r="O57">
+        <v>2</v>
+      </c>
+      <c r="P57">
+        <v>3</v>
+      </c>
+      <c r="Q57">
+        <v>1</v>
+      </c>
+      <c r="R57">
+        <v>2</v>
+      </c>
+      <c r="S57">
+        <v>342</v>
+      </c>
+      <c r="T57">
+        <v>251</v>
+      </c>
+      <c r="U57">
+        <v>17</v>
+      </c>
+      <c r="V57">
+        <v>8</v>
+      </c>
+      <c r="W57">
+        <v>10</v>
+      </c>
+      <c r="X57">
+        <v>3</v>
+      </c>
+      <c r="Y57" t="s">
+        <v>90</v>
+      </c>
+      <c r="Z57" t="s">
+        <v>90</v>
+      </c>
+      <c r="AA57">
+        <v>8</v>
+      </c>
+      <c r="AB57">
+        <v>3</v>
+      </c>
+      <c r="AC57">
+        <v>6</v>
+      </c>
+      <c r="AD57">
+        <v>1</v>
+      </c>
+      <c r="AE57">
+        <v>0</v>
+      </c>
+      <c r="AF57">
+        <v>0</v>
+      </c>
+      <c r="AG57">
+        <v>14</v>
+      </c>
+      <c r="AH57">
+        <v>7</v>
+      </c>
+      <c r="AI57">
+        <v>5</v>
+      </c>
+      <c r="AJ57">
+        <v>2</v>
+      </c>
+      <c r="AK57">
+        <v>0.54</v>
+      </c>
+      <c r="AL57">
+        <v>1.27</v>
+      </c>
+      <c r="AM57">
+        <v>0.95</v>
+      </c>
+      <c r="AN57">
+        <v>0.71</v>
+      </c>
+      <c r="AO57">
+        <v>1.49</v>
+      </c>
+      <c r="AP57">
+        <v>1.98</v>
+      </c>
+      <c r="AQ57">
+        <v>1.45</v>
+      </c>
+      <c r="AR57">
+        <v>1.64</v>
+      </c>
+      <c r="AS57">
+        <v>409</v>
+      </c>
+      <c r="AT57">
+        <v>314</v>
+      </c>
+      <c r="AU57">
+        <v>162</v>
+      </c>
+      <c r="AV57">
+        <v>144</v>
+      </c>
+      <c r="AW57">
+        <v>180</v>
+      </c>
+      <c r="AX57">
+        <v>107</v>
+      </c>
+      <c r="AY57">
+        <v>21</v>
+      </c>
+      <c r="AZ57">
+        <v>29</v>
+      </c>
+      <c r="BA57">
+        <v>14</v>
+      </c>
+      <c r="BB57">
+        <v>10</v>
+      </c>
+      <c r="BC57">
+        <v>18</v>
+      </c>
+      <c r="BD57">
+        <v>27</v>
+      </c>
+      <c r="BE57">
+        <v>42</v>
+      </c>
+      <c r="BF57">
+        <v>24</v>
+      </c>
+      <c r="BG57">
+        <v>1</v>
+      </c>
+      <c r="BH57">
+        <v>4</v>
+      </c>
+      <c r="BI57" t="s">
+        <v>90</v>
+      </c>
+      <c r="BJ57" t="s">
+        <v>90</v>
+      </c>
+      <c r="BK57">
+        <v>11</v>
+      </c>
+      <c r="BL57">
+        <v>22</v>
+      </c>
+      <c r="BM57">
+        <v>11</v>
+      </c>
+      <c r="BN57">
+        <v>12</v>
+      </c>
+      <c r="BO57">
+        <v>1</v>
+      </c>
+      <c r="BP57">
+        <v>5</v>
+      </c>
+      <c r="BQ57">
+        <v>17</v>
+      </c>
+      <c r="BR57">
+        <v>43</v>
+      </c>
+      <c r="BS57">
+        <v>3</v>
+      </c>
+      <c r="BT57">
+        <v>4</v>
+      </c>
+      <c r="BU57" t="s">
+        <v>90</v>
+      </c>
+      <c r="BV57" t="s">
+        <v>90</v>
+      </c>
+      <c r="BW57">
+        <v>51</v>
+      </c>
+      <c r="BX57">
+        <v>61</v>
+      </c>
+      <c r="BY57">
+        <v>29</v>
+      </c>
+      <c r="BZ57">
+        <v>44</v>
+      </c>
+      <c r="CA57">
+        <v>23</v>
+      </c>
+      <c r="CB57">
+        <v>17</v>
+      </c>
+      <c r="CC57">
+        <v>9</v>
+      </c>
+      <c r="CD57">
+        <v>5</v>
+      </c>
+      <c r="CE57" t="s">
+        <v>90</v>
+      </c>
+      <c r="CF57" t="s">
+        <v>90</v>
+      </c>
+      <c r="CG57">
+        <v>3</v>
+      </c>
+      <c r="CH57">
+        <v>2</v>
+      </c>
+      <c r="CI57">
+        <v>0</v>
+      </c>
+      <c r="CJ57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="2:88">
+      <c r="B58" s="5" t="s">
+        <v>152</v>
+      </c>
+      <c r="C58" t="s">
+        <v>105</v>
+      </c>
+      <c r="D58" t="s">
+        <v>107</v>
+      </c>
+      <c r="E58">
+        <v>1</v>
+      </c>
+      <c r="F58">
+        <v>1</v>
+      </c>
+      <c r="G58">
+        <v>41</v>
+      </c>
+      <c r="H58">
+        <f t="shared" si="0"/>
+        <v>59</v>
+      </c>
+      <c r="I58">
+        <v>1.19</v>
+      </c>
+      <c r="J58">
+        <v>1.18</v>
+      </c>
+      <c r="K58">
+        <v>10</v>
+      </c>
+      <c r="L58">
+        <v>11</v>
+      </c>
+      <c r="M58">
+        <v>4</v>
+      </c>
+      <c r="N58">
+        <v>6</v>
+      </c>
+      <c r="O58">
+        <v>1</v>
+      </c>
+      <c r="P58">
+        <v>3</v>
+      </c>
+      <c r="Q58">
+        <v>1</v>
+      </c>
+      <c r="R58">
+        <v>3</v>
+      </c>
+      <c r="S58">
+        <v>380</v>
+      </c>
+      <c r="T58">
+        <v>566</v>
+      </c>
+      <c r="U58">
+        <v>13</v>
+      </c>
+      <c r="V58">
+        <v>11</v>
+      </c>
+      <c r="W58">
+        <v>3</v>
+      </c>
+      <c r="X58">
+        <v>5</v>
+      </c>
+      <c r="Y58" t="s">
+        <v>90</v>
+      </c>
+      <c r="Z58" t="s">
+        <v>90</v>
+      </c>
+      <c r="AA58">
+        <v>4</v>
+      </c>
+      <c r="AB58">
+        <v>2</v>
+      </c>
+      <c r="AC58">
+        <v>2</v>
+      </c>
+      <c r="AD58">
+        <v>3</v>
+      </c>
+      <c r="AE58">
+        <v>0</v>
+      </c>
+      <c r="AF58">
+        <v>0</v>
+      </c>
+      <c r="AG58">
+        <v>4</v>
+      </c>
+      <c r="AH58">
+        <v>10</v>
+      </c>
+      <c r="AI58">
+        <v>6</v>
+      </c>
+      <c r="AJ58">
+        <v>1</v>
+      </c>
+      <c r="AK58">
+        <v>1.04</v>
+      </c>
+      <c r="AL58">
+        <v>0.63</v>
+      </c>
+      <c r="AM58">
+        <v>0.15</v>
+      </c>
+      <c r="AN58">
+        <v>0.54</v>
+      </c>
+      <c r="AO58">
+        <v>1.19</v>
+      </c>
+      <c r="AP58">
+        <v>1.18</v>
+      </c>
+      <c r="AQ58">
+        <v>1.24</v>
+      </c>
+      <c r="AR58">
+        <v>1.65</v>
+      </c>
+      <c r="AS58">
+        <v>438</v>
+      </c>
+      <c r="AT58">
+        <v>627</v>
+      </c>
+      <c r="AU58">
+        <v>208</v>
+      </c>
+      <c r="AV58">
+        <v>298</v>
+      </c>
+      <c r="AW58">
+        <v>172</v>
+      </c>
+      <c r="AX58">
+        <v>268</v>
+      </c>
+      <c r="AY58">
+        <v>24</v>
+      </c>
+      <c r="AZ58">
+        <v>24</v>
+      </c>
+      <c r="BA58">
+        <v>4</v>
+      </c>
+      <c r="BB58">
+        <v>10</v>
+      </c>
+      <c r="BC58">
+        <v>7</v>
+      </c>
+      <c r="BD58">
+        <v>17</v>
+      </c>
+      <c r="BE58">
+        <v>19</v>
+      </c>
+      <c r="BF58">
+        <v>28</v>
+      </c>
+      <c r="BG58">
+        <v>1</v>
+      </c>
+      <c r="BH58">
+        <v>0</v>
+      </c>
+      <c r="BI58" t="s">
+        <v>90</v>
+      </c>
+      <c r="BJ58" t="s">
+        <v>90</v>
+      </c>
+      <c r="BK58">
+        <v>22</v>
+      </c>
+      <c r="BL58">
+        <v>17</v>
+      </c>
+      <c r="BM58">
+        <v>9</v>
+      </c>
+      <c r="BN58">
+        <v>9</v>
+      </c>
+      <c r="BO58">
+        <v>3</v>
+      </c>
+      <c r="BP58">
+        <v>2</v>
+      </c>
+      <c r="BQ58">
+        <v>29</v>
+      </c>
+      <c r="BR58">
+        <v>13</v>
+      </c>
+      <c r="BS58">
+        <v>5</v>
+      </c>
+      <c r="BT58">
+        <v>3</v>
+      </c>
+      <c r="BU58" t="s">
+        <v>90</v>
+      </c>
+      <c r="BV58" t="s">
+        <v>90</v>
+      </c>
+      <c r="BW58">
+        <v>43</v>
+      </c>
+      <c r="BX58">
+        <v>39</v>
+      </c>
+      <c r="BY58">
+        <v>37</v>
+      </c>
+      <c r="BZ58">
+        <v>34</v>
+      </c>
+      <c r="CA58">
+        <v>6</v>
+      </c>
+      <c r="CB58">
+        <v>5</v>
+      </c>
+      <c r="CC58">
+        <v>4</v>
+      </c>
+      <c r="CD58">
+        <v>6</v>
+      </c>
+      <c r="CE58" t="s">
+        <v>90</v>
+      </c>
+      <c r="CF58" t="s">
+        <v>90</v>
+      </c>
+      <c r="CG58">
+        <v>2</v>
+      </c>
+      <c r="CH58">
+        <v>4</v>
+      </c>
+      <c r="CI58">
+        <v>0</v>
+      </c>
+      <c r="CJ58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="2:88">
+      <c r="B59" s="5" t="s">
+        <v>153</v>
+      </c>
+      <c r="C59" t="s">
+        <v>97</v>
+      </c>
+      <c r="D59" t="s">
+        <v>100</v>
+      </c>
+      <c r="E59">
+        <v>1</v>
+      </c>
+      <c r="F59">
+        <v>1</v>
+      </c>
+      <c r="G59">
+        <v>28</v>
+      </c>
+      <c r="H59">
+        <f t="shared" si="0"/>
+        <v>72</v>
+      </c>
+      <c r="I59">
+        <v>0.52</v>
+      </c>
+      <c r="J59">
+        <v>1.95</v>
+      </c>
+      <c r="K59">
+        <v>4</v>
+      </c>
+      <c r="L59">
+        <v>22</v>
+      </c>
+      <c r="M59">
+        <v>2</v>
+      </c>
+      <c r="N59">
+        <v>10</v>
+      </c>
+      <c r="O59">
+        <v>1</v>
+      </c>
+      <c r="P59">
+        <v>3</v>
+      </c>
+      <c r="Q59">
+        <v>0</v>
+      </c>
+      <c r="R59">
+        <v>2</v>
+      </c>
+      <c r="S59">
+        <v>278</v>
+      </c>
+      <c r="T59">
+        <v>781</v>
+      </c>
+      <c r="U59">
+        <v>8</v>
+      </c>
+      <c r="V59">
+        <v>8</v>
+      </c>
+      <c r="W59">
+        <v>1</v>
+      </c>
+      <c r="X59">
+        <v>9</v>
+      </c>
+      <c r="Y59" t="s">
+        <v>90</v>
+      </c>
+      <c r="Z59" t="s">
+        <v>90</v>
+      </c>
+      <c r="AA59">
+        <v>1</v>
+      </c>
+      <c r="AB59">
+        <v>6</v>
+      </c>
+      <c r="AC59">
+        <v>1</v>
+      </c>
+      <c r="AD59">
+        <v>6</v>
+      </c>
+      <c r="AE59">
+        <v>0</v>
+      </c>
+      <c r="AF59">
+        <v>1</v>
+      </c>
+      <c r="AG59">
+        <v>2</v>
+      </c>
+      <c r="AH59">
+        <v>8</v>
+      </c>
+      <c r="AI59">
+        <v>2</v>
+      </c>
+      <c r="AJ59">
+        <v>14</v>
+      </c>
+      <c r="AK59">
+        <v>0.5</v>
+      </c>
+      <c r="AL59">
+        <v>0.85</v>
+      </c>
+      <c r="AM59">
+        <v>0.02</v>
+      </c>
+      <c r="AN59">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="AO59">
+        <v>0.52300000000000002</v>
+      </c>
+      <c r="AP59">
+        <v>1.95</v>
+      </c>
+      <c r="AQ59">
+        <v>0.66</v>
+      </c>
+      <c r="AR59">
+        <v>2.5</v>
+      </c>
+      <c r="AS59">
+        <v>340</v>
+      </c>
+      <c r="AT59">
+        <v>843</v>
+      </c>
+      <c r="AU59">
+        <v>168</v>
+      </c>
+      <c r="AV59">
+        <v>206</v>
+      </c>
+      <c r="AW59">
+        <v>110</v>
+      </c>
+      <c r="AX59">
+        <v>575</v>
+      </c>
+      <c r="AY59">
+        <v>22</v>
+      </c>
+      <c r="AZ59">
+        <v>13</v>
+      </c>
+      <c r="BA59">
+        <v>0</v>
+      </c>
+      <c r="BB59">
+        <v>6</v>
+      </c>
+      <c r="BC59">
+        <v>12</v>
+      </c>
+      <c r="BD59">
+        <v>20</v>
+      </c>
+      <c r="BE59">
+        <v>5</v>
+      </c>
+      <c r="BF59">
+        <v>50</v>
+      </c>
+      <c r="BG59">
+        <v>2</v>
+      </c>
+      <c r="BH59">
+        <v>2</v>
+      </c>
+      <c r="BI59" t="s">
+        <v>90</v>
+      </c>
+      <c r="BJ59" t="s">
+        <v>90</v>
+      </c>
+      <c r="BK59">
+        <v>24</v>
+      </c>
+      <c r="BL59">
+        <v>22</v>
+      </c>
+      <c r="BM59">
+        <v>11</v>
+      </c>
+      <c r="BN59">
+        <v>3</v>
+      </c>
+      <c r="BO59">
+        <v>6</v>
+      </c>
+      <c r="BP59">
+        <v>1</v>
+      </c>
+      <c r="BQ59">
+        <v>35</v>
+      </c>
+      <c r="BR59">
+        <v>7</v>
+      </c>
+      <c r="BS59">
+        <v>9</v>
+      </c>
+      <c r="BT59">
+        <v>1</v>
+      </c>
+      <c r="BU59" t="s">
+        <v>90</v>
+      </c>
+      <c r="BV59" t="s">
+        <v>90</v>
+      </c>
+      <c r="BW59">
+        <v>49</v>
+      </c>
+      <c r="BX59">
+        <v>45</v>
+      </c>
+      <c r="BY59">
+        <v>40</v>
+      </c>
+      <c r="BZ59">
+        <v>39</v>
+      </c>
+      <c r="CA59">
+        <v>9</v>
+      </c>
+      <c r="CB59">
+        <v>6</v>
+      </c>
+      <c r="CC59">
+        <v>9</v>
+      </c>
+      <c r="CD59">
+        <v>11</v>
+      </c>
+      <c r="CE59" t="s">
+        <v>90</v>
+      </c>
+      <c r="CF59" t="s">
+        <v>90</v>
+      </c>
+      <c r="CG59">
+        <v>2</v>
+      </c>
+      <c r="CH59">
+        <v>1</v>
+      </c>
+      <c r="CI59">
+        <v>0</v>
+      </c>
+      <c r="CJ59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="2:88" ht="25.5">
+      <c r="B60" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="C60" t="s">
+        <v>104</v>
+      </c>
+      <c r="D60" t="s">
+        <v>101</v>
+      </c>
+      <c r="E60">
+        <v>3</v>
+      </c>
+      <c r="F60">
+        <v>1</v>
+      </c>
+      <c r="G60">
+        <v>36</v>
+      </c>
+      <c r="H60">
+        <f t="shared" si="0"/>
+        <v>64</v>
+      </c>
+      <c r="I60">
+        <v>2.08</v>
+      </c>
+      <c r="J60">
+        <v>2.63</v>
+      </c>
+      <c r="K60">
+        <v>22</v>
+      </c>
+      <c r="L60">
+        <v>19</v>
+      </c>
+      <c r="M60">
+        <v>11</v>
+      </c>
+      <c r="N60">
+        <v>4</v>
+      </c>
+      <c r="O60">
+        <v>6</v>
+      </c>
+      <c r="P60">
+        <v>5</v>
+      </c>
+      <c r="Q60">
+        <v>4</v>
+      </c>
+      <c r="R60">
+        <v>4</v>
+      </c>
+      <c r="S60">
+        <v>276</v>
+      </c>
+      <c r="T60">
+        <v>526</v>
+      </c>
+      <c r="U60">
+        <v>14</v>
+      </c>
+      <c r="V60">
+        <v>6</v>
+      </c>
+      <c r="W60">
+        <v>8</v>
+      </c>
+      <c r="X60">
+        <v>7</v>
+      </c>
+      <c r="Y60" t="s">
+        <v>90</v>
+      </c>
+      <c r="Z60" t="s">
+        <v>90</v>
+      </c>
+      <c r="AA60">
+        <v>6</v>
+      </c>
+      <c r="AB60">
+        <v>9</v>
+      </c>
+      <c r="AC60">
+        <v>5</v>
+      </c>
+      <c r="AD60">
+        <v>6</v>
+      </c>
+      <c r="AE60">
+        <v>0</v>
+      </c>
+      <c r="AF60">
+        <v>2</v>
+      </c>
+      <c r="AG60">
+        <v>16</v>
+      </c>
+      <c r="AH60">
+        <v>10</v>
+      </c>
+      <c r="AI60">
+        <v>6</v>
+      </c>
+      <c r="AJ60">
+        <v>9</v>
+      </c>
+      <c r="AK60">
+        <v>1.59</v>
+      </c>
+      <c r="AL60">
+        <v>2.2200000000000002</v>
+      </c>
+      <c r="AM60">
+        <v>0.49</v>
+      </c>
+      <c r="AN60">
+        <v>0.4</v>
+      </c>
+      <c r="AO60">
+        <v>2.08</v>
+      </c>
+      <c r="AP60">
+        <v>2.63</v>
+      </c>
+      <c r="AQ60">
+        <v>2.5</v>
+      </c>
+      <c r="AR60">
+        <v>1.5</v>
+      </c>
+      <c r="AS60">
+        <v>332</v>
+      </c>
+      <c r="AT60">
+        <v>580</v>
+      </c>
+      <c r="AU60">
+        <v>154</v>
+      </c>
+      <c r="AV60">
+        <v>261</v>
+      </c>
+      <c r="AW60">
+        <v>122</v>
+      </c>
+      <c r="AX60">
+        <v>265</v>
+      </c>
+      <c r="AY60">
+        <v>17</v>
+      </c>
+      <c r="AZ60">
+        <v>31</v>
+      </c>
+      <c r="BA60">
+        <v>7</v>
+      </c>
+      <c r="BB60">
+        <v>6</v>
+      </c>
+      <c r="BC60">
+        <v>15</v>
+      </c>
+      <c r="BD60">
+        <v>17</v>
+      </c>
+      <c r="BE60">
+        <v>25</v>
+      </c>
+      <c r="BF60">
+        <v>27</v>
+      </c>
+      <c r="BG60">
+        <v>0</v>
+      </c>
+      <c r="BH60">
+        <v>5</v>
+      </c>
+      <c r="BI60" t="s">
+        <v>90</v>
+      </c>
+      <c r="BJ60" t="s">
+        <v>90</v>
+      </c>
+      <c r="BK60">
+        <v>11</v>
+      </c>
+      <c r="BL60">
+        <v>13</v>
+      </c>
+      <c r="BM60">
+        <v>9</v>
+      </c>
+      <c r="BN60">
+        <v>9</v>
+      </c>
+      <c r="BO60">
+        <v>6</v>
+      </c>
+      <c r="BP60">
+        <v>6</v>
+      </c>
+      <c r="BQ60">
+        <v>27</v>
+      </c>
+      <c r="BR60">
+        <v>15</v>
+      </c>
+      <c r="BS60">
+        <v>3</v>
+      </c>
+      <c r="BT60">
+        <v>7</v>
+      </c>
+      <c r="BU60" t="s">
+        <v>90</v>
+      </c>
+      <c r="BV60" t="s">
+        <v>90</v>
+      </c>
+      <c r="BW60">
+        <v>26</v>
+      </c>
+      <c r="BX60">
+        <v>38</v>
+      </c>
+      <c r="BY60">
+        <v>19</v>
+      </c>
+      <c r="BZ60">
+        <v>32</v>
+      </c>
+      <c r="CA60">
+        <v>7</v>
+      </c>
+      <c r="CB60">
+        <v>6</v>
+      </c>
+      <c r="CC60">
+        <v>3</v>
+      </c>
+      <c r="CD60">
+        <v>9</v>
+      </c>
+      <c r="CE60" t="s">
+        <v>90</v>
+      </c>
+      <c r="CF60" t="s">
+        <v>90</v>
+      </c>
+      <c r="CG60">
+        <v>0</v>
+      </c>
+      <c r="CH60">
+        <v>2</v>
+      </c>
+      <c r="CI60">
+        <v>1</v>
+      </c>
+      <c r="CJ60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="2:88" ht="25.5">
+      <c r="B61" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="C61" t="s">
+        <v>106</v>
+      </c>
+      <c r="D61" t="s">
+        <v>91</v>
+      </c>
+      <c r="E61">
+        <v>2</v>
+      </c>
+      <c r="F61">
+        <v>1</v>
+      </c>
+      <c r="G61">
+        <v>38</v>
+      </c>
+      <c r="H61">
+        <f t="shared" si="0"/>
+        <v>62</v>
+      </c>
+      <c r="I61">
+        <v>2.42</v>
+      </c>
+      <c r="J61">
+        <v>0.7</v>
+      </c>
+      <c r="K61">
+        <v>12</v>
+      </c>
+      <c r="L61">
+        <v>15</v>
+      </c>
+      <c r="M61">
+        <v>4</v>
+      </c>
+      <c r="N61">
+        <v>1</v>
+      </c>
+      <c r="O61">
+        <v>4</v>
+      </c>
+      <c r="P61">
+        <v>0</v>
+      </c>
+      <c r="Q61">
+        <v>2</v>
+      </c>
+      <c r="R61">
+        <v>0</v>
+      </c>
+      <c r="S61">
+        <v>332</v>
+      </c>
+      <c r="T61">
+        <v>583</v>
+      </c>
+      <c r="U61">
+        <v>4</v>
+      </c>
+      <c r="V61">
+        <v>10</v>
+      </c>
+      <c r="W61">
+        <v>4</v>
+      </c>
+      <c r="X61">
+        <v>3</v>
+      </c>
+      <c r="Y61" t="s">
+        <v>90</v>
+      </c>
+      <c r="Z61" t="s">
+        <v>90</v>
+      </c>
+      <c r="AA61">
+        <v>5</v>
+      </c>
+      <c r="AB61">
+        <v>9</v>
+      </c>
+      <c r="AC61">
+        <v>3</v>
+      </c>
+      <c r="AD61">
+        <v>5</v>
+      </c>
+      <c r="AE61">
+        <v>1</v>
+      </c>
+      <c r="AF61">
+        <v>0</v>
+      </c>
+      <c r="AG61">
+        <v>8</v>
+      </c>
+      <c r="AH61">
+        <v>9</v>
+      </c>
+      <c r="AI61">
+        <v>4</v>
+      </c>
+      <c r="AJ61">
+        <v>6</v>
+      </c>
+      <c r="AK61">
+        <v>1.26</v>
+      </c>
+      <c r="AL61">
+        <v>0.61</v>
+      </c>
+      <c r="AM61">
+        <v>1.17</v>
+      </c>
+      <c r="AN61">
+        <v>0.09</v>
+      </c>
+      <c r="AO61">
+        <v>2.42</v>
+      </c>
+      <c r="AP61">
+        <v>0.7</v>
+      </c>
+      <c r="AQ61">
+        <v>2.13</v>
+      </c>
+      <c r="AR61">
+        <v>0.15</v>
+      </c>
+      <c r="AS61">
+        <v>402</v>
+      </c>
+      <c r="AT61">
+        <v>641</v>
+      </c>
+      <c r="AU61">
+        <v>245</v>
+      </c>
+      <c r="AV61">
+        <v>264</v>
+      </c>
+      <c r="AW61">
+        <v>87</v>
+      </c>
+      <c r="AX61">
+        <v>319</v>
+      </c>
+      <c r="AY61">
+        <v>17</v>
+      </c>
+      <c r="AZ61">
+        <v>17</v>
+      </c>
+      <c r="BA61">
+        <v>1</v>
+      </c>
+      <c r="BB61">
+        <v>7</v>
+      </c>
+      <c r="BC61">
+        <v>13</v>
+      </c>
+      <c r="BD61">
+        <v>14</v>
+      </c>
+      <c r="BE61">
+        <v>13</v>
+      </c>
+      <c r="BF61">
+        <v>20</v>
+      </c>
+      <c r="BG61">
+        <v>7</v>
+      </c>
+      <c r="BH61">
+        <v>0</v>
+      </c>
+      <c r="BI61" t="s">
+        <v>90</v>
+      </c>
+      <c r="BJ61" t="s">
+        <v>90</v>
+      </c>
+      <c r="BK61">
+        <v>17</v>
+      </c>
+      <c r="BL61">
+        <v>14</v>
+      </c>
+      <c r="BM61">
+        <v>11</v>
+      </c>
+      <c r="BN61">
+        <v>5</v>
+      </c>
+      <c r="BO61">
+        <v>5</v>
+      </c>
+      <c r="BP61">
+        <v>2</v>
+      </c>
+      <c r="BQ61">
+        <v>16</v>
+      </c>
+      <c r="BR61">
+        <v>19</v>
+      </c>
+      <c r="BS61">
+        <v>0</v>
+      </c>
+      <c r="BT61">
+        <v>2</v>
+      </c>
+      <c r="BU61" t="s">
+        <v>90</v>
+      </c>
+      <c r="BV61" t="s">
+        <v>90</v>
+      </c>
+      <c r="BW61">
+        <v>43</v>
+      </c>
+      <c r="BX61">
+        <v>32</v>
+      </c>
+      <c r="BY61">
+        <v>31</v>
+      </c>
+      <c r="BZ61">
+        <v>24</v>
+      </c>
+      <c r="CA61">
+        <v>12</v>
+      </c>
+      <c r="CB61">
+        <v>8</v>
+      </c>
+      <c r="CC61">
+        <v>6</v>
+      </c>
+      <c r="CD61">
+        <v>7</v>
+      </c>
+      <c r="CE61" t="s">
+        <v>90</v>
+      </c>
+      <c r="CF61" t="s">
+        <v>90</v>
+      </c>
+      <c r="CG61">
+        <v>0</v>
+      </c>
+      <c r="CH61">
+        <v>1</v>
+      </c>
+      <c r="CI61">
+        <v>0</v>
+      </c>
+      <c r="CJ61">
         <v>0</v>
       </c>
     </row>

--- a/Serie A 26-27.xlsx
+++ b/Serie A 26-27.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kuba\Desktop\analityczka\26-27\Ekstraklasa 26-27\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{666383AD-F874-457C-9658-D14464C98B2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B6A03145-9C79-43AD-B227-3D1C1BD0B52D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="408" xr2:uid="{1DB53276-41DA-4D3A-8911-B22B4D34B4C3}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="747" uniqueCount="156">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="758" uniqueCount="157">
   <si>
     <t>date</t>
   </si>
@@ -508,6 +508,9 @@
   <si>
     <t>Mon 12 October, 20:45</t>
   </si>
+  <si>
+    <t>Fri 16 October, 20:45</t>
+  </si>
 </sst>
 </file>
 
@@ -916,7 +919,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{830FE08A-34EB-4CC3-870F-27849C4CD8BD}">
-  <dimension ref="A1:CJ61"/>
+  <dimension ref="A1:CJ62"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="19.5703125" bestFit="1" customWidth="1"/>
@@ -1240,7 +1243,7 @@
         <v>70</v>
       </c>
       <c r="H2">
-        <f t="shared" ref="H2:H61" si="0">100-G2</f>
+        <f t="shared" ref="H2:H62" si="0">100-G2</f>
         <v>30</v>
       </c>
       <c r="I2">
@@ -17096,6 +17099,270 @@
         <v>0</v>
       </c>
       <c r="CJ61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="2:88">
+      <c r="B62" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="C62" t="s">
+        <v>99</v>
+      </c>
+      <c r="D62" t="s">
+        <v>105</v>
+      </c>
+      <c r="E62">
+        <v>4</v>
+      </c>
+      <c r="F62">
+        <v>2</v>
+      </c>
+      <c r="G62">
+        <v>42</v>
+      </c>
+      <c r="H62">
+        <f t="shared" si="0"/>
+        <v>58</v>
+      </c>
+      <c r="I62">
+        <v>2.5499999999999998</v>
+      </c>
+      <c r="J62">
+        <v>2.02</v>
+      </c>
+      <c r="K62">
+        <v>21</v>
+      </c>
+      <c r="L62">
+        <v>14</v>
+      </c>
+      <c r="M62">
+        <v>10</v>
+      </c>
+      <c r="N62">
+        <v>6</v>
+      </c>
+      <c r="O62">
+        <v>5</v>
+      </c>
+      <c r="P62">
+        <v>4</v>
+      </c>
+      <c r="Q62">
+        <v>1</v>
+      </c>
+      <c r="R62">
+        <v>2</v>
+      </c>
+      <c r="S62">
+        <v>248</v>
+      </c>
+      <c r="T62">
+        <v>376</v>
+      </c>
+      <c r="U62">
+        <v>13</v>
+      </c>
+      <c r="V62">
+        <v>11</v>
+      </c>
+      <c r="W62">
+        <v>5</v>
+      </c>
+      <c r="X62">
+        <v>4</v>
+      </c>
+      <c r="Y62" t="s">
+        <v>90</v>
+      </c>
+      <c r="Z62" t="s">
+        <v>90</v>
+      </c>
+      <c r="AA62">
+        <v>7</v>
+      </c>
+      <c r="AB62">
+        <v>5</v>
+      </c>
+      <c r="AC62">
+        <v>4</v>
+      </c>
+      <c r="AD62">
+        <v>3</v>
+      </c>
+      <c r="AE62">
+        <v>0</v>
+      </c>
+      <c r="AF62">
+        <v>0</v>
+      </c>
+      <c r="AG62">
+        <v>11</v>
+      </c>
+      <c r="AH62">
+        <v>11</v>
+      </c>
+      <c r="AI62">
+        <v>10</v>
+      </c>
+      <c r="AJ62">
+        <v>3</v>
+      </c>
+      <c r="AK62">
+        <v>2.04</v>
+      </c>
+      <c r="AL62">
+        <v>1.72</v>
+      </c>
+      <c r="AM62">
+        <v>0.52</v>
+      </c>
+      <c r="AN62">
+        <v>0.3</v>
+      </c>
+      <c r="AO62">
+        <v>2.5499999999999998</v>
+      </c>
+      <c r="AP62">
+        <v>2.02</v>
+      </c>
+      <c r="AQ62">
+        <v>4.0599999999999996</v>
+      </c>
+      <c r="AR62">
+        <v>3.12</v>
+      </c>
+      <c r="AS62">
+        <v>333</v>
+      </c>
+      <c r="AT62">
+        <v>467</v>
+      </c>
+      <c r="AU62">
+        <v>76</v>
+      </c>
+      <c r="AV62">
+        <v>210</v>
+      </c>
+      <c r="AW62">
+        <v>172</v>
+      </c>
+      <c r="AX62">
+        <v>166</v>
+      </c>
+      <c r="AY62">
+        <v>16</v>
+      </c>
+      <c r="AZ62">
+        <v>25</v>
+      </c>
+      <c r="BA62">
+        <v>3</v>
+      </c>
+      <c r="BB62">
+        <v>4</v>
+      </c>
+      <c r="BC62">
+        <v>23</v>
+      </c>
+      <c r="BD62">
+        <v>19</v>
+      </c>
+      <c r="BE62">
+        <v>44</v>
+      </c>
+      <c r="BF62">
+        <v>35</v>
+      </c>
+      <c r="BG62">
+        <v>3</v>
+      </c>
+      <c r="BH62">
+        <v>3</v>
+      </c>
+      <c r="BI62" t="s">
+        <v>90</v>
+      </c>
+      <c r="BJ62" t="s">
+        <v>90</v>
+      </c>
+      <c r="BK62">
+        <v>20</v>
+      </c>
+      <c r="BL62">
+        <v>17</v>
+      </c>
+      <c r="BM62">
+        <v>8</v>
+      </c>
+      <c r="BN62">
+        <v>9</v>
+      </c>
+      <c r="BO62">
+        <v>3</v>
+      </c>
+      <c r="BP62">
+        <v>3</v>
+      </c>
+      <c r="BQ62">
+        <v>20</v>
+      </c>
+      <c r="BR62">
+        <v>20</v>
+      </c>
+      <c r="BS62">
+        <v>4</v>
+      </c>
+      <c r="BT62">
+        <v>6</v>
+      </c>
+      <c r="BU62" t="s">
+        <v>90</v>
+      </c>
+      <c r="BV62" t="s">
+        <v>90</v>
+      </c>
+      <c r="BW62">
+        <v>46</v>
+      </c>
+      <c r="BX62">
+        <v>44</v>
+      </c>
+      <c r="BY62">
+        <v>37</v>
+      </c>
+      <c r="BZ62">
+        <v>36</v>
+      </c>
+      <c r="CA62">
+        <v>9</v>
+      </c>
+      <c r="CB62">
+        <v>8</v>
+      </c>
+      <c r="CC62">
+        <v>6</v>
+      </c>
+      <c r="CD62">
+        <v>6</v>
+      </c>
+      <c r="CE62" t="s">
+        <v>90</v>
+      </c>
+      <c r="CF62" t="s">
+        <v>90</v>
+      </c>
+      <c r="CG62">
+        <v>0</v>
+      </c>
+      <c r="CH62">
+        <v>1</v>
+      </c>
+      <c r="CI62">
+        <v>0</v>
+      </c>
+      <c r="CJ62">
         <v>0</v>
       </c>
     </row>

--- a/Serie A 26-27.xlsx
+++ b/Serie A 26-27.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kuba\Desktop\analityczka\26-27\Ekstraklasa 26-27\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B6A03145-9C79-43AD-B227-3D1C1BD0B52D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{564A9192-0441-473E-945E-DC08336996C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="408" xr2:uid="{1DB53276-41DA-4D3A-8911-B22B4D34B4C3}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="758" uniqueCount="157">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="824" uniqueCount="163">
   <si>
     <t>date</t>
   </si>
@@ -511,6 +511,24 @@
   <si>
     <t>Fri 16 October, 20:45</t>
   </si>
+  <si>
+    <t>Sat 17 October, 15:00</t>
+  </si>
+  <si>
+    <t>Sat 17 October, 18:00</t>
+  </si>
+  <si>
+    <t>Sat 17 October, 20:45</t>
+  </si>
+  <si>
+    <t>Sun 18 October, 12:30</t>
+  </si>
+  <si>
+    <t>Sun 18 October, 15:00</t>
+  </si>
+  <si>
+    <t>Sun 18 October, 18:00</t>
+  </si>
 </sst>
 </file>
 
@@ -919,7 +937,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{830FE08A-34EB-4CC3-870F-27849C4CD8BD}">
-  <dimension ref="A1:CJ62"/>
+  <dimension ref="A1:CJ68"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="19.5703125" bestFit="1" customWidth="1"/>
@@ -1243,7 +1261,7 @@
         <v>70</v>
       </c>
       <c r="H2">
-        <f t="shared" ref="H2:H62" si="0">100-G2</f>
+        <f t="shared" ref="H2:H68" si="0">100-G2</f>
         <v>30</v>
       </c>
       <c r="I2">
@@ -17363,6 +17381,1590 @@
         <v>0</v>
       </c>
       <c r="CJ62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="2:88">
+      <c r="B63" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="C63" t="s">
+        <v>101</v>
+      </c>
+      <c r="D63" t="s">
+        <v>95</v>
+      </c>
+      <c r="E63">
+        <v>1</v>
+      </c>
+      <c r="F63">
+        <v>0</v>
+      </c>
+      <c r="G63">
+        <v>29</v>
+      </c>
+      <c r="H63">
+        <f t="shared" si="0"/>
+        <v>71</v>
+      </c>
+      <c r="I63">
+        <v>0.98</v>
+      </c>
+      <c r="J63">
+        <v>2.36</v>
+      </c>
+      <c r="K63">
+        <v>9</v>
+      </c>
+      <c r="L63">
+        <v>29</v>
+      </c>
+      <c r="M63">
+        <v>4</v>
+      </c>
+      <c r="N63">
+        <v>10</v>
+      </c>
+      <c r="O63">
+        <v>0</v>
+      </c>
+      <c r="P63">
+        <v>4</v>
+      </c>
+      <c r="Q63">
+        <v>0</v>
+      </c>
+      <c r="R63">
+        <v>4</v>
+      </c>
+      <c r="S63">
+        <v>234</v>
+      </c>
+      <c r="T63">
+        <v>658</v>
+      </c>
+      <c r="U63">
+        <v>7</v>
+      </c>
+      <c r="V63">
+        <v>6</v>
+      </c>
+      <c r="W63">
+        <v>0</v>
+      </c>
+      <c r="X63">
+        <v>12</v>
+      </c>
+      <c r="Y63" t="s">
+        <v>90</v>
+      </c>
+      <c r="Z63" t="s">
+        <v>90</v>
+      </c>
+      <c r="AA63">
+        <v>5</v>
+      </c>
+      <c r="AB63">
+        <v>7</v>
+      </c>
+      <c r="AC63">
+        <v>0</v>
+      </c>
+      <c r="AD63">
+        <v>12</v>
+      </c>
+      <c r="AE63">
+        <v>0</v>
+      </c>
+      <c r="AF63">
+        <v>0</v>
+      </c>
+      <c r="AG63">
+        <v>8</v>
+      </c>
+      <c r="AH63">
+        <v>22</v>
+      </c>
+      <c r="AI63">
+        <v>1</v>
+      </c>
+      <c r="AJ63">
+        <v>7</v>
+      </c>
+      <c r="AK63">
+        <v>0.98</v>
+      </c>
+      <c r="AL63">
+        <v>1.05</v>
+      </c>
+      <c r="AM63">
+        <v>0</v>
+      </c>
+      <c r="AN63">
+        <v>0.52</v>
+      </c>
+      <c r="AO63">
+        <v>0.98</v>
+      </c>
+      <c r="AP63">
+        <v>1.57</v>
+      </c>
+      <c r="AQ63">
+        <v>1.58</v>
+      </c>
+      <c r="AR63">
+        <v>2.06</v>
+      </c>
+      <c r="AS63">
+        <v>312</v>
+      </c>
+      <c r="AT63">
+        <v>733</v>
+      </c>
+      <c r="AU63">
+        <v>112</v>
+      </c>
+      <c r="AV63">
+        <v>275</v>
+      </c>
+      <c r="AW63">
+        <v>122</v>
+      </c>
+      <c r="AX63">
+        <v>383</v>
+      </c>
+      <c r="AY63">
+        <v>21</v>
+      </c>
+      <c r="AZ63">
+        <v>27</v>
+      </c>
+      <c r="BA63">
+        <v>1</v>
+      </c>
+      <c r="BB63">
+        <v>7</v>
+      </c>
+      <c r="BC63">
+        <v>15</v>
+      </c>
+      <c r="BD63">
+        <v>22</v>
+      </c>
+      <c r="BE63">
+        <v>14</v>
+      </c>
+      <c r="BF63">
+        <v>40</v>
+      </c>
+      <c r="BG63">
+        <v>0</v>
+      </c>
+      <c r="BH63">
+        <v>5</v>
+      </c>
+      <c r="BI63" t="s">
+        <v>90</v>
+      </c>
+      <c r="BJ63" t="s">
+        <v>90</v>
+      </c>
+      <c r="BK63">
+        <v>13</v>
+      </c>
+      <c r="BL63">
+        <v>11</v>
+      </c>
+      <c r="BM63">
+        <v>8</v>
+      </c>
+      <c r="BN63">
+        <v>4</v>
+      </c>
+      <c r="BO63">
+        <v>12</v>
+      </c>
+      <c r="BP63">
+        <v>0</v>
+      </c>
+      <c r="BQ63">
+        <v>50</v>
+      </c>
+      <c r="BR63">
+        <v>20</v>
+      </c>
+      <c r="BS63">
+        <v>9</v>
+      </c>
+      <c r="BT63">
+        <v>3</v>
+      </c>
+      <c r="BU63" t="s">
+        <v>90</v>
+      </c>
+      <c r="BV63" t="s">
+        <v>90</v>
+      </c>
+      <c r="BW63">
+        <v>37</v>
+      </c>
+      <c r="BX63">
+        <v>36</v>
+      </c>
+      <c r="BY63">
+        <v>21</v>
+      </c>
+      <c r="BZ63">
+        <v>22</v>
+      </c>
+      <c r="CA63">
+        <v>16</v>
+      </c>
+      <c r="CB63">
+        <v>14</v>
+      </c>
+      <c r="CC63">
+        <v>3</v>
+      </c>
+      <c r="CD63">
+        <v>4</v>
+      </c>
+      <c r="CE63" t="s">
+        <v>90</v>
+      </c>
+      <c r="CF63" t="s">
+        <v>90</v>
+      </c>
+      <c r="CG63">
+        <v>2</v>
+      </c>
+      <c r="CH63">
+        <v>0</v>
+      </c>
+      <c r="CI63">
+        <v>0</v>
+      </c>
+      <c r="CJ63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="2:88">
+      <c r="B64" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="C64" t="s">
+        <v>109</v>
+      </c>
+      <c r="D64" t="s">
+        <v>88</v>
+      </c>
+      <c r="E64">
+        <v>1</v>
+      </c>
+      <c r="F64">
+        <v>3</v>
+      </c>
+      <c r="G64">
+        <v>35</v>
+      </c>
+      <c r="H64">
+        <f t="shared" si="0"/>
+        <v>65</v>
+      </c>
+      <c r="I64">
+        <v>1</v>
+      </c>
+      <c r="J64">
+        <v>3.16</v>
+      </c>
+      <c r="K64">
+        <v>11</v>
+      </c>
+      <c r="L64">
+        <v>17</v>
+      </c>
+      <c r="M64">
+        <v>4</v>
+      </c>
+      <c r="N64">
+        <v>8</v>
+      </c>
+      <c r="O64">
+        <v>3</v>
+      </c>
+      <c r="P64">
+        <v>7</v>
+      </c>
+      <c r="Q64">
+        <v>2</v>
+      </c>
+      <c r="R64">
+        <v>4</v>
+      </c>
+      <c r="S64">
+        <v>301</v>
+      </c>
+      <c r="T64">
+        <v>623</v>
+      </c>
+      <c r="U64">
+        <v>8</v>
+      </c>
+      <c r="V64">
+        <v>11</v>
+      </c>
+      <c r="W64">
+        <v>2</v>
+      </c>
+      <c r="X64">
+        <v>6</v>
+      </c>
+      <c r="Y64" t="s">
+        <v>90</v>
+      </c>
+      <c r="Z64" t="s">
+        <v>90</v>
+      </c>
+      <c r="AA64">
+        <v>5</v>
+      </c>
+      <c r="AB64">
+        <v>5</v>
+      </c>
+      <c r="AC64">
+        <v>2</v>
+      </c>
+      <c r="AD64">
+        <v>4</v>
+      </c>
+      <c r="AE64">
+        <v>1</v>
+      </c>
+      <c r="AF64">
+        <v>1</v>
+      </c>
+      <c r="AG64">
+        <v>6</v>
+      </c>
+      <c r="AH64">
+        <v>11</v>
+      </c>
+      <c r="AI64">
+        <v>5</v>
+      </c>
+      <c r="AJ64">
+        <v>6</v>
+      </c>
+      <c r="AK64">
+        <v>0.62</v>
+      </c>
+      <c r="AL64">
+        <v>2.63</v>
+      </c>
+      <c r="AM64">
+        <v>0.38</v>
+      </c>
+      <c r="AN64">
+        <v>0.52</v>
+      </c>
+      <c r="AO64">
+        <v>1</v>
+      </c>
+      <c r="AP64">
+        <v>3.16</v>
+      </c>
+      <c r="AQ64">
+        <v>0.83</v>
+      </c>
+      <c r="AR64">
+        <v>2.89</v>
+      </c>
+      <c r="AS64">
+        <v>367</v>
+      </c>
+      <c r="AT64">
+        <v>683</v>
+      </c>
+      <c r="AU64">
+        <v>177</v>
+      </c>
+      <c r="AV64">
+        <v>259</v>
+      </c>
+      <c r="AW64">
+        <v>124</v>
+      </c>
+      <c r="AX64">
+        <v>364</v>
+      </c>
+      <c r="AY64">
+        <v>23</v>
+      </c>
+      <c r="AZ64">
+        <v>34</v>
+      </c>
+      <c r="BA64">
+        <v>3</v>
+      </c>
+      <c r="BB64">
+        <v>3</v>
+      </c>
+      <c r="BC64">
+        <v>9</v>
+      </c>
+      <c r="BD64">
+        <v>17</v>
+      </c>
+      <c r="BE64">
+        <v>19</v>
+      </c>
+      <c r="BF64">
+        <v>28</v>
+      </c>
+      <c r="BG64">
+        <v>3</v>
+      </c>
+      <c r="BH64">
+        <v>3</v>
+      </c>
+      <c r="BI64" t="s">
+        <v>90</v>
+      </c>
+      <c r="BJ64" t="s">
+        <v>90</v>
+      </c>
+      <c r="BK64">
+        <v>12</v>
+      </c>
+      <c r="BL64">
+        <v>11</v>
+      </c>
+      <c r="BM64">
+        <v>12</v>
+      </c>
+      <c r="BN64">
+        <v>7</v>
+      </c>
+      <c r="BO64">
+        <v>4</v>
+      </c>
+      <c r="BP64">
+        <v>2</v>
+      </c>
+      <c r="BQ64">
+        <v>17</v>
+      </c>
+      <c r="BR64">
+        <v>15</v>
+      </c>
+      <c r="BS64">
+        <v>5</v>
+      </c>
+      <c r="BT64">
+        <v>3</v>
+      </c>
+      <c r="BU64" t="s">
+        <v>90</v>
+      </c>
+      <c r="BV64" t="s">
+        <v>90</v>
+      </c>
+      <c r="BW64">
+        <v>29</v>
+      </c>
+      <c r="BX64">
+        <v>32</v>
+      </c>
+      <c r="BY64">
+        <v>25</v>
+      </c>
+      <c r="BZ64">
+        <v>22</v>
+      </c>
+      <c r="CA64">
+        <v>4</v>
+      </c>
+      <c r="CB64">
+        <v>10</v>
+      </c>
+      <c r="CC64">
+        <v>5</v>
+      </c>
+      <c r="CD64">
+        <v>5</v>
+      </c>
+      <c r="CE64" t="s">
+        <v>90</v>
+      </c>
+      <c r="CF64" t="s">
+        <v>90</v>
+      </c>
+      <c r="CG64">
+        <v>4</v>
+      </c>
+      <c r="CH64">
+        <v>3</v>
+      </c>
+      <c r="CI64">
+        <v>0</v>
+      </c>
+      <c r="CJ64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:88">
+      <c r="B65" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="C65" t="s">
+        <v>112</v>
+      </c>
+      <c r="D65" t="s">
+        <v>94</v>
+      </c>
+      <c r="E65">
+        <v>2</v>
+      </c>
+      <c r="F65">
+        <v>0</v>
+      </c>
+      <c r="G65">
+        <v>66</v>
+      </c>
+      <c r="H65">
+        <f t="shared" si="0"/>
+        <v>34</v>
+      </c>
+      <c r="I65">
+        <v>1.33</v>
+      </c>
+      <c r="J65">
+        <v>0.47</v>
+      </c>
+      <c r="K65">
+        <v>15</v>
+      </c>
+      <c r="L65">
+        <v>9</v>
+      </c>
+      <c r="M65">
+        <v>5</v>
+      </c>
+      <c r="N65">
+        <v>1</v>
+      </c>
+      <c r="O65">
+        <v>2</v>
+      </c>
+      <c r="P65">
+        <v>0</v>
+      </c>
+      <c r="Q65">
+        <v>1</v>
+      </c>
+      <c r="R65">
+        <v>0</v>
+      </c>
+      <c r="S65">
+        <v>499</v>
+      </c>
+      <c r="T65">
+        <v>221</v>
+      </c>
+      <c r="U65">
+        <v>10</v>
+      </c>
+      <c r="V65">
+        <v>7</v>
+      </c>
+      <c r="W65">
+        <v>5</v>
+      </c>
+      <c r="X65">
+        <v>3</v>
+      </c>
+      <c r="Y65" t="s">
+        <v>90</v>
+      </c>
+      <c r="Z65" t="s">
+        <v>90</v>
+      </c>
+      <c r="AA65">
+        <v>5</v>
+      </c>
+      <c r="AB65">
+        <v>5</v>
+      </c>
+      <c r="AC65">
+        <v>5</v>
+      </c>
+      <c r="AD65">
+        <v>3</v>
+      </c>
+      <c r="AE65">
+        <v>1</v>
+      </c>
+      <c r="AF65">
+        <v>1</v>
+      </c>
+      <c r="AG65">
+        <v>12</v>
+      </c>
+      <c r="AH65">
+        <v>7</v>
+      </c>
+      <c r="AI65">
+        <v>3</v>
+      </c>
+      <c r="AJ65">
+        <v>2</v>
+      </c>
+      <c r="AK65">
+        <v>1</v>
+      </c>
+      <c r="AL65">
+        <v>0.37</v>
+      </c>
+      <c r="AM65">
+        <v>0.34</v>
+      </c>
+      <c r="AN65">
+        <v>0.1</v>
+      </c>
+      <c r="AO65">
+        <v>1.33</v>
+      </c>
+      <c r="AP65">
+        <v>0.47</v>
+      </c>
+      <c r="AQ65">
+        <v>2.15</v>
+      </c>
+      <c r="AR65">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="AS65">
+        <v>622</v>
+      </c>
+      <c r="AT65">
+        <v>323</v>
+      </c>
+      <c r="AU65">
+        <v>256</v>
+      </c>
+      <c r="AV65">
+        <v>125</v>
+      </c>
+      <c r="AW65">
+        <v>243</v>
+      </c>
+      <c r="AX65">
+        <v>96</v>
+      </c>
+      <c r="AY65">
+        <v>25</v>
+      </c>
+      <c r="AZ65">
+        <v>34</v>
+      </c>
+      <c r="BA65">
+        <v>6</v>
+      </c>
+      <c r="BB65">
+        <v>3</v>
+      </c>
+      <c r="BC65">
+        <v>27</v>
+      </c>
+      <c r="BD65">
+        <v>28</v>
+      </c>
+      <c r="BE65">
+        <v>27</v>
+      </c>
+      <c r="BF65">
+        <v>16</v>
+      </c>
+      <c r="BG65">
+        <v>3</v>
+      </c>
+      <c r="BH65">
+        <v>2</v>
+      </c>
+      <c r="BI65" t="s">
+        <v>90</v>
+      </c>
+      <c r="BJ65" t="s">
+        <v>90</v>
+      </c>
+      <c r="BK65">
+        <v>11</v>
+      </c>
+      <c r="BL65">
+        <v>18</v>
+      </c>
+      <c r="BM65">
+        <v>6</v>
+      </c>
+      <c r="BN65">
+        <v>12</v>
+      </c>
+      <c r="BO65">
+        <v>3</v>
+      </c>
+      <c r="BP65">
+        <v>5</v>
+      </c>
+      <c r="BQ65">
+        <v>25</v>
+      </c>
+      <c r="BR65">
+        <v>18</v>
+      </c>
+      <c r="BS65">
+        <v>1</v>
+      </c>
+      <c r="BT65">
+        <v>3</v>
+      </c>
+      <c r="BU65" t="s">
+        <v>90</v>
+      </c>
+      <c r="BV65" t="s">
+        <v>90</v>
+      </c>
+      <c r="BW65">
+        <v>53</v>
+      </c>
+      <c r="BX65">
+        <v>47</v>
+      </c>
+      <c r="BY65">
+        <v>25</v>
+      </c>
+      <c r="BZ65">
+        <v>30</v>
+      </c>
+      <c r="CA65">
+        <v>28</v>
+      </c>
+      <c r="CB65">
+        <v>17</v>
+      </c>
+      <c r="CC65">
+        <v>8</v>
+      </c>
+      <c r="CD65">
+        <v>3</v>
+      </c>
+      <c r="CE65" t="s">
+        <v>90</v>
+      </c>
+      <c r="CF65" t="s">
+        <v>90</v>
+      </c>
+      <c r="CG65">
+        <v>2</v>
+      </c>
+      <c r="CH65">
+        <v>3</v>
+      </c>
+      <c r="CI65">
+        <v>0</v>
+      </c>
+      <c r="CJ65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:88">
+      <c r="B66" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="C66" t="s">
+        <v>91</v>
+      </c>
+      <c r="D66" t="s">
+        <v>102</v>
+      </c>
+      <c r="E66">
+        <v>0</v>
+      </c>
+      <c r="F66">
+        <v>3</v>
+      </c>
+      <c r="G66">
+        <v>67</v>
+      </c>
+      <c r="H66">
+        <f t="shared" si="0"/>
+        <v>33</v>
+      </c>
+      <c r="I66">
+        <v>0.54</v>
+      </c>
+      <c r="J66">
+        <v>3.47</v>
+      </c>
+      <c r="K66">
+        <v>14</v>
+      </c>
+      <c r="L66">
+        <v>17</v>
+      </c>
+      <c r="M66">
+        <v>2</v>
+      </c>
+      <c r="N66">
+        <v>11</v>
+      </c>
+      <c r="O66">
+        <v>1</v>
+      </c>
+      <c r="P66">
+        <v>8</v>
+      </c>
+      <c r="Q66">
+        <v>1</v>
+      </c>
+      <c r="R66">
+        <v>5</v>
+      </c>
+      <c r="S66">
+        <v>435</v>
+      </c>
+      <c r="T66">
+        <v>182</v>
+      </c>
+      <c r="U66">
+        <v>10</v>
+      </c>
+      <c r="V66">
+        <v>11</v>
+      </c>
+      <c r="W66">
+        <v>1</v>
+      </c>
+      <c r="X66">
+        <v>4</v>
+      </c>
+      <c r="Y66" t="s">
+        <v>90</v>
+      </c>
+      <c r="Z66" t="s">
+        <v>90</v>
+      </c>
+      <c r="AA66">
+        <v>7</v>
+      </c>
+      <c r="AB66">
+        <v>4</v>
+      </c>
+      <c r="AC66">
+        <v>5</v>
+      </c>
+      <c r="AD66">
+        <v>2</v>
+      </c>
+      <c r="AE66">
+        <v>0</v>
+      </c>
+      <c r="AF66">
+        <v>2</v>
+      </c>
+      <c r="AG66">
+        <v>7</v>
+      </c>
+      <c r="AH66">
+        <v>15</v>
+      </c>
+      <c r="AI66">
+        <v>7</v>
+      </c>
+      <c r="AJ66">
+        <v>2</v>
+      </c>
+      <c r="AK66">
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="AL66">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="AM66">
+        <v>0.26</v>
+      </c>
+      <c r="AN66">
+        <v>1.27</v>
+      </c>
+      <c r="AO66">
+        <v>0.54</v>
+      </c>
+      <c r="AP66">
+        <v>3.47</v>
+      </c>
+      <c r="AQ66">
+        <v>0.09</v>
+      </c>
+      <c r="AR66">
+        <v>3.34</v>
+      </c>
+      <c r="AS66">
+        <v>520</v>
+      </c>
+      <c r="AT66">
+        <v>258</v>
+      </c>
+      <c r="AU66">
+        <v>223</v>
+      </c>
+      <c r="AV66">
+        <v>67</v>
+      </c>
+      <c r="AW66">
+        <v>212</v>
+      </c>
+      <c r="AX66">
+        <v>115</v>
+      </c>
+      <c r="AY66">
+        <v>14</v>
+      </c>
+      <c r="AZ66">
+        <v>15</v>
+      </c>
+      <c r="BA66">
+        <v>7</v>
+      </c>
+      <c r="BB66">
+        <v>4</v>
+      </c>
+      <c r="BC66">
+        <v>24</v>
+      </c>
+      <c r="BD66">
+        <v>20</v>
+      </c>
+      <c r="BE66">
+        <v>22</v>
+      </c>
+      <c r="BF66">
+        <v>30</v>
+      </c>
+      <c r="BG66">
+        <v>3</v>
+      </c>
+      <c r="BH66">
+        <v>8</v>
+      </c>
+      <c r="BI66" t="s">
+        <v>90</v>
+      </c>
+      <c r="BJ66" t="s">
+        <v>90</v>
+      </c>
+      <c r="BK66">
+        <v>14</v>
+      </c>
+      <c r="BL66">
+        <v>21</v>
+      </c>
+      <c r="BM66">
+        <v>8</v>
+      </c>
+      <c r="BN66">
+        <v>13</v>
+      </c>
+      <c r="BO66">
+        <v>1</v>
+      </c>
+      <c r="BP66">
+        <v>5</v>
+      </c>
+      <c r="BQ66">
+        <v>14</v>
+      </c>
+      <c r="BR66">
+        <v>36</v>
+      </c>
+      <c r="BS66">
+        <v>8</v>
+      </c>
+      <c r="BT66">
+        <v>2</v>
+      </c>
+      <c r="BU66" t="s">
+        <v>90</v>
+      </c>
+      <c r="BV66" t="s">
+        <v>90</v>
+      </c>
+      <c r="BW66">
+        <v>38</v>
+      </c>
+      <c r="BX66">
+        <v>44</v>
+      </c>
+      <c r="BY66">
+        <v>26</v>
+      </c>
+      <c r="BZ66">
+        <v>32</v>
+      </c>
+      <c r="CA66">
+        <v>12</v>
+      </c>
+      <c r="CB66">
+        <v>12</v>
+      </c>
+      <c r="CC66">
+        <v>3</v>
+      </c>
+      <c r="CD66">
+        <v>2</v>
+      </c>
+      <c r="CE66" t="s">
+        <v>90</v>
+      </c>
+      <c r="CF66" t="s">
+        <v>90</v>
+      </c>
+      <c r="CG66">
+        <v>1</v>
+      </c>
+      <c r="CH66">
+        <v>0</v>
+      </c>
+      <c r="CI66">
+        <v>0</v>
+      </c>
+      <c r="CJ66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="2:88">
+      <c r="B67" s="5" t="s">
+        <v>161</v>
+      </c>
+      <c r="C67" t="s">
+        <v>113</v>
+      </c>
+      <c r="D67" t="s">
+        <v>92</v>
+      </c>
+      <c r="E67">
+        <v>1</v>
+      </c>
+      <c r="F67">
+        <v>3</v>
+      </c>
+      <c r="G67">
+        <v>47</v>
+      </c>
+      <c r="H67">
+        <f t="shared" si="0"/>
+        <v>53</v>
+      </c>
+      <c r="I67">
+        <v>2.25</v>
+      </c>
+      <c r="J67">
+        <v>1.77</v>
+      </c>
+      <c r="K67">
+        <v>19</v>
+      </c>
+      <c r="L67">
+        <v>16</v>
+      </c>
+      <c r="M67">
+        <v>7</v>
+      </c>
+      <c r="N67">
+        <v>8</v>
+      </c>
+      <c r="O67">
+        <v>5</v>
+      </c>
+      <c r="P67">
+        <v>3</v>
+      </c>
+      <c r="Q67">
+        <v>4</v>
+      </c>
+      <c r="R67">
+        <v>3</v>
+      </c>
+      <c r="S67">
+        <v>383</v>
+      </c>
+      <c r="T67">
+        <v>459</v>
+      </c>
+      <c r="U67">
+        <v>12</v>
+      </c>
+      <c r="V67">
+        <v>12</v>
+      </c>
+      <c r="W67">
+        <v>10</v>
+      </c>
+      <c r="X67">
+        <v>5</v>
+      </c>
+      <c r="Y67" t="s">
+        <v>90</v>
+      </c>
+      <c r="Z67" t="s">
+        <v>90</v>
+      </c>
+      <c r="AA67">
+        <v>7</v>
+      </c>
+      <c r="AB67">
+        <v>5</v>
+      </c>
+      <c r="AC67">
+        <v>5</v>
+      </c>
+      <c r="AD67">
+        <v>3</v>
+      </c>
+      <c r="AE67">
+        <v>1</v>
+      </c>
+      <c r="AF67">
+        <v>0</v>
+      </c>
+      <c r="AG67">
+        <v>10</v>
+      </c>
+      <c r="AH67">
+        <v>11</v>
+      </c>
+      <c r="AI67">
+        <v>9</v>
+      </c>
+      <c r="AJ67">
+        <v>5</v>
+      </c>
+      <c r="AK67">
+        <v>1.5</v>
+      </c>
+      <c r="AL67">
+        <v>1.02</v>
+      </c>
+      <c r="AM67">
+        <v>0.75</v>
+      </c>
+      <c r="AN67">
+        <v>0.75</v>
+      </c>
+      <c r="AO67">
+        <v>2.25</v>
+      </c>
+      <c r="AP67">
+        <v>1.77</v>
+      </c>
+      <c r="AQ67">
+        <v>1.78</v>
+      </c>
+      <c r="AR67">
+        <v>1.54</v>
+      </c>
+      <c r="AS67">
+        <v>438</v>
+      </c>
+      <c r="AT67">
+        <v>522</v>
+      </c>
+      <c r="AU67">
+        <v>177</v>
+      </c>
+      <c r="AV67">
+        <v>322</v>
+      </c>
+      <c r="AW67">
+        <v>206</v>
+      </c>
+      <c r="AX67">
+        <v>137</v>
+      </c>
+      <c r="AY67">
+        <v>10</v>
+      </c>
+      <c r="AZ67">
+        <v>17</v>
+      </c>
+      <c r="BA67">
+        <v>3</v>
+      </c>
+      <c r="BB67">
+        <v>6</v>
+      </c>
+      <c r="BC67">
+        <v>18</v>
+      </c>
+      <c r="BD67">
+        <v>8</v>
+      </c>
+      <c r="BE67">
+        <v>32</v>
+      </c>
+      <c r="BF67">
+        <v>16</v>
+      </c>
+      <c r="BG67">
+        <v>4</v>
+      </c>
+      <c r="BH67">
+        <v>0</v>
+      </c>
+      <c r="BI67" t="s">
+        <v>90</v>
+      </c>
+      <c r="BJ67" t="s">
+        <v>90</v>
+      </c>
+      <c r="BK67">
+        <v>12</v>
+      </c>
+      <c r="BL67">
+        <v>23</v>
+      </c>
+      <c r="BM67">
+        <v>9</v>
+      </c>
+      <c r="BN67">
+        <v>11</v>
+      </c>
+      <c r="BO67">
+        <v>3</v>
+      </c>
+      <c r="BP67">
+        <v>5</v>
+      </c>
+      <c r="BQ67">
+        <v>11</v>
+      </c>
+      <c r="BR67">
+        <v>25</v>
+      </c>
+      <c r="BS67">
+        <v>5</v>
+      </c>
+      <c r="BT67">
+        <v>5</v>
+      </c>
+      <c r="BU67" t="s">
+        <v>90</v>
+      </c>
+      <c r="BV67" t="s">
+        <v>90</v>
+      </c>
+      <c r="BW67">
+        <v>48</v>
+      </c>
+      <c r="BX67">
+        <v>54</v>
+      </c>
+      <c r="BY67">
+        <v>37</v>
+      </c>
+      <c r="BZ67">
+        <v>42</v>
+      </c>
+      <c r="CA67">
+        <v>11</v>
+      </c>
+      <c r="CB67">
+        <v>12</v>
+      </c>
+      <c r="CC67">
+        <v>14</v>
+      </c>
+      <c r="CD67">
+        <v>9</v>
+      </c>
+      <c r="CE67" t="s">
+        <v>90</v>
+      </c>
+      <c r="CF67" t="s">
+        <v>90</v>
+      </c>
+      <c r="CG67">
+        <v>2</v>
+      </c>
+      <c r="CH67">
+        <v>3</v>
+      </c>
+      <c r="CI67">
+        <v>0</v>
+      </c>
+      <c r="CJ67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="2:88">
+      <c r="B68" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="C68" t="s">
+        <v>107</v>
+      </c>
+      <c r="D68" t="s">
+        <v>104</v>
+      </c>
+      <c r="E68">
+        <v>3</v>
+      </c>
+      <c r="F68">
+        <v>2</v>
+      </c>
+      <c r="G68">
+        <v>56</v>
+      </c>
+      <c r="H68">
+        <f t="shared" si="0"/>
+        <v>44</v>
+      </c>
+      <c r="I68">
+        <v>2.41</v>
+      </c>
+      <c r="J68">
+        <v>1.65</v>
+      </c>
+      <c r="K68">
+        <v>11</v>
+      </c>
+      <c r="L68">
+        <v>12</v>
+      </c>
+      <c r="M68">
+        <v>6</v>
+      </c>
+      <c r="N68">
+        <v>4</v>
+      </c>
+      <c r="O68">
+        <v>3</v>
+      </c>
+      <c r="P68">
+        <v>4</v>
+      </c>
+      <c r="Q68">
+        <v>1</v>
+      </c>
+      <c r="R68">
+        <v>2</v>
+      </c>
+      <c r="S68">
+        <v>547</v>
+      </c>
+      <c r="T68">
+        <v>423</v>
+      </c>
+      <c r="U68">
+        <v>3</v>
+      </c>
+      <c r="V68">
+        <v>10</v>
+      </c>
+      <c r="W68">
+        <v>2</v>
+      </c>
+      <c r="X68">
+        <v>2</v>
+      </c>
+      <c r="Y68" t="s">
+        <v>90</v>
+      </c>
+      <c r="Z68" t="s">
+        <v>90</v>
+      </c>
+      <c r="AA68">
+        <v>2</v>
+      </c>
+      <c r="AB68">
+        <v>6</v>
+      </c>
+      <c r="AC68">
+        <v>3</v>
+      </c>
+      <c r="AD68">
+        <v>2</v>
+      </c>
+      <c r="AE68">
+        <v>0</v>
+      </c>
+      <c r="AF68">
+        <v>1</v>
+      </c>
+      <c r="AG68">
+        <v>7</v>
+      </c>
+      <c r="AH68">
+        <v>6</v>
+      </c>
+      <c r="AI68">
+        <v>4</v>
+      </c>
+      <c r="AJ68">
+        <v>6</v>
+      </c>
+      <c r="AK68">
+        <v>0.45</v>
+      </c>
+      <c r="AL68">
+        <v>1.65</v>
+      </c>
+      <c r="AM68">
+        <v>0.37</v>
+      </c>
+      <c r="AN68">
+        <v>0</v>
+      </c>
+      <c r="AO68">
+        <v>0.84</v>
+      </c>
+      <c r="AP68">
+        <v>1.65</v>
+      </c>
+      <c r="AQ68">
+        <v>3.51</v>
+      </c>
+      <c r="AR68">
+        <v>1.83</v>
+      </c>
+      <c r="AS68">
+        <v>601</v>
+      </c>
+      <c r="AT68">
+        <v>464</v>
+      </c>
+      <c r="AU68">
+        <v>358</v>
+      </c>
+      <c r="AV68">
+        <v>180</v>
+      </c>
+      <c r="AW68">
+        <v>189</v>
+      </c>
+      <c r="AX68">
+        <v>243</v>
+      </c>
+      <c r="AY68">
+        <v>24</v>
+      </c>
+      <c r="AZ68">
+        <v>13</v>
+      </c>
+      <c r="BA68">
+        <v>3</v>
+      </c>
+      <c r="BB68">
+        <v>0</v>
+      </c>
+      <c r="BC68">
+        <v>12</v>
+      </c>
+      <c r="BD68">
+        <v>10</v>
+      </c>
+      <c r="BE68">
+        <v>22</v>
+      </c>
+      <c r="BF68">
+        <v>15</v>
+      </c>
+      <c r="BG68">
+        <v>1</v>
+      </c>
+      <c r="BH68">
+        <v>1</v>
+      </c>
+      <c r="BI68" t="s">
+        <v>90</v>
+      </c>
+      <c r="BJ68" t="s">
+        <v>90</v>
+      </c>
+      <c r="BK68">
+        <v>20</v>
+      </c>
+      <c r="BL68">
+        <v>14</v>
+      </c>
+      <c r="BM68">
+        <v>10</v>
+      </c>
+      <c r="BN68">
+        <v>7</v>
+      </c>
+      <c r="BO68">
+        <v>2</v>
+      </c>
+      <c r="BP68">
+        <v>1</v>
+      </c>
+      <c r="BQ68">
+        <v>17</v>
+      </c>
+      <c r="BR68">
+        <v>20</v>
+      </c>
+      <c r="BS68">
+        <v>2</v>
+      </c>
+      <c r="BT68">
+        <v>3</v>
+      </c>
+      <c r="BU68" t="s">
+        <v>90</v>
+      </c>
+      <c r="BV68" t="s">
+        <v>90</v>
+      </c>
+      <c r="BW68">
+        <v>37</v>
+      </c>
+      <c r="BX68">
+        <v>29</v>
+      </c>
+      <c r="BY68">
+        <v>31</v>
+      </c>
+      <c r="BZ68">
+        <v>24</v>
+      </c>
+      <c r="CA68">
+        <v>6</v>
+      </c>
+      <c r="CB68">
+        <v>5</v>
+      </c>
+      <c r="CC68">
+        <v>4</v>
+      </c>
+      <c r="CD68">
+        <v>7</v>
+      </c>
+      <c r="CE68" t="s">
+        <v>90</v>
+      </c>
+      <c r="CF68" t="s">
+        <v>90</v>
+      </c>
+      <c r="CG68">
+        <v>1</v>
+      </c>
+      <c r="CH68">
+        <v>2</v>
+      </c>
+      <c r="CI68">
+        <v>0</v>
+      </c>
+      <c r="CJ68">
         <v>0</v>
       </c>
     </row>

--- a/Serie A 26-27.xlsx
+++ b/Serie A 26-27.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kuba\Desktop\analityczka\26-27\Ekstraklasa 26-27\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{564A9192-0441-473E-945E-DC08336996C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{422877F7-7C16-48DB-ADD7-A23835980234}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="408" xr2:uid="{1DB53276-41DA-4D3A-8911-B22B4D34B4C3}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="824" uniqueCount="163">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="857" uniqueCount="166">
   <si>
     <t>date</t>
   </si>
@@ -529,6 +529,15 @@
   <si>
     <t>Sun 18 October, 18:00</t>
   </si>
+  <si>
+    <t>Mon 19 October, 18:30</t>
+  </si>
+  <si>
+    <t>Mon 19 October, 20:45</t>
+  </si>
+  <si>
+    <t>Fri 23 October, 20:45</t>
+  </si>
 </sst>
 </file>
 
@@ -583,7 +592,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
@@ -602,6 +611,9 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -937,10 +949,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{830FE08A-34EB-4CC3-870F-27849C4CD8BD}">
-  <dimension ref="A1:CJ68"/>
+  <dimension ref="A1:CJ71"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="19.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.5703125" customWidth="1"/>
     <col min="3" max="3" width="13.140625" customWidth="1"/>
     <col min="4" max="4" width="13.85546875" customWidth="1"/>
     <col min="5" max="5" width="14.42578125" customWidth="1"/>
@@ -1261,7 +1273,7 @@
         <v>70</v>
       </c>
       <c r="H2">
-        <f t="shared" ref="H2:H68" si="0">100-G2</f>
+        <f t="shared" ref="H2:H71" si="0">100-G2</f>
         <v>30</v>
       </c>
       <c r="I2">
@@ -8144,7 +8156,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="2:88" ht="25.5">
+    <row r="28" spans="2:88">
       <c r="B28" s="2" t="s">
         <v>126</v>
       </c>
@@ -8408,7 +8420,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="2:88" ht="25.5">
+    <row r="29" spans="2:88">
       <c r="B29" s="2" t="s">
         <v>127</v>
       </c>
@@ -9200,7 +9212,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="2:88" ht="25.5">
+    <row r="32" spans="2:88">
       <c r="B32" s="2" t="s">
         <v>130</v>
       </c>
@@ -16592,7 +16604,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="2:88" ht="25.5">
+    <row r="60" spans="2:88">
       <c r="B60" s="6" t="s">
         <v>154</v>
       </c>
@@ -16856,7 +16868,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="2:88" ht="25.5">
+    <row r="61" spans="2:88">
       <c r="B61" s="6" t="s">
         <v>155</v>
       </c>
@@ -18965,6 +18977,798 @@
         <v>0</v>
       </c>
       <c r="CJ68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:88">
+      <c r="B69" s="7" t="s">
+        <v>163</v>
+      </c>
+      <c r="C69" t="s">
+        <v>89</v>
+      </c>
+      <c r="D69" t="s">
+        <v>97</v>
+      </c>
+      <c r="E69">
+        <v>4</v>
+      </c>
+      <c r="F69">
+        <v>0</v>
+      </c>
+      <c r="G69">
+        <v>46</v>
+      </c>
+      <c r="H69">
+        <f t="shared" si="0"/>
+        <v>54</v>
+      </c>
+      <c r="I69">
+        <v>2.06</v>
+      </c>
+      <c r="J69">
+        <v>2.37</v>
+      </c>
+      <c r="K69">
+        <v>14</v>
+      </c>
+      <c r="L69">
+        <v>16</v>
+      </c>
+      <c r="M69">
+        <v>6</v>
+      </c>
+      <c r="N69">
+        <v>5</v>
+      </c>
+      <c r="O69">
+        <v>3</v>
+      </c>
+      <c r="P69">
+        <v>4</v>
+      </c>
+      <c r="Q69">
+        <v>0</v>
+      </c>
+      <c r="R69">
+        <v>4</v>
+      </c>
+      <c r="S69">
+        <v>347</v>
+      </c>
+      <c r="T69">
+        <v>431</v>
+      </c>
+      <c r="U69">
+        <v>10</v>
+      </c>
+      <c r="V69">
+        <v>14</v>
+      </c>
+      <c r="W69">
+        <v>2</v>
+      </c>
+      <c r="X69">
+        <v>7</v>
+      </c>
+      <c r="Y69" t="s">
+        <v>90</v>
+      </c>
+      <c r="Z69" t="s">
+        <v>90</v>
+      </c>
+      <c r="AA69">
+        <v>5</v>
+      </c>
+      <c r="AB69">
+        <v>9</v>
+      </c>
+      <c r="AC69">
+        <v>3</v>
+      </c>
+      <c r="AD69">
+        <v>2</v>
+      </c>
+      <c r="AE69">
+        <v>2</v>
+      </c>
+      <c r="AF69">
+        <v>0</v>
+      </c>
+      <c r="AG69">
+        <v>10</v>
+      </c>
+      <c r="AH69">
+        <v>13</v>
+      </c>
+      <c r="AI69">
+        <v>4</v>
+      </c>
+      <c r="AJ69">
+        <v>3</v>
+      </c>
+      <c r="AK69">
+        <v>1.83</v>
+      </c>
+      <c r="AL69">
+        <v>1.93</v>
+      </c>
+      <c r="AM69">
+        <v>0.23</v>
+      </c>
+      <c r="AN69">
+        <v>0.44</v>
+      </c>
+      <c r="AO69">
+        <v>2.06</v>
+      </c>
+      <c r="AP69">
+        <v>2.37</v>
+      </c>
+      <c r="AQ69">
+        <v>2.36</v>
+      </c>
+      <c r="AR69">
+        <v>1.26</v>
+      </c>
+      <c r="AS69">
+        <v>419</v>
+      </c>
+      <c r="AT69">
+        <v>503</v>
+      </c>
+      <c r="AU69">
+        <v>157</v>
+      </c>
+      <c r="AV69">
+        <v>231</v>
+      </c>
+      <c r="AW69">
+        <v>190</v>
+      </c>
+      <c r="AX69">
+        <v>200</v>
+      </c>
+      <c r="AY69">
+        <v>29</v>
+      </c>
+      <c r="AZ69">
+        <v>26</v>
+      </c>
+      <c r="BA69">
+        <v>3</v>
+      </c>
+      <c r="BB69">
+        <v>7</v>
+      </c>
+      <c r="BC69">
+        <v>21</v>
+      </c>
+      <c r="BD69">
+        <v>20</v>
+      </c>
+      <c r="BE69">
+        <v>26</v>
+      </c>
+      <c r="BF69">
+        <v>26</v>
+      </c>
+      <c r="BG69">
+        <v>2</v>
+      </c>
+      <c r="BH69">
+        <v>1</v>
+      </c>
+      <c r="BI69" t="s">
+        <v>90</v>
+      </c>
+      <c r="BJ69" t="s">
+        <v>90</v>
+      </c>
+      <c r="BK69">
+        <v>15</v>
+      </c>
+      <c r="BL69">
+        <v>19</v>
+      </c>
+      <c r="BM69">
+        <v>11</v>
+      </c>
+      <c r="BN69">
+        <v>13</v>
+      </c>
+      <c r="BO69">
+        <v>2</v>
+      </c>
+      <c r="BP69">
+        <v>3</v>
+      </c>
+      <c r="BQ69">
+        <v>23</v>
+      </c>
+      <c r="BR69">
+        <v>25</v>
+      </c>
+      <c r="BS69">
+        <v>5</v>
+      </c>
+      <c r="BT69">
+        <v>2</v>
+      </c>
+      <c r="BU69" t="s">
+        <v>90</v>
+      </c>
+      <c r="BV69" t="s">
+        <v>90</v>
+      </c>
+      <c r="BW69">
+        <v>57</v>
+      </c>
+      <c r="BX69">
+        <v>50</v>
+      </c>
+      <c r="BY69">
+        <v>41</v>
+      </c>
+      <c r="BZ69">
+        <v>34</v>
+      </c>
+      <c r="CA69">
+        <v>16</v>
+      </c>
+      <c r="CB69">
+        <v>16</v>
+      </c>
+      <c r="CC69">
+        <v>12</v>
+      </c>
+      <c r="CD69">
+        <v>5</v>
+      </c>
+      <c r="CE69" t="s">
+        <v>90</v>
+      </c>
+      <c r="CF69" t="s">
+        <v>90</v>
+      </c>
+      <c r="CG69">
+        <v>1</v>
+      </c>
+      <c r="CH69">
+        <v>2</v>
+      </c>
+      <c r="CI69">
+        <v>0</v>
+      </c>
+      <c r="CJ69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:88">
+      <c r="B70" s="7" t="s">
+        <v>164</v>
+      </c>
+      <c r="C70" t="s">
+        <v>96</v>
+      </c>
+      <c r="D70" t="s">
+        <v>106</v>
+      </c>
+      <c r="E70">
+        <v>0</v>
+      </c>
+      <c r="F70">
+        <v>3</v>
+      </c>
+      <c r="G70">
+        <v>51</v>
+      </c>
+      <c r="H70">
+        <f t="shared" si="0"/>
+        <v>49</v>
+      </c>
+      <c r="I70">
+        <v>1.57</v>
+      </c>
+      <c r="J70">
+        <v>1.56</v>
+      </c>
+      <c r="K70">
+        <v>25</v>
+      </c>
+      <c r="L70">
+        <v>9</v>
+      </c>
+      <c r="M70">
+        <v>8</v>
+      </c>
+      <c r="N70">
+        <v>3</v>
+      </c>
+      <c r="O70">
+        <v>1</v>
+      </c>
+      <c r="P70">
+        <v>2</v>
+      </c>
+      <c r="Q70">
+        <v>1</v>
+      </c>
+      <c r="R70">
+        <v>0</v>
+      </c>
+      <c r="S70">
+        <v>386</v>
+      </c>
+      <c r="T70">
+        <v>375</v>
+      </c>
+      <c r="U70">
+        <v>7</v>
+      </c>
+      <c r="V70">
+        <v>16</v>
+      </c>
+      <c r="W70">
+        <v>6</v>
+      </c>
+      <c r="X70">
+        <v>2</v>
+      </c>
+      <c r="Y70" t="s">
+        <v>90</v>
+      </c>
+      <c r="Z70" t="s">
+        <v>90</v>
+      </c>
+      <c r="AA70">
+        <v>10</v>
+      </c>
+      <c r="AB70">
+        <v>4</v>
+      </c>
+      <c r="AC70">
+        <v>7</v>
+      </c>
+      <c r="AD70">
+        <v>2</v>
+      </c>
+      <c r="AE70">
+        <v>0</v>
+      </c>
+      <c r="AF70">
+        <v>0</v>
+      </c>
+      <c r="AG70">
+        <v>19</v>
+      </c>
+      <c r="AH70">
+        <v>6</v>
+      </c>
+      <c r="AI70">
+        <v>6</v>
+      </c>
+      <c r="AJ70">
+        <v>3</v>
+      </c>
+      <c r="AK70">
+        <v>1.1200000000000001</v>
+      </c>
+      <c r="AL70">
+        <v>1.3</v>
+      </c>
+      <c r="AM70">
+        <v>0.45</v>
+      </c>
+      <c r="AN70">
+        <v>0.26</v>
+      </c>
+      <c r="AO70">
+        <v>1.57</v>
+      </c>
+      <c r="AP70">
+        <v>1.56</v>
+      </c>
+      <c r="AQ70">
+        <v>1.08</v>
+      </c>
+      <c r="AR70">
+        <v>1.6</v>
+      </c>
+      <c r="AS70">
+        <v>463</v>
+      </c>
+      <c r="AT70">
+        <v>453</v>
+      </c>
+      <c r="AU70">
+        <v>178</v>
+      </c>
+      <c r="AV70">
+        <v>205</v>
+      </c>
+      <c r="AW70">
+        <v>208</v>
+      </c>
+      <c r="AX70">
+        <v>170</v>
+      </c>
+      <c r="AY70">
+        <v>15</v>
+      </c>
+      <c r="AZ70">
+        <v>21</v>
+      </c>
+      <c r="BA70">
+        <v>9</v>
+      </c>
+      <c r="BB70">
+        <v>3</v>
+      </c>
+      <c r="BC70">
+        <v>16</v>
+      </c>
+      <c r="BD70">
+        <v>11</v>
+      </c>
+      <c r="BE70">
+        <v>50</v>
+      </c>
+      <c r="BF70">
+        <v>22</v>
+      </c>
+      <c r="BG70">
+        <v>2</v>
+      </c>
+      <c r="BH70">
+        <v>3</v>
+      </c>
+      <c r="BI70" t="s">
+        <v>90</v>
+      </c>
+      <c r="BJ70" t="s">
+        <v>90</v>
+      </c>
+      <c r="BK70">
+        <v>20</v>
+      </c>
+      <c r="BL70">
+        <v>12</v>
+      </c>
+      <c r="BM70">
+        <v>7</v>
+      </c>
+      <c r="BN70">
+        <v>12</v>
+      </c>
+      <c r="BO70">
+        <v>2</v>
+      </c>
+      <c r="BP70">
+        <v>6</v>
+      </c>
+      <c r="BQ70">
+        <v>8</v>
+      </c>
+      <c r="BR70">
+        <v>32</v>
+      </c>
+      <c r="BS70">
+        <v>0</v>
+      </c>
+      <c r="BT70">
+        <v>8</v>
+      </c>
+      <c r="BU70" t="s">
+        <v>90</v>
+      </c>
+      <c r="BV70" t="s">
+        <v>90</v>
+      </c>
+      <c r="BW70">
+        <v>61</v>
+      </c>
+      <c r="BX70">
+        <v>35</v>
+      </c>
+      <c r="BY70">
+        <v>43</v>
+      </c>
+      <c r="BZ70">
+        <v>24</v>
+      </c>
+      <c r="CA70">
+        <v>18</v>
+      </c>
+      <c r="CB70">
+        <v>11</v>
+      </c>
+      <c r="CC70">
+        <v>9</v>
+      </c>
+      <c r="CD70">
+        <v>6</v>
+      </c>
+      <c r="CE70" t="s">
+        <v>90</v>
+      </c>
+      <c r="CF70" t="s">
+        <v>90</v>
+      </c>
+      <c r="CG70">
+        <v>3</v>
+      </c>
+      <c r="CH70">
+        <v>2</v>
+      </c>
+      <c r="CI70">
+        <v>0</v>
+      </c>
+      <c r="CJ70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:88">
+      <c r="B71" s="6" t="s">
+        <v>165</v>
+      </c>
+      <c r="C71" t="s">
+        <v>106</v>
+      </c>
+      <c r="D71" t="s">
+        <v>89</v>
+      </c>
+      <c r="E71">
+        <v>3</v>
+      </c>
+      <c r="F71">
+        <v>2</v>
+      </c>
+      <c r="G71">
+        <v>51</v>
+      </c>
+      <c r="H71">
+        <f t="shared" si="0"/>
+        <v>49</v>
+      </c>
+      <c r="I71">
+        <v>1.36</v>
+      </c>
+      <c r="J71">
+        <v>0.65</v>
+      </c>
+      <c r="K71">
+        <v>17</v>
+      </c>
+      <c r="L71">
+        <v>7</v>
+      </c>
+      <c r="M71">
+        <v>7</v>
+      </c>
+      <c r="N71">
+        <v>3</v>
+      </c>
+      <c r="O71">
+        <v>3</v>
+      </c>
+      <c r="P71">
+        <v>1</v>
+      </c>
+      <c r="Q71">
+        <v>2</v>
+      </c>
+      <c r="R71">
+        <v>0</v>
+      </c>
+      <c r="S71">
+        <v>360</v>
+      </c>
+      <c r="T71">
+        <v>366</v>
+      </c>
+      <c r="U71">
+        <v>8</v>
+      </c>
+      <c r="V71">
+        <v>4</v>
+      </c>
+      <c r="W71">
+        <v>3</v>
+      </c>
+      <c r="X71">
+        <v>4</v>
+      </c>
+      <c r="Y71" t="s">
+        <v>90</v>
+      </c>
+      <c r="Z71" t="s">
+        <v>90</v>
+      </c>
+      <c r="AA71">
+        <v>7</v>
+      </c>
+      <c r="AB71">
+        <v>3</v>
+      </c>
+      <c r="AC71">
+        <v>3</v>
+      </c>
+      <c r="AD71">
+        <v>1</v>
+      </c>
+      <c r="AE71">
+        <v>0</v>
+      </c>
+      <c r="AF71">
+        <v>0</v>
+      </c>
+      <c r="AG71">
+        <v>8</v>
+      </c>
+      <c r="AH71">
+        <v>3</v>
+      </c>
+      <c r="AI71">
+        <v>9</v>
+      </c>
+      <c r="AJ71">
+        <v>4</v>
+      </c>
+      <c r="AK71">
+        <v>1.28</v>
+      </c>
+      <c r="AL71">
+        <v>0.52</v>
+      </c>
+      <c r="AM71">
+        <v>0.09</v>
+      </c>
+      <c r="AN71">
+        <v>0.13</v>
+      </c>
+      <c r="AO71">
+        <v>1.36</v>
+      </c>
+      <c r="AP71">
+        <v>0.65</v>
+      </c>
+      <c r="AQ71">
+        <v>1.46</v>
+      </c>
+      <c r="AR71">
+        <v>1.3</v>
+      </c>
+      <c r="AS71">
+        <v>456</v>
+      </c>
+      <c r="AT71">
+        <v>441</v>
+      </c>
+      <c r="AU71">
+        <v>186</v>
+      </c>
+      <c r="AV71">
+        <v>188</v>
+      </c>
+      <c r="AW71">
+        <v>174</v>
+      </c>
+      <c r="AX71">
+        <v>178</v>
+      </c>
+      <c r="AY71">
+        <v>27</v>
+      </c>
+      <c r="AZ71">
+        <v>18</v>
+      </c>
+      <c r="BA71">
+        <v>3</v>
+      </c>
+      <c r="BB71">
+        <v>1</v>
+      </c>
+      <c r="BC71">
+        <v>20</v>
+      </c>
+      <c r="BD71">
+        <v>29</v>
+      </c>
+      <c r="BE71">
+        <v>26</v>
+      </c>
+      <c r="BF71">
+        <v>13</v>
+      </c>
+      <c r="BG71">
+        <v>1</v>
+      </c>
+      <c r="BH71">
+        <v>2</v>
+      </c>
+      <c r="BI71" t="s">
+        <v>90</v>
+      </c>
+      <c r="BJ71" t="s">
+        <v>90</v>
+      </c>
+      <c r="BK71">
+        <v>14</v>
+      </c>
+      <c r="BL71">
+        <v>14</v>
+      </c>
+      <c r="BM71">
+        <v>8</v>
+      </c>
+      <c r="BN71">
+        <v>16</v>
+      </c>
+      <c r="BO71">
+        <v>1</v>
+      </c>
+      <c r="BP71">
+        <v>3</v>
+      </c>
+      <c r="BQ71">
+        <v>21</v>
+      </c>
+      <c r="BR71">
+        <v>19</v>
+      </c>
+      <c r="BS71">
+        <v>2</v>
+      </c>
+      <c r="BT71">
+        <v>4</v>
+      </c>
+      <c r="BU71" t="s">
+        <v>90</v>
+      </c>
+      <c r="BV71" t="s">
+        <v>90</v>
+      </c>
+      <c r="BW71">
+        <v>51</v>
+      </c>
+      <c r="BX71">
+        <v>47</v>
+      </c>
+      <c r="BY71">
+        <v>29</v>
+      </c>
+      <c r="BZ71">
+        <v>30</v>
+      </c>
+      <c r="CA71">
+        <v>22</v>
+      </c>
+      <c r="CB71">
+        <v>17</v>
+      </c>
+      <c r="CC71">
+        <v>11</v>
+      </c>
+      <c r="CD71">
+        <v>8</v>
+      </c>
+      <c r="CE71" t="s">
+        <v>90</v>
+      </c>
+      <c r="CF71" t="s">
+        <v>90</v>
+      </c>
+      <c r="CG71">
+        <v>1</v>
+      </c>
+      <c r="CH71">
+        <v>0</v>
+      </c>
+      <c r="CI71">
+        <v>0</v>
+      </c>
+      <c r="CJ71">
         <v>0</v>
       </c>
     </row>

--- a/Serie A 26-27.xlsx
+++ b/Serie A 26-27.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kuba\Desktop\analityczka\26-27\Ekstraklasa 26-27\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{422877F7-7C16-48DB-ADD7-A23835980234}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{758F2812-B5FF-495C-85DC-22DECFAEA570}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="408" xr2:uid="{1DB53276-41DA-4D3A-8911-B22B4D34B4C3}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="376" xr2:uid="{1DB53276-41DA-4D3A-8911-B22B4D34B4C3}"/>
   </bookViews>
   <sheets>
     <sheet name="Arkusz1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="857" uniqueCount="166">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1066" uniqueCount="179">
   <si>
     <t>date</t>
   </si>
@@ -538,6 +538,45 @@
   <si>
     <t>Fri 23 October, 20:45</t>
   </si>
+  <si>
+    <t>Sat 24 October, 15:00</t>
+  </si>
+  <si>
+    <t>Sat 24 October, 18:00</t>
+  </si>
+  <si>
+    <t>Sat 24 October, 20:45</t>
+  </si>
+  <si>
+    <t>Sun 25 October, 12:30</t>
+  </si>
+  <si>
+    <t>Sun 25 October, 15:00</t>
+  </si>
+  <si>
+    <t>Sun 25 October, 18:05</t>
+  </si>
+  <si>
+    <t>Sun 25 October, 20:45</t>
+  </si>
+  <si>
+    <t>Tue 27 October, 20:45</t>
+  </si>
+  <si>
+    <t>Tue 27 October, 18:30</t>
+  </si>
+  <si>
+    <t>Wed 28 October, 18:30</t>
+  </si>
+  <si>
+    <t>Wed 28 October, 20:45</t>
+  </si>
+  <si>
+    <t>Thu 29 October, 18:30</t>
+  </si>
+  <si>
+    <t>Thu 29 October, 20:45</t>
+  </si>
 </sst>
 </file>
 
@@ -592,7 +631,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
@@ -614,6 +653,12 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -949,7 +994,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{830FE08A-34EB-4CC3-870F-27849C4CD8BD}">
-  <dimension ref="A1:CJ71"/>
+  <dimension ref="A1:CJ90"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="21.5703125" customWidth="1"/>
@@ -1273,7 +1318,7 @@
         <v>70</v>
       </c>
       <c r="H2">
-        <f t="shared" ref="H2:H71" si="0">100-G2</f>
+        <f t="shared" ref="H2:H90" si="0">100-G2</f>
         <v>30</v>
       </c>
       <c r="I2">
@@ -19769,6 +19814,5022 @@
         <v>0</v>
       </c>
       <c r="CJ71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:88">
+      <c r="B72" s="8" t="s">
+        <v>166</v>
+      </c>
+      <c r="C72" t="s">
+        <v>97</v>
+      </c>
+      <c r="D72" t="s">
+        <v>109</v>
+      </c>
+      <c r="E72">
+        <v>0</v>
+      </c>
+      <c r="F72">
+        <v>2</v>
+      </c>
+      <c r="G72">
+        <v>57</v>
+      </c>
+      <c r="H72">
+        <f t="shared" si="0"/>
+        <v>43</v>
+      </c>
+      <c r="I72">
+        <v>0.52</v>
+      </c>
+      <c r="J72">
+        <v>1.66</v>
+      </c>
+      <c r="K72">
+        <v>4</v>
+      </c>
+      <c r="L72">
+        <v>10</v>
+      </c>
+      <c r="M72">
+        <v>1</v>
+      </c>
+      <c r="N72">
+        <v>5</v>
+      </c>
+      <c r="O72">
+        <v>0</v>
+      </c>
+      <c r="P72">
+        <v>3</v>
+      </c>
+      <c r="Q72">
+        <v>0</v>
+      </c>
+      <c r="R72">
+        <v>1</v>
+      </c>
+      <c r="S72">
+        <v>435</v>
+      </c>
+      <c r="T72">
+        <v>317</v>
+      </c>
+      <c r="U72">
+        <v>25</v>
+      </c>
+      <c r="V72">
+        <v>13</v>
+      </c>
+      <c r="W72">
+        <v>1</v>
+      </c>
+      <c r="X72">
+        <v>6</v>
+      </c>
+      <c r="Y72" t="s">
+        <v>90</v>
+      </c>
+      <c r="Z72" t="s">
+        <v>90</v>
+      </c>
+      <c r="AA72">
+        <v>3</v>
+      </c>
+      <c r="AB72">
+        <v>2</v>
+      </c>
+      <c r="AC72">
+        <v>0</v>
+      </c>
+      <c r="AD72">
+        <v>3</v>
+      </c>
+      <c r="AE72">
+        <v>0</v>
+      </c>
+      <c r="AF72">
+        <v>0</v>
+      </c>
+      <c r="AG72">
+        <v>4</v>
+      </c>
+      <c r="AH72">
+        <v>5</v>
+      </c>
+      <c r="AI72">
+        <v>0</v>
+      </c>
+      <c r="AJ72">
+        <v>5</v>
+      </c>
+      <c r="AK72">
+        <v>0.39</v>
+      </c>
+      <c r="AL72">
+        <v>0.23</v>
+      </c>
+      <c r="AM72">
+        <v>0.13</v>
+      </c>
+      <c r="AN72">
+        <v>0.64</v>
+      </c>
+      <c r="AO72">
+        <v>0.52</v>
+      </c>
+      <c r="AP72">
+        <v>0.87</v>
+      </c>
+      <c r="AQ72">
+        <v>0.81</v>
+      </c>
+      <c r="AR72">
+        <v>1.93</v>
+      </c>
+      <c r="AS72">
+        <v>512</v>
+      </c>
+      <c r="AT72">
+        <v>379</v>
+      </c>
+      <c r="AU72">
+        <v>283</v>
+      </c>
+      <c r="AV72">
+        <v>163</v>
+      </c>
+      <c r="AW72">
+        <v>152</v>
+      </c>
+      <c r="AX72">
+        <v>154</v>
+      </c>
+      <c r="AY72">
+        <v>20</v>
+      </c>
+      <c r="AZ72">
+        <v>16</v>
+      </c>
+      <c r="BA72">
+        <v>5</v>
+      </c>
+      <c r="BB72">
+        <v>3</v>
+      </c>
+      <c r="BC72">
+        <v>24</v>
+      </c>
+      <c r="BD72">
+        <v>20</v>
+      </c>
+      <c r="BE72">
+        <v>14</v>
+      </c>
+      <c r="BF72">
+        <v>10</v>
+      </c>
+      <c r="BG72">
+        <v>2</v>
+      </c>
+      <c r="BH72">
+        <v>1</v>
+      </c>
+      <c r="BI72" t="s">
+        <v>90</v>
+      </c>
+      <c r="BJ72" t="s">
+        <v>90</v>
+      </c>
+      <c r="BK72">
+        <v>11</v>
+      </c>
+      <c r="BL72">
+        <v>20</v>
+      </c>
+      <c r="BM72">
+        <v>6</v>
+      </c>
+      <c r="BN72">
+        <v>10</v>
+      </c>
+      <c r="BO72">
+        <v>2</v>
+      </c>
+      <c r="BP72">
+        <v>0</v>
+      </c>
+      <c r="BQ72">
+        <v>25</v>
+      </c>
+      <c r="BR72">
+        <v>27</v>
+      </c>
+      <c r="BS72">
+        <v>3</v>
+      </c>
+      <c r="BT72">
+        <v>1</v>
+      </c>
+      <c r="BU72" t="s">
+        <v>90</v>
+      </c>
+      <c r="BV72" t="s">
+        <v>90</v>
+      </c>
+      <c r="BW72">
+        <v>44</v>
+      </c>
+      <c r="BX72">
+        <v>61</v>
+      </c>
+      <c r="BY72">
+        <v>29</v>
+      </c>
+      <c r="BZ72">
+        <v>52</v>
+      </c>
+      <c r="CA72">
+        <v>15</v>
+      </c>
+      <c r="CB72">
+        <v>9</v>
+      </c>
+      <c r="CC72">
+        <v>6</v>
+      </c>
+      <c r="CD72">
+        <v>8</v>
+      </c>
+      <c r="CE72" t="s">
+        <v>90</v>
+      </c>
+      <c r="CF72" t="s">
+        <v>90</v>
+      </c>
+      <c r="CG72">
+        <v>3</v>
+      </c>
+      <c r="CH72">
+        <v>1</v>
+      </c>
+      <c r="CI72">
+        <v>0</v>
+      </c>
+      <c r="CJ72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="2:88">
+      <c r="B73" s="8" t="s">
+        <v>166</v>
+      </c>
+      <c r="C73" t="s">
+        <v>92</v>
+      </c>
+      <c r="D73" t="s">
+        <v>105</v>
+      </c>
+      <c r="E73">
+        <v>2</v>
+      </c>
+      <c r="F73">
+        <v>0</v>
+      </c>
+      <c r="G73">
+        <v>56</v>
+      </c>
+      <c r="H73">
+        <f t="shared" si="0"/>
+        <v>44</v>
+      </c>
+      <c r="I73">
+        <v>2.0699999999999998</v>
+      </c>
+      <c r="J73">
+        <v>0.33</v>
+      </c>
+      <c r="K73">
+        <v>14</v>
+      </c>
+      <c r="L73">
+        <v>7</v>
+      </c>
+      <c r="M73">
+        <v>6</v>
+      </c>
+      <c r="N73">
+        <v>0</v>
+      </c>
+      <c r="O73">
+        <v>4</v>
+      </c>
+      <c r="P73">
+        <v>0</v>
+      </c>
+      <c r="Q73">
+        <v>2</v>
+      </c>
+      <c r="R73">
+        <v>0</v>
+      </c>
+      <c r="S73">
+        <v>528</v>
+      </c>
+      <c r="T73">
+        <v>399</v>
+      </c>
+      <c r="U73">
+        <v>14</v>
+      </c>
+      <c r="V73">
+        <v>10</v>
+      </c>
+      <c r="W73">
+        <v>6</v>
+      </c>
+      <c r="X73">
+        <v>4</v>
+      </c>
+      <c r="Y73" t="s">
+        <v>90</v>
+      </c>
+      <c r="Z73" t="s">
+        <v>90</v>
+      </c>
+      <c r="AA73">
+        <v>4</v>
+      </c>
+      <c r="AB73">
+        <v>5</v>
+      </c>
+      <c r="AC73">
+        <v>4</v>
+      </c>
+      <c r="AD73">
+        <v>2</v>
+      </c>
+      <c r="AE73">
+        <v>1</v>
+      </c>
+      <c r="AF73">
+        <v>0</v>
+      </c>
+      <c r="AG73">
+        <v>12</v>
+      </c>
+      <c r="AH73">
+        <v>4</v>
+      </c>
+      <c r="AI73">
+        <v>2</v>
+      </c>
+      <c r="AJ73">
+        <v>3</v>
+      </c>
+      <c r="AK73">
+        <v>1.89</v>
+      </c>
+      <c r="AL73">
+        <v>0.23</v>
+      </c>
+      <c r="AM73">
+        <v>0.19</v>
+      </c>
+      <c r="AN73">
+        <v>0.09</v>
+      </c>
+      <c r="AO73">
+        <v>2.0699999999999998</v>
+      </c>
+      <c r="AP73">
+        <v>0.33</v>
+      </c>
+      <c r="AQ73">
+        <v>2.1800000000000002</v>
+      </c>
+      <c r="AR73">
+        <v>0</v>
+      </c>
+      <c r="AS73">
+        <v>582</v>
+      </c>
+      <c r="AT73">
+        <v>462</v>
+      </c>
+      <c r="AU73">
+        <v>246</v>
+      </c>
+      <c r="AV73">
+        <v>195</v>
+      </c>
+      <c r="AW73">
+        <v>282</v>
+      </c>
+      <c r="AX73">
+        <v>204</v>
+      </c>
+      <c r="AY73">
+        <v>19</v>
+      </c>
+      <c r="AZ73">
+        <v>12</v>
+      </c>
+      <c r="BA73">
+        <v>3</v>
+      </c>
+      <c r="BB73">
+        <v>4</v>
+      </c>
+      <c r="BC73">
+        <v>13</v>
+      </c>
+      <c r="BD73">
+        <v>17</v>
+      </c>
+      <c r="BE73">
+        <v>26</v>
+      </c>
+      <c r="BF73">
+        <v>25</v>
+      </c>
+      <c r="BG73">
+        <v>2</v>
+      </c>
+      <c r="BH73">
+        <v>5</v>
+      </c>
+      <c r="BI73" t="s">
+        <v>90</v>
+      </c>
+      <c r="BJ73" t="s">
+        <v>90</v>
+      </c>
+      <c r="BK73">
+        <v>14</v>
+      </c>
+      <c r="BL73">
+        <v>13</v>
+      </c>
+      <c r="BM73">
+        <v>11</v>
+      </c>
+      <c r="BN73">
+        <v>9</v>
+      </c>
+      <c r="BO73">
+        <v>2</v>
+      </c>
+      <c r="BP73">
+        <v>4</v>
+      </c>
+      <c r="BQ73">
+        <v>21</v>
+      </c>
+      <c r="BR73">
+        <v>22</v>
+      </c>
+      <c r="BS73">
+        <v>0</v>
+      </c>
+      <c r="BT73">
+        <v>4</v>
+      </c>
+      <c r="BU73" t="s">
+        <v>90</v>
+      </c>
+      <c r="BV73" t="s">
+        <v>90</v>
+      </c>
+      <c r="BW73">
+        <v>33</v>
+      </c>
+      <c r="BX73">
+        <v>42</v>
+      </c>
+      <c r="BY73">
+        <v>29</v>
+      </c>
+      <c r="BZ73">
+        <v>36</v>
+      </c>
+      <c r="CA73">
+        <v>4</v>
+      </c>
+      <c r="CB73">
+        <v>6</v>
+      </c>
+      <c r="CC73">
+        <v>6</v>
+      </c>
+      <c r="CD73">
+        <v>10</v>
+      </c>
+      <c r="CE73" t="s">
+        <v>90</v>
+      </c>
+      <c r="CF73" t="s">
+        <v>90</v>
+      </c>
+      <c r="CG73">
+        <v>2</v>
+      </c>
+      <c r="CH73">
+        <v>2</v>
+      </c>
+      <c r="CI73">
+        <v>0</v>
+      </c>
+      <c r="CJ73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:88">
+      <c r="B74" s="8" t="s">
+        <v>167</v>
+      </c>
+      <c r="C74" t="s">
+        <v>95</v>
+      </c>
+      <c r="D74" t="s">
+        <v>112</v>
+      </c>
+      <c r="E74">
+        <v>3</v>
+      </c>
+      <c r="F74">
+        <v>3</v>
+      </c>
+      <c r="G74">
+        <v>39</v>
+      </c>
+      <c r="H74">
+        <f t="shared" si="0"/>
+        <v>61</v>
+      </c>
+      <c r="I74">
+        <v>2.44</v>
+      </c>
+      <c r="J74">
+        <v>1.9</v>
+      </c>
+      <c r="K74">
+        <v>15</v>
+      </c>
+      <c r="L74">
+        <v>24</v>
+      </c>
+      <c r="M74">
+        <v>9</v>
+      </c>
+      <c r="N74">
+        <v>4</v>
+      </c>
+      <c r="O74">
+        <v>4</v>
+      </c>
+      <c r="P74">
+        <v>2</v>
+      </c>
+      <c r="Q74">
+        <v>3</v>
+      </c>
+      <c r="R74">
+        <v>0</v>
+      </c>
+      <c r="S74">
+        <v>296</v>
+      </c>
+      <c r="T74">
+        <v>502</v>
+      </c>
+      <c r="U74">
+        <v>6</v>
+      </c>
+      <c r="V74">
+        <v>11</v>
+      </c>
+      <c r="W74">
+        <v>2</v>
+      </c>
+      <c r="X74">
+        <v>11</v>
+      </c>
+      <c r="Y74" t="s">
+        <v>90</v>
+      </c>
+      <c r="Z74" t="s">
+        <v>90</v>
+      </c>
+      <c r="AA74">
+        <v>5</v>
+      </c>
+      <c r="AB74">
+        <v>7</v>
+      </c>
+      <c r="AC74">
+        <v>1</v>
+      </c>
+      <c r="AD74">
+        <v>13</v>
+      </c>
+      <c r="AE74">
+        <v>0</v>
+      </c>
+      <c r="AF74">
+        <v>1</v>
+      </c>
+      <c r="AG74">
+        <v>10</v>
+      </c>
+      <c r="AH74">
+        <v>14</v>
+      </c>
+      <c r="AI74">
+        <v>5</v>
+      </c>
+      <c r="AJ74">
+        <v>10</v>
+      </c>
+      <c r="AK74">
+        <v>2.2799999999999998</v>
+      </c>
+      <c r="AL74">
+        <v>1.29</v>
+      </c>
+      <c r="AM74">
+        <v>0.15</v>
+      </c>
+      <c r="AN74">
+        <v>0.61</v>
+      </c>
+      <c r="AO74">
+        <v>2.44</v>
+      </c>
+      <c r="AP74">
+        <v>1.9</v>
+      </c>
+      <c r="AQ74">
+        <v>1.92</v>
+      </c>
+      <c r="AR74">
+        <v>1.93</v>
+      </c>
+      <c r="AS74">
+        <v>378</v>
+      </c>
+      <c r="AT74">
+        <v>582</v>
+      </c>
+      <c r="AU74">
+        <v>188</v>
+      </c>
+      <c r="AV74">
+        <v>173</v>
+      </c>
+      <c r="AW74">
+        <v>108</v>
+      </c>
+      <c r="AX74">
+        <v>329</v>
+      </c>
+      <c r="AY74">
+        <v>16</v>
+      </c>
+      <c r="AZ74">
+        <v>17</v>
+      </c>
+      <c r="BA74">
+        <v>3</v>
+      </c>
+      <c r="BB74">
+        <v>8</v>
+      </c>
+      <c r="BC74">
+        <v>15</v>
+      </c>
+      <c r="BD74">
+        <v>25</v>
+      </c>
+      <c r="BE74">
+        <v>21</v>
+      </c>
+      <c r="BF74">
+        <v>47</v>
+      </c>
+      <c r="BG74">
+        <v>0</v>
+      </c>
+      <c r="BH74">
+        <v>1</v>
+      </c>
+      <c r="BI74" t="s">
+        <v>90</v>
+      </c>
+      <c r="BJ74" t="s">
+        <v>90</v>
+      </c>
+      <c r="BK74">
+        <v>15</v>
+      </c>
+      <c r="BL74">
+        <v>15</v>
+      </c>
+      <c r="BM74">
+        <v>13</v>
+      </c>
+      <c r="BN74">
+        <v>9</v>
+      </c>
+      <c r="BO74">
+        <v>12</v>
+      </c>
+      <c r="BP74">
+        <v>2</v>
+      </c>
+      <c r="BQ74">
+        <v>36</v>
+      </c>
+      <c r="BR74">
+        <v>11</v>
+      </c>
+      <c r="BS74">
+        <v>1</v>
+      </c>
+      <c r="BT74">
+        <v>5</v>
+      </c>
+      <c r="BU74" t="s">
+        <v>90</v>
+      </c>
+      <c r="BV74" t="s">
+        <v>90</v>
+      </c>
+      <c r="BW74">
+        <v>44</v>
+      </c>
+      <c r="BX74">
+        <v>43</v>
+      </c>
+      <c r="BY74">
+        <v>32</v>
+      </c>
+      <c r="BZ74">
+        <v>29</v>
+      </c>
+      <c r="CA74">
+        <v>12</v>
+      </c>
+      <c r="CB74">
+        <v>14</v>
+      </c>
+      <c r="CC74">
+        <v>6</v>
+      </c>
+      <c r="CD74">
+        <v>8</v>
+      </c>
+      <c r="CE74" t="s">
+        <v>90</v>
+      </c>
+      <c r="CF74" t="s">
+        <v>90</v>
+      </c>
+      <c r="CG74">
+        <v>1</v>
+      </c>
+      <c r="CH74">
+        <v>4</v>
+      </c>
+      <c r="CI74">
+        <v>0</v>
+      </c>
+      <c r="CJ74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:88">
+      <c r="B75" s="8" t="s">
+        <v>168</v>
+      </c>
+      <c r="C75" t="s">
+        <v>110</v>
+      </c>
+      <c r="D75" t="s">
+        <v>96</v>
+      </c>
+      <c r="E75">
+        <v>2</v>
+      </c>
+      <c r="F75">
+        <v>1</v>
+      </c>
+      <c r="G75">
+        <v>68</v>
+      </c>
+      <c r="H75">
+        <f t="shared" si="0"/>
+        <v>32</v>
+      </c>
+      <c r="I75">
+        <v>1.74</v>
+      </c>
+      <c r="J75">
+        <v>0.81</v>
+      </c>
+      <c r="K75">
+        <v>21</v>
+      </c>
+      <c r="L75">
+        <v>10</v>
+      </c>
+      <c r="M75">
+        <v>5</v>
+      </c>
+      <c r="N75">
+        <v>4</v>
+      </c>
+      <c r="O75">
+        <v>4</v>
+      </c>
+      <c r="P75">
+        <v>3</v>
+      </c>
+      <c r="Q75">
+        <v>4</v>
+      </c>
+      <c r="R75">
+        <v>3</v>
+      </c>
+      <c r="S75">
+        <v>572</v>
+      </c>
+      <c r="T75">
+        <v>212</v>
+      </c>
+      <c r="U75">
+        <v>5</v>
+      </c>
+      <c r="V75">
+        <v>12</v>
+      </c>
+      <c r="W75">
+        <v>8</v>
+      </c>
+      <c r="X75">
+        <v>3</v>
+      </c>
+      <c r="Y75" t="s">
+        <v>90</v>
+      </c>
+      <c r="Z75" t="s">
+        <v>90</v>
+      </c>
+      <c r="AA75">
+        <v>13</v>
+      </c>
+      <c r="AB75">
+        <v>5</v>
+      </c>
+      <c r="AC75">
+        <v>3</v>
+      </c>
+      <c r="AD75">
+        <v>1</v>
+      </c>
+      <c r="AE75">
+        <v>1</v>
+      </c>
+      <c r="AF75">
+        <v>0</v>
+      </c>
+      <c r="AG75">
+        <v>15</v>
+      </c>
+      <c r="AH75">
+        <v>8</v>
+      </c>
+      <c r="AI75">
+        <v>6</v>
+      </c>
+      <c r="AJ75">
+        <v>2</v>
+      </c>
+      <c r="AK75">
+        <v>1.4</v>
+      </c>
+      <c r="AL75">
+        <v>0.56999999999999995</v>
+      </c>
+      <c r="AM75">
+        <v>0.34</v>
+      </c>
+      <c r="AN75">
+        <v>0.24</v>
+      </c>
+      <c r="AO75">
+        <v>1.74</v>
+      </c>
+      <c r="AP75">
+        <v>0.81</v>
+      </c>
+      <c r="AQ75">
+        <v>0.83</v>
+      </c>
+      <c r="AR75">
+        <v>1.18</v>
+      </c>
+      <c r="AS75">
+        <v>643</v>
+      </c>
+      <c r="AT75">
+        <v>295</v>
+      </c>
+      <c r="AU75">
+        <v>207</v>
+      </c>
+      <c r="AV75">
+        <v>102</v>
+      </c>
+      <c r="AW75">
+        <v>365</v>
+      </c>
+      <c r="AX75">
+        <v>110</v>
+      </c>
+      <c r="AY75">
+        <v>27</v>
+      </c>
+      <c r="AZ75">
+        <v>30</v>
+      </c>
+      <c r="BA75">
+        <v>9</v>
+      </c>
+      <c r="BB75">
+        <v>5</v>
+      </c>
+      <c r="BC75">
+        <v>20</v>
+      </c>
+      <c r="BD75">
+        <v>18</v>
+      </c>
+      <c r="BE75">
+        <v>54</v>
+      </c>
+      <c r="BF75">
+        <v>15</v>
+      </c>
+      <c r="BG75">
+        <v>2</v>
+      </c>
+      <c r="BH75">
+        <v>3</v>
+      </c>
+      <c r="BI75" t="s">
+        <v>90</v>
+      </c>
+      <c r="BJ75" t="s">
+        <v>90</v>
+      </c>
+      <c r="BK75">
+        <v>13</v>
+      </c>
+      <c r="BL75">
+        <v>19</v>
+      </c>
+      <c r="BM75">
+        <v>12</v>
+      </c>
+      <c r="BN75">
+        <v>11</v>
+      </c>
+      <c r="BO75">
+        <v>1</v>
+      </c>
+      <c r="BP75">
+        <v>3</v>
+      </c>
+      <c r="BQ75">
+        <v>27</v>
+      </c>
+      <c r="BR75">
+        <v>36</v>
+      </c>
+      <c r="BS75">
+        <v>3</v>
+      </c>
+      <c r="BT75">
+        <v>4</v>
+      </c>
+      <c r="BU75" t="s">
+        <v>90</v>
+      </c>
+      <c r="BV75" t="s">
+        <v>90</v>
+      </c>
+      <c r="BW75">
+        <v>54</v>
+      </c>
+      <c r="BX75">
+        <v>50</v>
+      </c>
+      <c r="BY75">
+        <v>33</v>
+      </c>
+      <c r="BZ75">
+        <v>29</v>
+      </c>
+      <c r="CA75">
+        <v>21</v>
+      </c>
+      <c r="CB75">
+        <v>21</v>
+      </c>
+      <c r="CC75">
+        <v>10</v>
+      </c>
+      <c r="CD75">
+        <v>5</v>
+      </c>
+      <c r="CE75" t="s">
+        <v>90</v>
+      </c>
+      <c r="CF75" t="s">
+        <v>90</v>
+      </c>
+      <c r="CG75">
+        <v>1</v>
+      </c>
+      <c r="CH75">
+        <v>1</v>
+      </c>
+      <c r="CI75">
+        <v>0</v>
+      </c>
+      <c r="CJ75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:88">
+      <c r="B76" s="8" t="s">
+        <v>169</v>
+      </c>
+      <c r="C76" t="s">
+        <v>88</v>
+      </c>
+      <c r="D76" t="s">
+        <v>113</v>
+      </c>
+      <c r="E76">
+        <v>2</v>
+      </c>
+      <c r="F76">
+        <v>1</v>
+      </c>
+      <c r="G76">
+        <v>63</v>
+      </c>
+      <c r="H76">
+        <f t="shared" si="0"/>
+        <v>37</v>
+      </c>
+      <c r="I76">
+        <v>3.15</v>
+      </c>
+      <c r="J76">
+        <v>0.24</v>
+      </c>
+      <c r="K76">
+        <v>33</v>
+      </c>
+      <c r="L76">
+        <v>7</v>
+      </c>
+      <c r="M76">
+        <v>11</v>
+      </c>
+      <c r="N76">
+        <v>2</v>
+      </c>
+      <c r="O76">
+        <v>4</v>
+      </c>
+      <c r="P76">
+        <v>0</v>
+      </c>
+      <c r="Q76">
+        <v>3</v>
+      </c>
+      <c r="R76">
+        <v>0</v>
+      </c>
+      <c r="S76">
+        <v>512</v>
+      </c>
+      <c r="T76">
+        <v>269</v>
+      </c>
+      <c r="U76">
+        <v>13</v>
+      </c>
+      <c r="V76">
+        <v>14</v>
+      </c>
+      <c r="W76">
+        <v>6</v>
+      </c>
+      <c r="X76">
+        <v>1</v>
+      </c>
+      <c r="Y76" t="s">
+        <v>90</v>
+      </c>
+      <c r="Z76" t="s">
+        <v>90</v>
+      </c>
+      <c r="AA76">
+        <v>17</v>
+      </c>
+      <c r="AB76">
+        <v>0</v>
+      </c>
+      <c r="AC76">
+        <v>5</v>
+      </c>
+      <c r="AD76">
+        <v>5</v>
+      </c>
+      <c r="AE76">
+        <v>2</v>
+      </c>
+      <c r="AF76">
+        <v>0</v>
+      </c>
+      <c r="AG76">
+        <v>26</v>
+      </c>
+      <c r="AH76">
+        <v>3</v>
+      </c>
+      <c r="AI76">
+        <v>7</v>
+      </c>
+      <c r="AJ76">
+        <v>4</v>
+      </c>
+      <c r="AK76">
+        <v>2.0099999999999998</v>
+      </c>
+      <c r="AL76">
+        <v>0.2</v>
+      </c>
+      <c r="AM76">
+        <v>0.35</v>
+      </c>
+      <c r="AN76">
+        <v>0.04</v>
+      </c>
+      <c r="AO76">
+        <v>2.36</v>
+      </c>
+      <c r="AP76">
+        <v>0.24</v>
+      </c>
+      <c r="AQ76">
+        <v>3</v>
+      </c>
+      <c r="AR76">
+        <v>0.16</v>
+      </c>
+      <c r="AS76">
+        <v>566</v>
+      </c>
+      <c r="AT76">
+        <v>339</v>
+      </c>
+      <c r="AU76">
+        <v>163</v>
+      </c>
+      <c r="AV76">
+        <v>173</v>
+      </c>
+      <c r="AW76">
+        <v>349</v>
+      </c>
+      <c r="AX76">
+        <v>96</v>
+      </c>
+      <c r="AY76">
+        <v>22</v>
+      </c>
+      <c r="AZ76">
+        <v>22</v>
+      </c>
+      <c r="BA76">
+        <v>13</v>
+      </c>
+      <c r="BB76">
+        <v>3</v>
+      </c>
+      <c r="BC76">
+        <v>15</v>
+      </c>
+      <c r="BD76">
+        <v>15</v>
+      </c>
+      <c r="BE76">
+        <v>58</v>
+      </c>
+      <c r="BF76">
+        <v>13</v>
+      </c>
+      <c r="BG76">
+        <v>1</v>
+      </c>
+      <c r="BH76">
+        <v>3</v>
+      </c>
+      <c r="BI76" t="s">
+        <v>90</v>
+      </c>
+      <c r="BJ76" t="s">
+        <v>90</v>
+      </c>
+      <c r="BK76">
+        <v>20</v>
+      </c>
+      <c r="BL76">
+        <v>17</v>
+      </c>
+      <c r="BM76">
+        <v>11</v>
+      </c>
+      <c r="BN76">
+        <v>6</v>
+      </c>
+      <c r="BO76">
+        <v>5</v>
+      </c>
+      <c r="BP76">
+        <v>6</v>
+      </c>
+      <c r="BQ76">
+        <v>12</v>
+      </c>
+      <c r="BR76">
+        <v>31</v>
+      </c>
+      <c r="BS76">
+        <v>1</v>
+      </c>
+      <c r="BT76">
+        <v>9</v>
+      </c>
+      <c r="BU76" t="s">
+        <v>90</v>
+      </c>
+      <c r="BV76" t="s">
+        <v>90</v>
+      </c>
+      <c r="BW76">
+        <v>53</v>
+      </c>
+      <c r="BX76">
+        <v>45</v>
+      </c>
+      <c r="BY76">
+        <v>40</v>
+      </c>
+      <c r="BZ76">
+        <v>32</v>
+      </c>
+      <c r="CA76">
+        <v>13</v>
+      </c>
+      <c r="CB76">
+        <v>13</v>
+      </c>
+      <c r="CC76">
+        <v>7</v>
+      </c>
+      <c r="CD76">
+        <v>3</v>
+      </c>
+      <c r="CE76" t="s">
+        <v>90</v>
+      </c>
+      <c r="CF76" t="s">
+        <v>90</v>
+      </c>
+      <c r="CG76">
+        <v>0</v>
+      </c>
+      <c r="CH76">
+        <v>3</v>
+      </c>
+      <c r="CI76">
+        <v>0</v>
+      </c>
+      <c r="CJ76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="2:88">
+      <c r="B77" s="8" t="s">
+        <v>170</v>
+      </c>
+      <c r="C77" t="s">
+        <v>104</v>
+      </c>
+      <c r="D77" t="s">
+        <v>99</v>
+      </c>
+      <c r="E77">
+        <v>4</v>
+      </c>
+      <c r="F77">
+        <v>4</v>
+      </c>
+      <c r="G77">
+        <v>46</v>
+      </c>
+      <c r="H77">
+        <f t="shared" si="0"/>
+        <v>54</v>
+      </c>
+      <c r="I77">
+        <v>3.88</v>
+      </c>
+      <c r="J77">
+        <v>1.95</v>
+      </c>
+      <c r="K77">
+        <v>22</v>
+      </c>
+      <c r="L77">
+        <v>24</v>
+      </c>
+      <c r="M77">
+        <v>9</v>
+      </c>
+      <c r="N77">
+        <v>10</v>
+      </c>
+      <c r="O77">
+        <v>6</v>
+      </c>
+      <c r="P77">
+        <v>3</v>
+      </c>
+      <c r="Q77">
+        <v>3</v>
+      </c>
+      <c r="R77">
+        <v>2</v>
+      </c>
+      <c r="S77">
+        <v>228</v>
+      </c>
+      <c r="T77">
+        <v>279</v>
+      </c>
+      <c r="U77">
+        <v>7</v>
+      </c>
+      <c r="V77">
+        <v>13</v>
+      </c>
+      <c r="W77">
+        <v>8</v>
+      </c>
+      <c r="X77">
+        <v>9</v>
+      </c>
+      <c r="Y77" t="s">
+        <v>90</v>
+      </c>
+      <c r="Z77" t="s">
+        <v>90</v>
+      </c>
+      <c r="AA77">
+        <v>6</v>
+      </c>
+      <c r="AB77">
+        <v>6</v>
+      </c>
+      <c r="AC77">
+        <v>7</v>
+      </c>
+      <c r="AD77">
+        <v>8</v>
+      </c>
+      <c r="AE77">
+        <v>0</v>
+      </c>
+      <c r="AF77">
+        <v>0</v>
+      </c>
+      <c r="AG77">
+        <v>19</v>
+      </c>
+      <c r="AH77">
+        <v>15</v>
+      </c>
+      <c r="AI77">
+        <v>3</v>
+      </c>
+      <c r="AJ77">
+        <v>9</v>
+      </c>
+      <c r="AK77">
+        <v>2.0499999999999998</v>
+      </c>
+      <c r="AL77">
+        <v>1.66</v>
+      </c>
+      <c r="AM77">
+        <v>1.04</v>
+      </c>
+      <c r="AN77">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="AO77">
+        <v>3.09</v>
+      </c>
+      <c r="AP77">
+        <v>1.95</v>
+      </c>
+      <c r="AQ77">
+        <v>3.85</v>
+      </c>
+      <c r="AR77">
+        <v>2.15</v>
+      </c>
+      <c r="AS77">
+        <v>322</v>
+      </c>
+      <c r="AT77">
+        <v>371</v>
+      </c>
+      <c r="AU77">
+        <v>131</v>
+      </c>
+      <c r="AV77">
+        <v>90</v>
+      </c>
+      <c r="AW77">
+        <v>97</v>
+      </c>
+      <c r="AX77">
+        <v>189</v>
+      </c>
+      <c r="AY77">
+        <v>24</v>
+      </c>
+      <c r="AZ77">
+        <v>20</v>
+      </c>
+      <c r="BA77">
+        <v>10</v>
+      </c>
+      <c r="BB77">
+        <v>2</v>
+      </c>
+      <c r="BC77">
+        <v>21</v>
+      </c>
+      <c r="BD77">
+        <v>19</v>
+      </c>
+      <c r="BE77">
+        <v>40</v>
+      </c>
+      <c r="BF77">
+        <v>47</v>
+      </c>
+      <c r="BG77">
+        <v>2</v>
+      </c>
+      <c r="BH77">
+        <v>2</v>
+      </c>
+      <c r="BI77" t="s">
+        <v>90</v>
+      </c>
+      <c r="BJ77" t="s">
+        <v>90</v>
+      </c>
+      <c r="BK77">
+        <v>22</v>
+      </c>
+      <c r="BL77">
+        <v>20</v>
+      </c>
+      <c r="BM77">
+        <v>18</v>
+      </c>
+      <c r="BN77">
+        <v>21</v>
+      </c>
+      <c r="BO77">
+        <v>7</v>
+      </c>
+      <c r="BP77">
+        <v>9</v>
+      </c>
+      <c r="BQ77">
+        <v>44</v>
+      </c>
+      <c r="BR77">
+        <v>15</v>
+      </c>
+      <c r="BS77">
+        <v>6</v>
+      </c>
+      <c r="BT77">
+        <v>3</v>
+      </c>
+      <c r="BU77" t="s">
+        <v>90</v>
+      </c>
+      <c r="BV77" t="s">
+        <v>90</v>
+      </c>
+      <c r="BW77">
+        <v>66</v>
+      </c>
+      <c r="BX77">
+        <v>44</v>
+      </c>
+      <c r="BY77">
+        <v>41</v>
+      </c>
+      <c r="BZ77">
+        <v>30</v>
+      </c>
+      <c r="CA77">
+        <v>25</v>
+      </c>
+      <c r="CB77">
+        <v>14</v>
+      </c>
+      <c r="CC77">
+        <v>8</v>
+      </c>
+      <c r="CD77">
+        <v>4</v>
+      </c>
+      <c r="CE77" t="s">
+        <v>90</v>
+      </c>
+      <c r="CF77" t="s">
+        <v>90</v>
+      </c>
+      <c r="CG77">
+        <v>1</v>
+      </c>
+      <c r="CH77">
+        <v>4</v>
+      </c>
+      <c r="CI77">
+        <v>0</v>
+      </c>
+      <c r="CJ77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" spans="2:88">
+      <c r="B78" s="8" t="s">
+        <v>170</v>
+      </c>
+      <c r="C78" t="s">
+        <v>94</v>
+      </c>
+      <c r="D78" t="s">
+        <v>101</v>
+      </c>
+      <c r="E78">
+        <v>2</v>
+      </c>
+      <c r="F78">
+        <v>1</v>
+      </c>
+      <c r="G78">
+        <v>45</v>
+      </c>
+      <c r="H78">
+        <f t="shared" si="0"/>
+        <v>55</v>
+      </c>
+      <c r="I78">
+        <v>0.34</v>
+      </c>
+      <c r="J78">
+        <v>1.98</v>
+      </c>
+      <c r="K78">
+        <v>7</v>
+      </c>
+      <c r="L78">
+        <v>19</v>
+      </c>
+      <c r="M78">
+        <v>4</v>
+      </c>
+      <c r="N78">
+        <v>5</v>
+      </c>
+      <c r="O78">
+        <v>1</v>
+      </c>
+      <c r="P78">
+        <v>2</v>
+      </c>
+      <c r="Q78">
+        <v>1</v>
+      </c>
+      <c r="R78">
+        <v>2</v>
+      </c>
+      <c r="S78">
+        <v>390</v>
+      </c>
+      <c r="T78">
+        <v>476</v>
+      </c>
+      <c r="U78">
+        <v>12</v>
+      </c>
+      <c r="V78">
+        <v>11</v>
+      </c>
+      <c r="W78">
+        <v>2</v>
+      </c>
+      <c r="X78">
+        <v>10</v>
+      </c>
+      <c r="Y78" t="s">
+        <v>90</v>
+      </c>
+      <c r="Z78" t="s">
+        <v>90</v>
+      </c>
+      <c r="AA78">
+        <v>2</v>
+      </c>
+      <c r="AB78">
+        <v>7</v>
+      </c>
+      <c r="AC78">
+        <v>1</v>
+      </c>
+      <c r="AD78">
+        <v>7</v>
+      </c>
+      <c r="AE78">
+        <v>0</v>
+      </c>
+      <c r="AF78">
+        <v>0</v>
+      </c>
+      <c r="AG78">
+        <v>3</v>
+      </c>
+      <c r="AH78">
+        <v>11</v>
+      </c>
+      <c r="AI78">
+        <v>4</v>
+      </c>
+      <c r="AJ78">
+        <v>8</v>
+      </c>
+      <c r="AK78">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="AL78">
+        <v>1.33</v>
+      </c>
+      <c r="AM78">
+        <v>0.06</v>
+      </c>
+      <c r="AN78">
+        <v>0.65</v>
+      </c>
+      <c r="AO78">
+        <v>0.34</v>
+      </c>
+      <c r="AP78">
+        <v>1.98</v>
+      </c>
+      <c r="AQ78">
+        <v>0.4</v>
+      </c>
+      <c r="AR78">
+        <v>0.84</v>
+      </c>
+      <c r="AS78">
+        <v>464</v>
+      </c>
+      <c r="AT78">
+        <v>548</v>
+      </c>
+      <c r="AU78">
+        <v>218</v>
+      </c>
+      <c r="AV78">
+        <v>213</v>
+      </c>
+      <c r="AW78">
+        <v>172</v>
+      </c>
+      <c r="AX78">
+        <v>263</v>
+      </c>
+      <c r="AY78">
+        <v>16</v>
+      </c>
+      <c r="AZ78">
+        <v>24</v>
+      </c>
+      <c r="BA78">
+        <v>1</v>
+      </c>
+      <c r="BB78">
+        <v>10</v>
+      </c>
+      <c r="BC78">
+        <v>15</v>
+      </c>
+      <c r="BD78">
+        <v>16</v>
+      </c>
+      <c r="BE78">
+        <v>3</v>
+      </c>
+      <c r="BF78">
+        <v>33</v>
+      </c>
+      <c r="BG78">
+        <v>1</v>
+      </c>
+      <c r="BH78">
+        <v>0</v>
+      </c>
+      <c r="BI78" t="s">
+        <v>90</v>
+      </c>
+      <c r="BJ78" t="s">
+        <v>90</v>
+      </c>
+      <c r="BK78">
+        <v>11</v>
+      </c>
+      <c r="BL78">
+        <v>11</v>
+      </c>
+      <c r="BM78">
+        <v>12</v>
+      </c>
+      <c r="BN78">
+        <v>9</v>
+      </c>
+      <c r="BO78">
+        <v>7</v>
+      </c>
+      <c r="BP78">
+        <v>1</v>
+      </c>
+      <c r="BQ78">
+        <v>36</v>
+      </c>
+      <c r="BR78">
+        <v>15</v>
+      </c>
+      <c r="BS78">
+        <v>5</v>
+      </c>
+      <c r="BT78">
+        <v>3</v>
+      </c>
+      <c r="BU78" t="s">
+        <v>90</v>
+      </c>
+      <c r="BV78" t="s">
+        <v>90</v>
+      </c>
+      <c r="BW78">
+        <v>35</v>
+      </c>
+      <c r="BX78">
+        <v>45</v>
+      </c>
+      <c r="BY78">
+        <v>23</v>
+      </c>
+      <c r="BZ78">
+        <v>28</v>
+      </c>
+      <c r="CA78">
+        <v>12</v>
+      </c>
+      <c r="CB78">
+        <v>17</v>
+      </c>
+      <c r="CC78">
+        <v>3</v>
+      </c>
+      <c r="CD78">
+        <v>5</v>
+      </c>
+      <c r="CE78" t="s">
+        <v>90</v>
+      </c>
+      <c r="CF78" t="s">
+        <v>90</v>
+      </c>
+      <c r="CG78">
+        <v>1</v>
+      </c>
+      <c r="CH78">
+        <v>0</v>
+      </c>
+      <c r="CI78">
+        <v>0</v>
+      </c>
+      <c r="CJ78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:88">
+      <c r="B79" s="8" t="s">
+        <v>171</v>
+      </c>
+      <c r="C79" t="s">
+        <v>102</v>
+      </c>
+      <c r="D79" t="s">
+        <v>100</v>
+      </c>
+      <c r="E79">
+        <v>0</v>
+      </c>
+      <c r="F79">
+        <v>2</v>
+      </c>
+      <c r="G79">
+        <v>42</v>
+      </c>
+      <c r="H79">
+        <f t="shared" si="0"/>
+        <v>58</v>
+      </c>
+      <c r="I79">
+        <v>0.86</v>
+      </c>
+      <c r="J79">
+        <v>1.06</v>
+      </c>
+      <c r="K79">
+        <v>16</v>
+      </c>
+      <c r="L79">
+        <v>8</v>
+      </c>
+      <c r="M79">
+        <v>4</v>
+      </c>
+      <c r="N79">
+        <v>2</v>
+      </c>
+      <c r="O79">
+        <v>0</v>
+      </c>
+      <c r="P79">
+        <v>1</v>
+      </c>
+      <c r="Q79">
+        <v>0</v>
+      </c>
+      <c r="R79">
+        <v>0</v>
+      </c>
+      <c r="S79">
+        <v>253</v>
+      </c>
+      <c r="T79">
+        <v>387</v>
+      </c>
+      <c r="U79">
+        <v>10</v>
+      </c>
+      <c r="V79">
+        <v>12</v>
+      </c>
+      <c r="W79">
+        <v>5</v>
+      </c>
+      <c r="X79">
+        <v>3</v>
+      </c>
+      <c r="Y79" t="s">
+        <v>90</v>
+      </c>
+      <c r="Z79" t="s">
+        <v>90</v>
+      </c>
+      <c r="AA79">
+        <v>8</v>
+      </c>
+      <c r="AB79">
+        <v>6</v>
+      </c>
+      <c r="AC79">
+        <v>4</v>
+      </c>
+      <c r="AD79">
+        <v>0</v>
+      </c>
+      <c r="AE79">
+        <v>0</v>
+      </c>
+      <c r="AF79">
+        <v>0</v>
+      </c>
+      <c r="AG79">
+        <v>10</v>
+      </c>
+      <c r="AH79">
+        <v>7</v>
+      </c>
+      <c r="AI79">
+        <v>6</v>
+      </c>
+      <c r="AJ79">
+        <v>1</v>
+      </c>
+      <c r="AK79">
+        <v>0.76</v>
+      </c>
+      <c r="AL79">
+        <v>0.45</v>
+      </c>
+      <c r="AM79">
+        <v>0.1</v>
+      </c>
+      <c r="AN79">
+        <v>0.61</v>
+      </c>
+      <c r="AO79">
+        <v>0.86</v>
+      </c>
+      <c r="AP79">
+        <v>1.06</v>
+      </c>
+      <c r="AQ79">
+        <v>1.38</v>
+      </c>
+      <c r="AR79">
+        <v>0.92</v>
+      </c>
+      <c r="AS79">
+        <v>331</v>
+      </c>
+      <c r="AT79">
+        <v>474</v>
+      </c>
+      <c r="AU79">
+        <v>110</v>
+      </c>
+      <c r="AV79">
+        <v>234</v>
+      </c>
+      <c r="AW79">
+        <v>143</v>
+      </c>
+      <c r="AX79">
+        <v>153</v>
+      </c>
+      <c r="AY79">
+        <v>16</v>
+      </c>
+      <c r="AZ79">
+        <v>24</v>
+      </c>
+      <c r="BA79">
+        <v>5</v>
+      </c>
+      <c r="BB79">
+        <v>5</v>
+      </c>
+      <c r="BC79">
+        <v>28</v>
+      </c>
+      <c r="BD79">
+        <v>21</v>
+      </c>
+      <c r="BE79">
+        <v>25</v>
+      </c>
+      <c r="BF79">
+        <v>26</v>
+      </c>
+      <c r="BG79">
+        <v>2</v>
+      </c>
+      <c r="BH79">
+        <v>4</v>
+      </c>
+      <c r="BI79" t="s">
+        <v>90</v>
+      </c>
+      <c r="BJ79" t="s">
+        <v>90</v>
+      </c>
+      <c r="BK79">
+        <v>15</v>
+      </c>
+      <c r="BL79">
+        <v>20</v>
+      </c>
+      <c r="BM79">
+        <v>9</v>
+      </c>
+      <c r="BN79">
+        <v>12</v>
+      </c>
+      <c r="BO79">
+        <v>0</v>
+      </c>
+      <c r="BP79">
+        <v>4</v>
+      </c>
+      <c r="BQ79">
+        <v>29</v>
+      </c>
+      <c r="BR79">
+        <v>27</v>
+      </c>
+      <c r="BS79">
+        <v>0</v>
+      </c>
+      <c r="BT79">
+        <v>4</v>
+      </c>
+      <c r="BU79" t="s">
+        <v>90</v>
+      </c>
+      <c r="BV79" t="s">
+        <v>90</v>
+      </c>
+      <c r="BW79">
+        <v>49</v>
+      </c>
+      <c r="BX79">
+        <v>49</v>
+      </c>
+      <c r="BY79">
+        <v>32</v>
+      </c>
+      <c r="BZ79">
+        <v>34</v>
+      </c>
+      <c r="CA79">
+        <v>17</v>
+      </c>
+      <c r="CB79">
+        <v>15</v>
+      </c>
+      <c r="CC79">
+        <v>8</v>
+      </c>
+      <c r="CD79">
+        <v>4</v>
+      </c>
+      <c r="CE79" t="s">
+        <v>90</v>
+      </c>
+      <c r="CF79" t="s">
+        <v>90</v>
+      </c>
+      <c r="CG79">
+        <v>1</v>
+      </c>
+      <c r="CH79">
+        <v>0</v>
+      </c>
+      <c r="CI79">
+        <v>1</v>
+      </c>
+      <c r="CJ79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" spans="2:88">
+      <c r="B80" s="8" t="s">
+        <v>172</v>
+      </c>
+      <c r="C80" t="s">
+        <v>91</v>
+      </c>
+      <c r="D80" t="s">
+        <v>107</v>
+      </c>
+      <c r="E80">
+        <v>0</v>
+      </c>
+      <c r="F80">
+        <v>2</v>
+      </c>
+      <c r="G80">
+        <v>40</v>
+      </c>
+      <c r="H80">
+        <f t="shared" si="0"/>
+        <v>60</v>
+      </c>
+      <c r="I80">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="J80">
+        <v>3.59</v>
+      </c>
+      <c r="K80">
+        <v>12</v>
+      </c>
+      <c r="L80">
+        <v>19</v>
+      </c>
+      <c r="M80">
+        <v>5</v>
+      </c>
+      <c r="N80">
+        <v>7</v>
+      </c>
+      <c r="O80">
+        <v>1</v>
+      </c>
+      <c r="P80">
+        <v>6</v>
+      </c>
+      <c r="Q80">
+        <v>1</v>
+      </c>
+      <c r="R80">
+        <v>4</v>
+      </c>
+      <c r="S80">
+        <v>338</v>
+      </c>
+      <c r="T80">
+        <v>534</v>
+      </c>
+      <c r="U80">
+        <v>11</v>
+      </c>
+      <c r="V80">
+        <v>13</v>
+      </c>
+      <c r="W80">
+        <v>5</v>
+      </c>
+      <c r="X80">
+        <v>4</v>
+      </c>
+      <c r="Y80" t="s">
+        <v>90</v>
+      </c>
+      <c r="Z80" t="s">
+        <v>90</v>
+      </c>
+      <c r="AA80">
+        <v>5</v>
+      </c>
+      <c r="AB80">
+        <v>7</v>
+      </c>
+      <c r="AC80">
+        <v>2</v>
+      </c>
+      <c r="AD80">
+        <v>5</v>
+      </c>
+      <c r="AE80">
+        <v>0</v>
+      </c>
+      <c r="AF80">
+        <v>2</v>
+      </c>
+      <c r="AG80">
+        <v>3</v>
+      </c>
+      <c r="AH80">
+        <v>15</v>
+      </c>
+      <c r="AI80">
+        <v>9</v>
+      </c>
+      <c r="AJ80">
+        <v>4</v>
+      </c>
+      <c r="AK80">
+        <v>0.35</v>
+      </c>
+      <c r="AL80">
+        <v>2.92</v>
+      </c>
+      <c r="AM80">
+        <v>0.2</v>
+      </c>
+      <c r="AN80">
+        <v>0.67</v>
+      </c>
+      <c r="AO80">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="AP80">
+        <v>3.59</v>
+      </c>
+      <c r="AQ80">
+        <v>0.31</v>
+      </c>
+      <c r="AR80">
+        <v>2.2200000000000002</v>
+      </c>
+      <c r="AS80">
+        <v>412</v>
+      </c>
+      <c r="AT80">
+        <v>617</v>
+      </c>
+      <c r="AU80">
+        <v>135</v>
+      </c>
+      <c r="AV80">
+        <v>339</v>
+      </c>
+      <c r="AW80">
+        <v>203</v>
+      </c>
+      <c r="AX80">
+        <v>195</v>
+      </c>
+      <c r="AY80">
+        <v>13</v>
+      </c>
+      <c r="AZ80">
+        <v>25</v>
+      </c>
+      <c r="BA80">
+        <v>1</v>
+      </c>
+      <c r="BB80">
+        <v>3</v>
+      </c>
+      <c r="BC80">
+        <v>16</v>
+      </c>
+      <c r="BD80">
+        <v>15</v>
+      </c>
+      <c r="BE80">
+        <v>15</v>
+      </c>
+      <c r="BF80">
+        <v>31</v>
+      </c>
+      <c r="BG80">
+        <v>0</v>
+      </c>
+      <c r="BH80">
+        <v>1</v>
+      </c>
+      <c r="BI80" t="s">
+        <v>90</v>
+      </c>
+      <c r="BJ80" t="s">
+        <v>90</v>
+      </c>
+      <c r="BK80">
+        <v>24</v>
+      </c>
+      <c r="BL80">
+        <v>16</v>
+      </c>
+      <c r="BM80">
+        <v>6</v>
+      </c>
+      <c r="BN80">
+        <v>10</v>
+      </c>
+      <c r="BO80">
+        <v>5</v>
+      </c>
+      <c r="BP80">
+        <v>2</v>
+      </c>
+      <c r="BQ80">
+        <v>31</v>
+      </c>
+      <c r="BR80">
+        <v>30</v>
+      </c>
+      <c r="BS80">
+        <v>5</v>
+      </c>
+      <c r="BT80">
+        <v>5</v>
+      </c>
+      <c r="BU80" t="s">
+        <v>90</v>
+      </c>
+      <c r="BV80" t="s">
+        <v>90</v>
+      </c>
+      <c r="BW80">
+        <v>55</v>
+      </c>
+      <c r="BX80">
+        <v>49</v>
+      </c>
+      <c r="BY80">
+        <v>45</v>
+      </c>
+      <c r="BZ80">
+        <v>30</v>
+      </c>
+      <c r="CA80">
+        <v>10</v>
+      </c>
+      <c r="CB80">
+        <v>19</v>
+      </c>
+      <c r="CC80">
+        <v>9</v>
+      </c>
+      <c r="CD80">
+        <v>7</v>
+      </c>
+      <c r="CE80" t="s">
+        <v>90</v>
+      </c>
+      <c r="CF80" t="s">
+        <v>90</v>
+      </c>
+      <c r="CG80">
+        <v>1</v>
+      </c>
+      <c r="CH80">
+        <v>2</v>
+      </c>
+      <c r="CI80">
+        <v>0</v>
+      </c>
+      <c r="CJ80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81" spans="2:88">
+      <c r="B81" s="8" t="s">
+        <v>174</v>
+      </c>
+      <c r="C81" t="s">
+        <v>105</v>
+      </c>
+      <c r="D81" t="s">
+        <v>110</v>
+      </c>
+      <c r="E81">
+        <v>2</v>
+      </c>
+      <c r="F81">
+        <v>6</v>
+      </c>
+      <c r="G81">
+        <v>42</v>
+      </c>
+      <c r="H81">
+        <f t="shared" si="0"/>
+        <v>58</v>
+      </c>
+      <c r="I81">
+        <v>0.76</v>
+      </c>
+      <c r="J81">
+        <v>3.57</v>
+      </c>
+      <c r="K81">
+        <v>9</v>
+      </c>
+      <c r="L81">
+        <v>16</v>
+      </c>
+      <c r="M81">
+        <v>1</v>
+      </c>
+      <c r="N81">
+        <v>8</v>
+      </c>
+      <c r="O81">
+        <v>2</v>
+      </c>
+      <c r="P81">
+        <v>7</v>
+      </c>
+      <c r="Q81">
+        <v>1</v>
+      </c>
+      <c r="R81">
+        <v>4</v>
+      </c>
+      <c r="S81">
+        <v>395</v>
+      </c>
+      <c r="T81">
+        <v>570</v>
+      </c>
+      <c r="U81">
+        <v>7</v>
+      </c>
+      <c r="V81">
+        <v>13</v>
+      </c>
+      <c r="W81">
+        <v>2</v>
+      </c>
+      <c r="X81">
+        <v>1</v>
+      </c>
+      <c r="Y81" t="s">
+        <v>90</v>
+      </c>
+      <c r="Z81" t="s">
+        <v>90</v>
+      </c>
+      <c r="AA81">
+        <v>6</v>
+      </c>
+      <c r="AB81">
+        <v>4</v>
+      </c>
+      <c r="AC81">
+        <v>2</v>
+      </c>
+      <c r="AD81">
+        <v>4</v>
+      </c>
+      <c r="AE81">
+        <v>0</v>
+      </c>
+      <c r="AF81">
+        <v>0</v>
+      </c>
+      <c r="AG81">
+        <v>2</v>
+      </c>
+      <c r="AH81">
+        <v>11</v>
+      </c>
+      <c r="AI81">
+        <v>7</v>
+      </c>
+      <c r="AJ81">
+        <v>5</v>
+      </c>
+      <c r="AK81">
+        <v>0.69</v>
+      </c>
+      <c r="AL81">
+        <v>1.99</v>
+      </c>
+      <c r="AM81">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="AN81">
+        <v>0</v>
+      </c>
+      <c r="AO81">
+        <v>0.76</v>
+      </c>
+      <c r="AP81">
+        <v>1.99</v>
+      </c>
+      <c r="AQ81">
+        <v>0.25</v>
+      </c>
+      <c r="AR81">
+        <v>4.62</v>
+      </c>
+      <c r="AS81">
+        <v>449</v>
+      </c>
+      <c r="AT81">
+        <v>622</v>
+      </c>
+      <c r="AU81">
+        <v>255</v>
+      </c>
+      <c r="AV81">
+        <v>264</v>
+      </c>
+      <c r="AW81">
+        <v>140</v>
+      </c>
+      <c r="AX81">
+        <v>306</v>
+      </c>
+      <c r="AY81">
+        <v>18</v>
+      </c>
+      <c r="AZ81">
+        <v>16</v>
+      </c>
+      <c r="BA81">
+        <v>0</v>
+      </c>
+      <c r="BB81">
+        <v>2</v>
+      </c>
+      <c r="BC81">
+        <v>10</v>
+      </c>
+      <c r="BD81">
+        <v>15</v>
+      </c>
+      <c r="BE81">
+        <v>11</v>
+      </c>
+      <c r="BF81">
+        <v>27</v>
+      </c>
+      <c r="BG81">
+        <v>3</v>
+      </c>
+      <c r="BH81">
+        <v>1</v>
+      </c>
+      <c r="BI81" t="s">
+        <v>90</v>
+      </c>
+      <c r="BJ81" t="s">
+        <v>90</v>
+      </c>
+      <c r="BK81">
+        <v>14</v>
+      </c>
+      <c r="BL81">
+        <v>13</v>
+      </c>
+      <c r="BM81">
+        <v>9</v>
+      </c>
+      <c r="BN81">
+        <v>4</v>
+      </c>
+      <c r="BO81">
+        <v>3</v>
+      </c>
+      <c r="BP81">
+        <v>2</v>
+      </c>
+      <c r="BQ81">
+        <v>16</v>
+      </c>
+      <c r="BR81">
+        <v>12</v>
+      </c>
+      <c r="BS81">
+        <v>2</v>
+      </c>
+      <c r="BT81">
+        <v>0</v>
+      </c>
+      <c r="BU81" t="s">
+        <v>90</v>
+      </c>
+      <c r="BV81" t="s">
+        <v>90</v>
+      </c>
+      <c r="BW81">
+        <v>41</v>
+      </c>
+      <c r="BX81">
+        <v>34</v>
+      </c>
+      <c r="BY81">
+        <v>35</v>
+      </c>
+      <c r="BZ81">
+        <v>28</v>
+      </c>
+      <c r="CA81">
+        <v>6</v>
+      </c>
+      <c r="CB81">
+        <v>6</v>
+      </c>
+      <c r="CC81">
+        <v>9</v>
+      </c>
+      <c r="CD81">
+        <v>9</v>
+      </c>
+      <c r="CE81" t="s">
+        <v>90</v>
+      </c>
+      <c r="CF81" t="s">
+        <v>90</v>
+      </c>
+      <c r="CG81">
+        <v>1</v>
+      </c>
+      <c r="CH81">
+        <v>1</v>
+      </c>
+      <c r="CI81">
+        <v>1</v>
+      </c>
+      <c r="CJ81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="2:88">
+      <c r="B82" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="C82" t="s">
+        <v>106</v>
+      </c>
+      <c r="D82" t="s">
+        <v>92</v>
+      </c>
+      <c r="E82">
+        <v>1</v>
+      </c>
+      <c r="F82">
+        <v>3</v>
+      </c>
+      <c r="G82">
+        <v>28</v>
+      </c>
+      <c r="H82">
+        <f t="shared" si="0"/>
+        <v>72</v>
+      </c>
+      <c r="I82">
+        <v>1.1299999999999999</v>
+      </c>
+      <c r="J82">
+        <v>2.2599999999999998</v>
+      </c>
+      <c r="K82">
+        <v>11</v>
+      </c>
+      <c r="L82">
+        <v>18</v>
+      </c>
+      <c r="M82">
+        <v>5</v>
+      </c>
+      <c r="N82">
+        <v>5</v>
+      </c>
+      <c r="O82">
+        <v>2</v>
+      </c>
+      <c r="P82">
+        <v>5</v>
+      </c>
+      <c r="Q82">
+        <v>1</v>
+      </c>
+      <c r="R82">
+        <v>2</v>
+      </c>
+      <c r="S82">
+        <v>204</v>
+      </c>
+      <c r="T82">
+        <v>639</v>
+      </c>
+      <c r="U82">
+        <v>10</v>
+      </c>
+      <c r="V82">
+        <v>3</v>
+      </c>
+      <c r="W82">
+        <v>5</v>
+      </c>
+      <c r="X82">
+        <v>6</v>
+      </c>
+      <c r="Y82" t="s">
+        <v>90</v>
+      </c>
+      <c r="Z82" t="s">
+        <v>90</v>
+      </c>
+      <c r="AA82">
+        <v>4</v>
+      </c>
+      <c r="AB82">
+        <v>8</v>
+      </c>
+      <c r="AC82">
+        <v>2</v>
+      </c>
+      <c r="AD82">
+        <v>5</v>
+      </c>
+      <c r="AE82">
+        <v>1</v>
+      </c>
+      <c r="AF82">
+        <v>2</v>
+      </c>
+      <c r="AG82">
+        <v>8</v>
+      </c>
+      <c r="AH82">
+        <v>13</v>
+      </c>
+      <c r="AI82">
+        <v>3</v>
+      </c>
+      <c r="AJ82">
+        <v>5</v>
+      </c>
+      <c r="AK82">
+        <v>0.74</v>
+      </c>
+      <c r="AL82">
+        <v>1.96</v>
+      </c>
+      <c r="AM82">
+        <v>0.4</v>
+      </c>
+      <c r="AN82">
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="AO82">
+        <v>1.1299999999999999</v>
+      </c>
+      <c r="AP82">
+        <v>2.2599999999999998</v>
+      </c>
+      <c r="AQ82">
+        <v>1</v>
+      </c>
+      <c r="AR82">
+        <v>1.71</v>
+      </c>
+      <c r="AS82">
+        <v>265</v>
+      </c>
+      <c r="AT82">
+        <v>700</v>
+      </c>
+      <c r="AU82">
+        <v>139</v>
+      </c>
+      <c r="AV82">
+        <v>217</v>
+      </c>
+      <c r="AW82">
+        <v>65</v>
+      </c>
+      <c r="AX82">
+        <v>422</v>
+      </c>
+      <c r="AY82">
+        <v>12</v>
+      </c>
+      <c r="AZ82">
+        <v>21</v>
+      </c>
+      <c r="BA82">
+        <v>1</v>
+      </c>
+      <c r="BB82">
+        <v>8</v>
+      </c>
+      <c r="BC82">
+        <v>12</v>
+      </c>
+      <c r="BD82">
+        <v>15</v>
+      </c>
+      <c r="BE82">
+        <v>20</v>
+      </c>
+      <c r="BF82">
+        <v>42</v>
+      </c>
+      <c r="BG82">
+        <v>3</v>
+      </c>
+      <c r="BH82">
+        <v>3</v>
+      </c>
+      <c r="BI82" t="s">
+        <v>90</v>
+      </c>
+      <c r="BJ82" t="s">
+        <v>90</v>
+      </c>
+      <c r="BK82">
+        <v>22</v>
+      </c>
+      <c r="BL82">
+        <v>14</v>
+      </c>
+      <c r="BM82">
+        <v>10</v>
+      </c>
+      <c r="BN82">
+        <v>3</v>
+      </c>
+      <c r="BO82">
+        <v>5</v>
+      </c>
+      <c r="BP82">
+        <v>2</v>
+      </c>
+      <c r="BQ82">
+        <v>46</v>
+      </c>
+      <c r="BR82">
+        <v>21</v>
+      </c>
+      <c r="BS82">
+        <v>3</v>
+      </c>
+      <c r="BT82">
+        <v>4</v>
+      </c>
+      <c r="BU82" t="s">
+        <v>90</v>
+      </c>
+      <c r="BV82" t="s">
+        <v>90</v>
+      </c>
+      <c r="BW82">
+        <v>43</v>
+      </c>
+      <c r="BX82">
+        <v>46</v>
+      </c>
+      <c r="BY82">
+        <v>33</v>
+      </c>
+      <c r="BZ82">
+        <v>26</v>
+      </c>
+      <c r="CA82">
+        <v>10</v>
+      </c>
+      <c r="CB82">
+        <v>20</v>
+      </c>
+      <c r="CC82">
+        <v>8</v>
+      </c>
+      <c r="CD82">
+        <v>2</v>
+      </c>
+      <c r="CE82" t="s">
+        <v>90</v>
+      </c>
+      <c r="CF82" t="s">
+        <v>90</v>
+      </c>
+      <c r="CG82">
+        <v>1</v>
+      </c>
+      <c r="CH82">
+        <v>0</v>
+      </c>
+      <c r="CI82">
+        <v>0</v>
+      </c>
+      <c r="CJ82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83" spans="2:88">
+      <c r="B83" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="C83" t="s">
+        <v>112</v>
+      </c>
+      <c r="D83" t="s">
+        <v>97</v>
+      </c>
+      <c r="E83">
+        <v>4</v>
+      </c>
+      <c r="F83">
+        <v>2</v>
+      </c>
+      <c r="G83">
+        <v>61</v>
+      </c>
+      <c r="H83">
+        <f t="shared" si="0"/>
+        <v>39</v>
+      </c>
+      <c r="I83">
+        <v>2.87</v>
+      </c>
+      <c r="J83">
+        <v>2.61</v>
+      </c>
+      <c r="K83">
+        <v>20</v>
+      </c>
+      <c r="L83">
+        <v>19</v>
+      </c>
+      <c r="M83">
+        <v>8</v>
+      </c>
+      <c r="N83">
+        <v>8</v>
+      </c>
+      <c r="O83">
+        <v>8</v>
+      </c>
+      <c r="P83">
+        <v>4</v>
+      </c>
+      <c r="Q83">
+        <v>4</v>
+      </c>
+      <c r="R83">
+        <v>2</v>
+      </c>
+      <c r="S83">
+        <v>507</v>
+      </c>
+      <c r="T83">
+        <v>296</v>
+      </c>
+      <c r="U83">
+        <v>8</v>
+      </c>
+      <c r="V83">
+        <v>8</v>
+      </c>
+      <c r="W83">
+        <v>7</v>
+      </c>
+      <c r="X83">
+        <v>8</v>
+      </c>
+      <c r="Y83" t="s">
+        <v>90</v>
+      </c>
+      <c r="Z83" t="s">
+        <v>90</v>
+      </c>
+      <c r="AA83">
+        <v>5</v>
+      </c>
+      <c r="AB83">
+        <v>7</v>
+      </c>
+      <c r="AC83">
+        <v>7</v>
+      </c>
+      <c r="AD83">
+        <v>4</v>
+      </c>
+      <c r="AE83">
+        <v>0</v>
+      </c>
+      <c r="AF83">
+        <v>0</v>
+      </c>
+      <c r="AG83">
+        <v>13</v>
+      </c>
+      <c r="AH83">
+        <v>12</v>
+      </c>
+      <c r="AI83">
+        <v>7</v>
+      </c>
+      <c r="AJ83">
+        <v>7</v>
+      </c>
+      <c r="AK83">
+        <v>2.5299999999999998</v>
+      </c>
+      <c r="AL83">
+        <v>1.64</v>
+      </c>
+      <c r="AM83">
+        <v>0.35</v>
+      </c>
+      <c r="AN83">
+        <v>0.18</v>
+      </c>
+      <c r="AO83">
+        <v>2.87</v>
+      </c>
+      <c r="AP83">
+        <v>1.83</v>
+      </c>
+      <c r="AQ83">
+        <v>2.74</v>
+      </c>
+      <c r="AR83">
+        <v>3.73</v>
+      </c>
+      <c r="AS83">
+        <v>584</v>
+      </c>
+      <c r="AT83">
+        <v>372</v>
+      </c>
+      <c r="AU83">
+        <v>253</v>
+      </c>
+      <c r="AV83">
+        <v>195</v>
+      </c>
+      <c r="AW83">
+        <v>254</v>
+      </c>
+      <c r="AX83">
+        <v>101</v>
+      </c>
+      <c r="AY83">
+        <v>22</v>
+      </c>
+      <c r="AZ83">
+        <v>24</v>
+      </c>
+      <c r="BA83">
+        <v>5</v>
+      </c>
+      <c r="BB83">
+        <v>5</v>
+      </c>
+      <c r="BC83">
+        <v>19</v>
+      </c>
+      <c r="BD83">
+        <v>21</v>
+      </c>
+      <c r="BE83">
+        <v>32</v>
+      </c>
+      <c r="BF83">
+        <v>23</v>
+      </c>
+      <c r="BG83">
+        <v>2</v>
+      </c>
+      <c r="BH83">
+        <v>3</v>
+      </c>
+      <c r="BI83" t="s">
+        <v>90</v>
+      </c>
+      <c r="BJ83" t="s">
+        <v>90</v>
+      </c>
+      <c r="BK83">
+        <v>15</v>
+      </c>
+      <c r="BL83">
+        <v>14</v>
+      </c>
+      <c r="BM83">
+        <v>4</v>
+      </c>
+      <c r="BN83">
+        <v>7</v>
+      </c>
+      <c r="BO83">
+        <v>3</v>
+      </c>
+      <c r="BP83">
+        <v>7</v>
+      </c>
+      <c r="BQ83">
+        <v>21</v>
+      </c>
+      <c r="BR83">
+        <v>31</v>
+      </c>
+      <c r="BS83">
+        <v>6</v>
+      </c>
+      <c r="BT83">
+        <v>4</v>
+      </c>
+      <c r="BU83" t="s">
+        <v>90</v>
+      </c>
+      <c r="BV83" t="s">
+        <v>90</v>
+      </c>
+      <c r="BW83">
+        <v>41</v>
+      </c>
+      <c r="BX83">
+        <v>41</v>
+      </c>
+      <c r="BY83">
+        <v>29</v>
+      </c>
+      <c r="BZ83">
+        <v>26</v>
+      </c>
+      <c r="CA83">
+        <v>12</v>
+      </c>
+      <c r="CB83">
+        <v>15</v>
+      </c>
+      <c r="CC83">
+        <v>8</v>
+      </c>
+      <c r="CD83">
+        <v>5</v>
+      </c>
+      <c r="CE83" t="s">
+        <v>90</v>
+      </c>
+      <c r="CF83" t="s">
+        <v>90</v>
+      </c>
+      <c r="CG83">
+        <v>0</v>
+      </c>
+      <c r="CH83">
+        <v>1</v>
+      </c>
+      <c r="CI83">
+        <v>0</v>
+      </c>
+      <c r="CJ83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="2:88">
+      <c r="B84" s="9" t="s">
+        <v>175</v>
+      </c>
+      <c r="C84" t="s">
+        <v>107</v>
+      </c>
+      <c r="D84" t="s">
+        <v>109</v>
+      </c>
+      <c r="E84">
+        <v>2</v>
+      </c>
+      <c r="F84">
+        <v>4</v>
+      </c>
+      <c r="G84">
+        <v>66</v>
+      </c>
+      <c r="H84">
+        <f t="shared" si="0"/>
+        <v>34</v>
+      </c>
+      <c r="I84">
+        <v>1.8</v>
+      </c>
+      <c r="J84">
+        <v>2.09</v>
+      </c>
+      <c r="K84">
+        <v>8</v>
+      </c>
+      <c r="L84">
+        <v>9</v>
+      </c>
+      <c r="M84">
+        <v>3</v>
+      </c>
+      <c r="N84">
+        <v>5</v>
+      </c>
+      <c r="O84">
+        <v>4</v>
+      </c>
+      <c r="P84">
+        <v>4</v>
+      </c>
+      <c r="Q84">
+        <v>2</v>
+      </c>
+      <c r="R84">
+        <v>1</v>
+      </c>
+      <c r="S84">
+        <v>593</v>
+      </c>
+      <c r="T84">
+        <v>271</v>
+      </c>
+      <c r="U84">
+        <v>10</v>
+      </c>
+      <c r="V84">
+        <v>16</v>
+      </c>
+      <c r="W84">
+        <v>2</v>
+      </c>
+      <c r="X84">
+        <v>3</v>
+      </c>
+      <c r="Y84" t="s">
+        <v>90</v>
+      </c>
+      <c r="Z84" t="s">
+        <v>90</v>
+      </c>
+      <c r="AA84">
+        <v>4</v>
+      </c>
+      <c r="AB84">
+        <v>3</v>
+      </c>
+      <c r="AC84">
+        <v>1</v>
+      </c>
+      <c r="AD84">
+        <v>1</v>
+      </c>
+      <c r="AE84">
+        <v>0</v>
+      </c>
+      <c r="AF84">
+        <v>0</v>
+      </c>
+      <c r="AG84">
+        <v>6</v>
+      </c>
+      <c r="AH84">
+        <v>6</v>
+      </c>
+      <c r="AI84">
+        <v>2</v>
+      </c>
+      <c r="AJ84">
+        <v>3</v>
+      </c>
+      <c r="AK84">
+        <v>1.72</v>
+      </c>
+      <c r="AL84">
+        <v>2.0699999999999998</v>
+      </c>
+      <c r="AM84">
+        <v>0.08</v>
+      </c>
+      <c r="AN84">
+        <v>0.02</v>
+      </c>
+      <c r="AO84">
+        <v>1.8</v>
+      </c>
+      <c r="AP84">
+        <v>2.09</v>
+      </c>
+      <c r="AQ84">
+        <v>1.5</v>
+      </c>
+      <c r="AR84">
+        <v>2.4900000000000002</v>
+      </c>
+      <c r="AS84">
+        <v>668</v>
+      </c>
+      <c r="AT84">
+        <v>338</v>
+      </c>
+      <c r="AU84">
+        <v>406</v>
+      </c>
+      <c r="AV84">
+        <v>144</v>
+      </c>
+      <c r="AW84">
+        <v>187</v>
+      </c>
+      <c r="AX84">
+        <v>127</v>
+      </c>
+      <c r="AY84">
+        <v>18</v>
+      </c>
+      <c r="AZ84">
+        <v>15</v>
+      </c>
+      <c r="BA84">
+        <v>5</v>
+      </c>
+      <c r="BB84">
+        <v>2</v>
+      </c>
+      <c r="BC84">
+        <v>19</v>
+      </c>
+      <c r="BD84">
+        <v>9</v>
+      </c>
+      <c r="BE84">
+        <v>15</v>
+      </c>
+      <c r="BF84">
+        <v>18</v>
+      </c>
+      <c r="BG84">
+        <v>0</v>
+      </c>
+      <c r="BH84">
+        <v>1</v>
+      </c>
+      <c r="BI84" t="s">
+        <v>90</v>
+      </c>
+      <c r="BJ84" t="s">
+        <v>90</v>
+      </c>
+      <c r="BK84">
+        <v>16</v>
+      </c>
+      <c r="BL84">
+        <v>19</v>
+      </c>
+      <c r="BM84">
+        <v>7</v>
+      </c>
+      <c r="BN84">
+        <v>11</v>
+      </c>
+      <c r="BO84">
+        <v>1</v>
+      </c>
+      <c r="BP84">
+        <v>1</v>
+      </c>
+      <c r="BQ84">
+        <v>10</v>
+      </c>
+      <c r="BR84">
+        <v>18</v>
+      </c>
+      <c r="BS84">
+        <v>2</v>
+      </c>
+      <c r="BT84">
+        <v>1</v>
+      </c>
+      <c r="BU84" t="s">
+        <v>90</v>
+      </c>
+      <c r="BV84" t="s">
+        <v>90</v>
+      </c>
+      <c r="BW84">
+        <v>52</v>
+      </c>
+      <c r="BX84">
+        <v>49</v>
+      </c>
+      <c r="BY84">
+        <v>37</v>
+      </c>
+      <c r="BZ84">
+        <v>36</v>
+      </c>
+      <c r="CA84">
+        <v>15</v>
+      </c>
+      <c r="CB84">
+        <v>13</v>
+      </c>
+      <c r="CC84">
+        <v>8</v>
+      </c>
+      <c r="CD84">
+        <v>7</v>
+      </c>
+      <c r="CE84" t="s">
+        <v>90</v>
+      </c>
+      <c r="CF84" t="s">
+        <v>90</v>
+      </c>
+      <c r="CG84">
+        <v>0</v>
+      </c>
+      <c r="CH84">
+        <v>2</v>
+      </c>
+      <c r="CI84">
+        <v>0</v>
+      </c>
+      <c r="CJ84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="2:88">
+      <c r="B85" s="9" t="s">
+        <v>175</v>
+      </c>
+      <c r="C85" t="s">
+        <v>96</v>
+      </c>
+      <c r="D85" t="s">
+        <v>91</v>
+      </c>
+      <c r="E85">
+        <v>0</v>
+      </c>
+      <c r="F85">
+        <v>0</v>
+      </c>
+      <c r="G85">
+        <v>42</v>
+      </c>
+      <c r="H85">
+        <f t="shared" si="0"/>
+        <v>58</v>
+      </c>
+      <c r="I85">
+        <v>1.1200000000000001</v>
+      </c>
+      <c r="J85">
+        <v>1.37</v>
+      </c>
+      <c r="K85">
+        <v>8</v>
+      </c>
+      <c r="L85">
+        <v>20</v>
+      </c>
+      <c r="M85">
+        <v>2</v>
+      </c>
+      <c r="N85">
+        <v>5</v>
+      </c>
+      <c r="O85">
+        <v>1</v>
+      </c>
+      <c r="P85">
+        <v>4</v>
+      </c>
+      <c r="Q85">
+        <v>1</v>
+      </c>
+      <c r="R85">
+        <v>4</v>
+      </c>
+      <c r="S85">
+        <v>228</v>
+      </c>
+      <c r="T85">
+        <v>370</v>
+      </c>
+      <c r="U85">
+        <v>12</v>
+      </c>
+      <c r="V85">
+        <v>14</v>
+      </c>
+      <c r="W85">
+        <v>3</v>
+      </c>
+      <c r="X85">
+        <v>6</v>
+      </c>
+      <c r="Y85" t="s">
+        <v>90</v>
+      </c>
+      <c r="Z85" t="s">
+        <v>90</v>
+      </c>
+      <c r="AA85">
+        <v>4</v>
+      </c>
+      <c r="AB85">
+        <v>9</v>
+      </c>
+      <c r="AC85">
+        <v>2</v>
+      </c>
+      <c r="AD85">
+        <v>6</v>
+      </c>
+      <c r="AE85">
+        <v>0</v>
+      </c>
+      <c r="AF85">
+        <v>0</v>
+      </c>
+      <c r="AG85">
+        <v>4</v>
+      </c>
+      <c r="AH85">
+        <v>12</v>
+      </c>
+      <c r="AI85">
+        <v>4</v>
+      </c>
+      <c r="AJ85">
+        <v>8</v>
+      </c>
+      <c r="AK85">
+        <v>0.19</v>
+      </c>
+      <c r="AL85">
+        <v>0.74</v>
+      </c>
+      <c r="AM85">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="AN85">
+        <v>0.63</v>
+      </c>
+      <c r="AO85">
+        <v>0.33</v>
+      </c>
+      <c r="AP85">
+        <v>1.37</v>
+      </c>
+      <c r="AQ85">
+        <v>0.92</v>
+      </c>
+      <c r="AR85">
+        <v>1.0900000000000001</v>
+      </c>
+      <c r="AS85">
+        <v>316</v>
+      </c>
+      <c r="AT85">
+        <v>477</v>
+      </c>
+      <c r="AU85">
+        <v>146</v>
+      </c>
+      <c r="AV85">
+        <v>155</v>
+      </c>
+      <c r="AW85">
+        <v>82</v>
+      </c>
+      <c r="AX85">
+        <v>215</v>
+      </c>
+      <c r="AY85">
+        <v>19</v>
+      </c>
+      <c r="AZ85">
+        <v>28</v>
+      </c>
+      <c r="BA85">
+        <v>3</v>
+      </c>
+      <c r="BB85">
+        <v>6</v>
+      </c>
+      <c r="BC85">
+        <v>19</v>
+      </c>
+      <c r="BD85">
+        <v>21</v>
+      </c>
+      <c r="BE85">
+        <v>11</v>
+      </c>
+      <c r="BF85">
+        <v>29</v>
+      </c>
+      <c r="BG85">
+        <v>0</v>
+      </c>
+      <c r="BH85">
+        <v>1</v>
+      </c>
+      <c r="BI85" t="s">
+        <v>90</v>
+      </c>
+      <c r="BJ85" t="s">
+        <v>90</v>
+      </c>
+      <c r="BK85">
+        <v>9</v>
+      </c>
+      <c r="BL85">
+        <v>7</v>
+      </c>
+      <c r="BM85">
+        <v>6</v>
+      </c>
+      <c r="BN85">
+        <v>12</v>
+      </c>
+      <c r="BO85">
+        <v>7</v>
+      </c>
+      <c r="BP85">
+        <v>1</v>
+      </c>
+      <c r="BQ85">
+        <v>29</v>
+      </c>
+      <c r="BR85">
+        <v>21</v>
+      </c>
+      <c r="BS85">
+        <v>4</v>
+      </c>
+      <c r="BT85">
+        <v>2</v>
+      </c>
+      <c r="BU85" t="s">
+        <v>90</v>
+      </c>
+      <c r="BV85" t="s">
+        <v>90</v>
+      </c>
+      <c r="BW85">
+        <v>41</v>
+      </c>
+      <c r="BX85">
+        <v>44</v>
+      </c>
+      <c r="BY85">
+        <v>23</v>
+      </c>
+      <c r="BZ85">
+        <v>25</v>
+      </c>
+      <c r="CA85">
+        <v>18</v>
+      </c>
+      <c r="CB85">
+        <v>19</v>
+      </c>
+      <c r="CC85">
+        <v>4</v>
+      </c>
+      <c r="CD85">
+        <v>7</v>
+      </c>
+      <c r="CE85" t="s">
+        <v>90</v>
+      </c>
+      <c r="CF85" t="s">
+        <v>90</v>
+      </c>
+      <c r="CG85">
+        <v>1</v>
+      </c>
+      <c r="CH85">
+        <v>2</v>
+      </c>
+      <c r="CI85">
+        <v>0</v>
+      </c>
+      <c r="CJ85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="2:88">
+      <c r="B86" s="9" t="s">
+        <v>175</v>
+      </c>
+      <c r="C86" t="s">
+        <v>101</v>
+      </c>
+      <c r="D86" t="s">
+        <v>88</v>
+      </c>
+      <c r="E86">
+        <v>0</v>
+      </c>
+      <c r="F86">
+        <v>2</v>
+      </c>
+      <c r="G86">
+        <v>35</v>
+      </c>
+      <c r="H86">
+        <f t="shared" si="0"/>
+        <v>65</v>
+      </c>
+      <c r="I86">
+        <v>1.59</v>
+      </c>
+      <c r="J86">
+        <v>2.33</v>
+      </c>
+      <c r="K86">
+        <v>12</v>
+      </c>
+      <c r="L86">
+        <v>16</v>
+      </c>
+      <c r="M86">
+        <v>4</v>
+      </c>
+      <c r="N86">
+        <v>2</v>
+      </c>
+      <c r="O86">
+        <v>2</v>
+      </c>
+      <c r="P86">
+        <v>3</v>
+      </c>
+      <c r="Q86">
+        <v>2</v>
+      </c>
+      <c r="R86">
+        <v>3</v>
+      </c>
+      <c r="S86">
+        <v>307</v>
+      </c>
+      <c r="T86">
+        <v>624</v>
+      </c>
+      <c r="U86">
+        <v>5</v>
+      </c>
+      <c r="V86">
+        <v>9</v>
+      </c>
+      <c r="W86">
+        <v>3</v>
+      </c>
+      <c r="X86">
+        <v>6</v>
+      </c>
+      <c r="Y86" t="s">
+        <v>90</v>
+      </c>
+      <c r="Z86" t="s">
+        <v>90</v>
+      </c>
+      <c r="AA86">
+        <v>5</v>
+      </c>
+      <c r="AB86">
+        <v>7</v>
+      </c>
+      <c r="AC86">
+        <v>3</v>
+      </c>
+      <c r="AD86">
+        <v>7</v>
+      </c>
+      <c r="AE86">
+        <v>1</v>
+      </c>
+      <c r="AF86">
+        <v>0</v>
+      </c>
+      <c r="AG86">
+        <v>5</v>
+      </c>
+      <c r="AH86">
+        <v>12</v>
+      </c>
+      <c r="AI86">
+        <v>7</v>
+      </c>
+      <c r="AJ86">
+        <v>4</v>
+      </c>
+      <c r="AK86">
+        <v>1.52</v>
+      </c>
+      <c r="AL86">
+        <v>2.16</v>
+      </c>
+      <c r="AM86">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="AN86">
+        <v>0.17</v>
+      </c>
+      <c r="AO86">
+        <v>1.59</v>
+      </c>
+      <c r="AP86">
+        <v>2.33</v>
+      </c>
+      <c r="AQ86">
+        <v>0.67</v>
+      </c>
+      <c r="AR86">
+        <v>0.49</v>
+      </c>
+      <c r="AS86">
+        <v>362</v>
+      </c>
+      <c r="AT86">
+        <v>683</v>
+      </c>
+      <c r="AU86">
+        <v>141</v>
+      </c>
+      <c r="AV86">
+        <v>216</v>
+      </c>
+      <c r="AW86">
+        <v>166</v>
+      </c>
+      <c r="AX86">
+        <v>408</v>
+      </c>
+      <c r="AY86">
+        <v>13</v>
+      </c>
+      <c r="AZ86">
+        <v>26</v>
+      </c>
+      <c r="BA86">
+        <v>3</v>
+      </c>
+      <c r="BB86">
+        <v>6</v>
+      </c>
+      <c r="BC86">
+        <v>15</v>
+      </c>
+      <c r="BD86">
+        <v>13</v>
+      </c>
+      <c r="BE86">
+        <v>18</v>
+      </c>
+      <c r="BF86">
+        <v>51</v>
+      </c>
+      <c r="BG86">
+        <v>5</v>
+      </c>
+      <c r="BH86">
+        <v>2</v>
+      </c>
+      <c r="BI86" t="s">
+        <v>90</v>
+      </c>
+      <c r="BJ86" t="s">
+        <v>90</v>
+      </c>
+      <c r="BK86">
+        <v>19</v>
+      </c>
+      <c r="BL86">
+        <v>18</v>
+      </c>
+      <c r="BM86">
+        <v>7</v>
+      </c>
+      <c r="BN86">
+        <v>7</v>
+      </c>
+      <c r="BO86">
+        <v>7</v>
+      </c>
+      <c r="BP86">
+        <v>3</v>
+      </c>
+      <c r="BQ86">
+        <v>37</v>
+      </c>
+      <c r="BR86">
+        <v>21</v>
+      </c>
+      <c r="BS86">
+        <v>2</v>
+      </c>
+      <c r="BT86">
+        <v>4</v>
+      </c>
+      <c r="BU86" t="s">
+        <v>90</v>
+      </c>
+      <c r="BV86" t="s">
+        <v>90</v>
+      </c>
+      <c r="BW86">
+        <v>46</v>
+      </c>
+      <c r="BX86">
+        <v>52</v>
+      </c>
+      <c r="BY86">
+        <v>35</v>
+      </c>
+      <c r="BZ86">
+        <v>36</v>
+      </c>
+      <c r="CA86">
+        <v>11</v>
+      </c>
+      <c r="CB86">
+        <v>16</v>
+      </c>
+      <c r="CC86">
+        <v>7</v>
+      </c>
+      <c r="CD86">
+        <v>13</v>
+      </c>
+      <c r="CE86" t="s">
+        <v>90</v>
+      </c>
+      <c r="CF86" t="s">
+        <v>90</v>
+      </c>
+      <c r="CG86">
+        <v>0</v>
+      </c>
+      <c r="CH86">
+        <v>2</v>
+      </c>
+      <c r="CI86">
+        <v>0</v>
+      </c>
+      <c r="CJ86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="2:88">
+      <c r="B87" s="9" t="s">
+        <v>176</v>
+      </c>
+      <c r="C87" t="s">
+        <v>94</v>
+      </c>
+      <c r="D87" t="s">
+        <v>100</v>
+      </c>
+      <c r="E87">
+        <v>2</v>
+      </c>
+      <c r="F87">
+        <v>0</v>
+      </c>
+      <c r="G87">
+        <v>37</v>
+      </c>
+      <c r="H87">
+        <f t="shared" si="0"/>
+        <v>63</v>
+      </c>
+      <c r="I87">
+        <v>1.01</v>
+      </c>
+      <c r="J87">
+        <v>1.26</v>
+      </c>
+      <c r="K87">
+        <v>14</v>
+      </c>
+      <c r="L87">
+        <v>17</v>
+      </c>
+      <c r="M87">
+        <v>2</v>
+      </c>
+      <c r="N87">
+        <v>4</v>
+      </c>
+      <c r="O87">
+        <v>0</v>
+      </c>
+      <c r="P87">
+        <v>0</v>
+      </c>
+      <c r="Q87">
+        <v>0</v>
+      </c>
+      <c r="R87">
+        <v>0</v>
+      </c>
+      <c r="S87">
+        <v>270</v>
+      </c>
+      <c r="T87">
+        <v>514</v>
+      </c>
+      <c r="U87">
+        <v>5</v>
+      </c>
+      <c r="V87">
+        <v>8</v>
+      </c>
+      <c r="W87">
+        <v>6</v>
+      </c>
+      <c r="X87">
+        <v>9</v>
+      </c>
+      <c r="Y87" t="s">
+        <v>90</v>
+      </c>
+      <c r="Z87" t="s">
+        <v>90</v>
+      </c>
+      <c r="AA87">
+        <v>7</v>
+      </c>
+      <c r="AB87">
+        <v>7</v>
+      </c>
+      <c r="AC87">
+        <v>5</v>
+      </c>
+      <c r="AD87">
+        <v>6</v>
+      </c>
+      <c r="AE87">
+        <v>0</v>
+      </c>
+      <c r="AF87">
+        <v>1</v>
+      </c>
+      <c r="AG87">
+        <v>11</v>
+      </c>
+      <c r="AH87">
+        <v>10</v>
+      </c>
+      <c r="AI87">
+        <v>3</v>
+      </c>
+      <c r="AJ87">
+        <v>7</v>
+      </c>
+      <c r="AK87">
+        <v>0.91</v>
+      </c>
+      <c r="AL87">
+        <v>0.65</v>
+      </c>
+      <c r="AM87">
+        <v>0.1</v>
+      </c>
+      <c r="AN87">
+        <v>0.61</v>
+      </c>
+      <c r="AO87">
+        <v>1.01</v>
+      </c>
+      <c r="AP87">
+        <v>1.26</v>
+      </c>
+      <c r="AQ87">
+        <v>0.93</v>
+      </c>
+      <c r="AR87">
+        <v>1.26</v>
+      </c>
+      <c r="AS87">
+        <v>340</v>
+      </c>
+      <c r="AT87">
+        <v>593</v>
+      </c>
+      <c r="AU87">
+        <v>146</v>
+      </c>
+      <c r="AV87">
+        <v>188</v>
+      </c>
+      <c r="AW87">
+        <v>124</v>
+      </c>
+      <c r="AX87">
+        <v>326</v>
+      </c>
+      <c r="AY87">
+        <v>20</v>
+      </c>
+      <c r="AZ87">
+        <v>16</v>
+      </c>
+      <c r="BA87">
+        <v>5</v>
+      </c>
+      <c r="BB87">
+        <v>5</v>
+      </c>
+      <c r="BC87">
+        <v>18</v>
+      </c>
+      <c r="BD87">
+        <v>16</v>
+      </c>
+      <c r="BE87">
+        <v>26</v>
+      </c>
+      <c r="BF87">
+        <v>40</v>
+      </c>
+      <c r="BG87">
+        <v>2</v>
+      </c>
+      <c r="BH87">
+        <v>2</v>
+      </c>
+      <c r="BI87" t="s">
+        <v>90</v>
+      </c>
+      <c r="BJ87" t="s">
+        <v>90</v>
+      </c>
+      <c r="BK87">
+        <v>14</v>
+      </c>
+      <c r="BL87">
+        <v>11</v>
+      </c>
+      <c r="BM87">
+        <v>10</v>
+      </c>
+      <c r="BN87">
+        <v>10</v>
+      </c>
+      <c r="BO87">
+        <v>6</v>
+      </c>
+      <c r="BP87">
+        <v>5</v>
+      </c>
+      <c r="BQ87">
+        <v>53</v>
+      </c>
+      <c r="BR87">
+        <v>21</v>
+      </c>
+      <c r="BS87">
+        <v>4</v>
+      </c>
+      <c r="BT87">
+        <v>0</v>
+      </c>
+      <c r="BU87" t="s">
+        <v>90</v>
+      </c>
+      <c r="BV87" t="s">
+        <v>90</v>
+      </c>
+      <c r="BW87">
+        <v>41</v>
+      </c>
+      <c r="BX87">
+        <v>36</v>
+      </c>
+      <c r="BY87">
+        <v>23</v>
+      </c>
+      <c r="BZ87">
+        <v>22</v>
+      </c>
+      <c r="CA87">
+        <v>18</v>
+      </c>
+      <c r="CB87">
+        <v>14</v>
+      </c>
+      <c r="CC87">
+        <v>1</v>
+      </c>
+      <c r="CD87">
+        <v>6</v>
+      </c>
+      <c r="CE87" t="s">
+        <v>90</v>
+      </c>
+      <c r="CF87" t="s">
+        <v>90</v>
+      </c>
+      <c r="CG87">
+        <v>0</v>
+      </c>
+      <c r="CH87">
+        <v>1</v>
+      </c>
+      <c r="CI87">
+        <v>0</v>
+      </c>
+      <c r="CJ87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="2:88">
+      <c r="B88" s="9" t="s">
+        <v>176</v>
+      </c>
+      <c r="C88" t="s">
+        <v>89</v>
+      </c>
+      <c r="D88" t="s">
+        <v>95</v>
+      </c>
+      <c r="E88">
+        <v>1</v>
+      </c>
+      <c r="F88">
+        <v>4</v>
+      </c>
+      <c r="G88">
+        <v>35</v>
+      </c>
+      <c r="H88">
+        <f t="shared" si="0"/>
+        <v>65</v>
+      </c>
+      <c r="I88">
+        <v>1.17</v>
+      </c>
+      <c r="J88">
+        <v>1.78</v>
+      </c>
+      <c r="K88">
+        <v>13</v>
+      </c>
+      <c r="L88">
+        <v>16</v>
+      </c>
+      <c r="M88">
+        <v>6</v>
+      </c>
+      <c r="N88">
+        <v>7</v>
+      </c>
+      <c r="O88">
+        <v>1</v>
+      </c>
+      <c r="P88">
+        <v>4</v>
+      </c>
+      <c r="Q88">
+        <v>0</v>
+      </c>
+      <c r="R88">
+        <v>2</v>
+      </c>
+      <c r="S88">
+        <v>273</v>
+      </c>
+      <c r="T88">
+        <v>566</v>
+      </c>
+      <c r="U88">
+        <v>14</v>
+      </c>
+      <c r="V88">
+        <v>6</v>
+      </c>
+      <c r="W88">
+        <v>2</v>
+      </c>
+      <c r="X88">
+        <v>2</v>
+      </c>
+      <c r="Y88" t="s">
+        <v>90</v>
+      </c>
+      <c r="Z88" t="s">
+        <v>90</v>
+      </c>
+      <c r="AA88">
+        <v>4</v>
+      </c>
+      <c r="AB88">
+        <v>5</v>
+      </c>
+      <c r="AC88">
+        <v>3</v>
+      </c>
+      <c r="AD88">
+        <v>4</v>
+      </c>
+      <c r="AE88">
+        <v>0</v>
+      </c>
+      <c r="AF88">
+        <v>0</v>
+      </c>
+      <c r="AG88">
+        <v>4</v>
+      </c>
+      <c r="AH88">
+        <v>12</v>
+      </c>
+      <c r="AI88">
+        <v>9</v>
+      </c>
+      <c r="AJ88">
+        <v>4</v>
+      </c>
+      <c r="AK88">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="AL88">
+        <v>1.45</v>
+      </c>
+      <c r="AM88">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="AN88">
+        <v>0.33</v>
+      </c>
+      <c r="AO88">
+        <v>1.17</v>
+      </c>
+      <c r="AP88">
+        <v>1.78</v>
+      </c>
+      <c r="AQ88">
+        <v>1.65</v>
+      </c>
+      <c r="AR88">
+        <v>3.51</v>
+      </c>
+      <c r="AS88">
+        <v>334</v>
+      </c>
+      <c r="AT88">
+        <v>631</v>
+      </c>
+      <c r="AU88">
+        <v>143</v>
+      </c>
+      <c r="AV88">
+        <v>346</v>
+      </c>
+      <c r="AW88">
+        <v>130</v>
+      </c>
+      <c r="AX88">
+        <v>210</v>
+      </c>
+      <c r="AY88">
+        <v>15</v>
+      </c>
+      <c r="AZ88">
+        <v>45</v>
+      </c>
+      <c r="BA88">
+        <v>2</v>
+      </c>
+      <c r="BB88">
+        <v>7</v>
+      </c>
+      <c r="BC88">
+        <v>17</v>
+      </c>
+      <c r="BD88">
+        <v>13</v>
+      </c>
+      <c r="BE88">
+        <v>13</v>
+      </c>
+      <c r="BF88">
+        <v>20</v>
+      </c>
+      <c r="BG88">
+        <v>1</v>
+      </c>
+      <c r="BH88">
+        <v>4</v>
+      </c>
+      <c r="BI88" t="s">
+        <v>90</v>
+      </c>
+      <c r="BJ88" t="s">
+        <v>90</v>
+      </c>
+      <c r="BK88">
+        <v>18</v>
+      </c>
+      <c r="BL88">
+        <v>16</v>
+      </c>
+      <c r="BM88">
+        <v>5</v>
+      </c>
+      <c r="BN88">
+        <v>4</v>
+      </c>
+      <c r="BO88">
+        <v>4</v>
+      </c>
+      <c r="BP88">
+        <v>3</v>
+      </c>
+      <c r="BQ88">
+        <v>14</v>
+      </c>
+      <c r="BR88">
+        <v>14</v>
+      </c>
+      <c r="BS88">
+        <v>3</v>
+      </c>
+      <c r="BT88">
+        <v>5</v>
+      </c>
+      <c r="BU88" t="s">
+        <v>90</v>
+      </c>
+      <c r="BV88" t="s">
+        <v>90</v>
+      </c>
+      <c r="BW88">
+        <v>40</v>
+      </c>
+      <c r="BX88">
+        <v>47</v>
+      </c>
+      <c r="BY88">
+        <v>30</v>
+      </c>
+      <c r="BZ88">
+        <v>35</v>
+      </c>
+      <c r="CA88">
+        <v>10</v>
+      </c>
+      <c r="CB88">
+        <v>12</v>
+      </c>
+      <c r="CC88">
+        <v>6</v>
+      </c>
+      <c r="CD88">
+        <v>6</v>
+      </c>
+      <c r="CE88" t="s">
+        <v>90</v>
+      </c>
+      <c r="CF88" t="s">
+        <v>90</v>
+      </c>
+      <c r="CG88">
+        <v>3</v>
+      </c>
+      <c r="CH88">
+        <v>0</v>
+      </c>
+      <c r="CI88">
+        <v>0</v>
+      </c>
+      <c r="CJ88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="2:88">
+      <c r="B89" s="8" t="s">
+        <v>177</v>
+      </c>
+      <c r="C89" t="s">
+        <v>99</v>
+      </c>
+      <c r="D89" t="s">
+        <v>102</v>
+      </c>
+      <c r="E89">
+        <v>5</v>
+      </c>
+      <c r="F89">
+        <v>1</v>
+      </c>
+      <c r="G89">
+        <v>60</v>
+      </c>
+      <c r="H89">
+        <f t="shared" si="0"/>
+        <v>40</v>
+      </c>
+      <c r="I89">
+        <v>3.36</v>
+      </c>
+      <c r="J89">
+        <v>1.4</v>
+      </c>
+      <c r="K89">
+        <v>26</v>
+      </c>
+      <c r="L89">
+        <v>15</v>
+      </c>
+      <c r="M89">
+        <v>9</v>
+      </c>
+      <c r="N89">
+        <v>6</v>
+      </c>
+      <c r="O89">
+        <v>7</v>
+      </c>
+      <c r="P89">
+        <v>2</v>
+      </c>
+      <c r="Q89">
+        <v>3</v>
+      </c>
+      <c r="R89">
+        <v>2</v>
+      </c>
+      <c r="S89">
+        <v>257</v>
+      </c>
+      <c r="T89">
+        <v>146</v>
+      </c>
+      <c r="U89">
+        <v>10</v>
+      </c>
+      <c r="V89">
+        <v>17</v>
+      </c>
+      <c r="W89">
+        <v>10</v>
+      </c>
+      <c r="X89">
+        <v>3</v>
+      </c>
+      <c r="Y89" t="s">
+        <v>90</v>
+      </c>
+      <c r="Z89" t="s">
+        <v>90</v>
+      </c>
+      <c r="AA89">
+        <v>9</v>
+      </c>
+      <c r="AB89">
+        <v>6</v>
+      </c>
+      <c r="AC89">
+        <v>8</v>
+      </c>
+      <c r="AD89">
+        <v>3</v>
+      </c>
+      <c r="AE89">
+        <v>0</v>
+      </c>
+      <c r="AF89">
+        <v>0</v>
+      </c>
+      <c r="AG89">
+        <v>17</v>
+      </c>
+      <c r="AH89">
+        <v>9</v>
+      </c>
+      <c r="AI89">
+        <v>9</v>
+      </c>
+      <c r="AJ89">
+        <v>6</v>
+      </c>
+      <c r="AK89">
+        <v>2.15</v>
+      </c>
+      <c r="AL89">
+        <v>0.63</v>
+      </c>
+      <c r="AM89">
+        <v>0.42</v>
+      </c>
+      <c r="AN89">
+        <v>0.78</v>
+      </c>
+      <c r="AO89">
+        <v>2.57</v>
+      </c>
+      <c r="AP89">
+        <v>1.4</v>
+      </c>
+      <c r="AQ89">
+        <v>3.73</v>
+      </c>
+      <c r="AR89">
+        <v>1.31</v>
+      </c>
+      <c r="AS89">
+        <v>364</v>
+      </c>
+      <c r="AT89">
+        <v>248</v>
+      </c>
+      <c r="AU89">
+        <v>92</v>
+      </c>
+      <c r="AV89">
+        <v>63</v>
+      </c>
+      <c r="AW89">
+        <v>165</v>
+      </c>
+      <c r="AX89">
+        <v>83</v>
+      </c>
+      <c r="AY89">
+        <v>35</v>
+      </c>
+      <c r="AZ89">
+        <v>20</v>
+      </c>
+      <c r="BA89">
+        <v>6</v>
+      </c>
+      <c r="BB89">
+        <v>2</v>
+      </c>
+      <c r="BC89">
+        <v>27</v>
+      </c>
+      <c r="BD89">
+        <v>31</v>
+      </c>
+      <c r="BE89">
+        <v>34</v>
+      </c>
+      <c r="BF89">
+        <v>14</v>
+      </c>
+      <c r="BG89">
+        <v>4</v>
+      </c>
+      <c r="BH89">
+        <v>0</v>
+      </c>
+      <c r="BI89" t="s">
+        <v>90</v>
+      </c>
+      <c r="BJ89" t="s">
+        <v>90</v>
+      </c>
+      <c r="BK89">
+        <v>21</v>
+      </c>
+      <c r="BL89">
+        <v>13</v>
+      </c>
+      <c r="BM89">
+        <v>15</v>
+      </c>
+      <c r="BN89">
+        <v>8</v>
+      </c>
+      <c r="BO89">
+        <v>2</v>
+      </c>
+      <c r="BP89">
+        <v>8</v>
+      </c>
+      <c r="BQ89">
+        <v>19</v>
+      </c>
+      <c r="BR89">
+        <v>36</v>
+      </c>
+      <c r="BS89">
+        <v>5</v>
+      </c>
+      <c r="BT89">
+        <v>4</v>
+      </c>
+      <c r="BU89" t="s">
+        <v>90</v>
+      </c>
+      <c r="BV89" t="s">
+        <v>90</v>
+      </c>
+      <c r="BW89">
+        <v>71</v>
+      </c>
+      <c r="BX89">
+        <v>60</v>
+      </c>
+      <c r="BY89">
+        <v>49</v>
+      </c>
+      <c r="BZ89">
+        <v>32</v>
+      </c>
+      <c r="CA89">
+        <v>22</v>
+      </c>
+      <c r="CB89">
+        <v>28</v>
+      </c>
+      <c r="CC89">
+        <v>12</v>
+      </c>
+      <c r="CD89">
+        <v>11</v>
+      </c>
+      <c r="CE89" t="s">
+        <v>90</v>
+      </c>
+      <c r="CF89" t="s">
+        <v>90</v>
+      </c>
+      <c r="CG89">
+        <v>0</v>
+      </c>
+      <c r="CH89">
+        <v>3</v>
+      </c>
+      <c r="CI89">
+        <v>0</v>
+      </c>
+      <c r="CJ89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="2:88">
+      <c r="B90" s="8" t="s">
+        <v>178</v>
+      </c>
+      <c r="C90" t="s">
+        <v>113</v>
+      </c>
+      <c r="D90" t="s">
+        <v>104</v>
+      </c>
+      <c r="E90">
+        <v>2</v>
+      </c>
+      <c r="F90">
+        <v>2</v>
+      </c>
+      <c r="G90">
+        <v>50</v>
+      </c>
+      <c r="H90">
+        <f t="shared" si="0"/>
+        <v>50</v>
+      </c>
+      <c r="I90">
+        <v>1.51</v>
+      </c>
+      <c r="J90">
+        <v>1.01</v>
+      </c>
+      <c r="K90">
+        <v>26</v>
+      </c>
+      <c r="L90">
+        <v>10</v>
+      </c>
+      <c r="M90">
+        <v>4</v>
+      </c>
+      <c r="N90">
+        <v>5</v>
+      </c>
+      <c r="O90">
+        <v>2</v>
+      </c>
+      <c r="P90">
+        <v>1</v>
+      </c>
+      <c r="Q90">
+        <v>1</v>
+      </c>
+      <c r="R90">
+        <v>0</v>
+      </c>
+      <c r="S90">
+        <v>406</v>
+      </c>
+      <c r="T90">
+        <v>410</v>
+      </c>
+      <c r="U90">
+        <v>10</v>
+      </c>
+      <c r="V90">
+        <v>13</v>
+      </c>
+      <c r="W90">
+        <v>8</v>
+      </c>
+      <c r="X90">
+        <v>2</v>
+      </c>
+      <c r="Y90" t="s">
+        <v>90</v>
+      </c>
+      <c r="Z90" t="s">
+        <v>90</v>
+      </c>
+      <c r="AA90">
+        <v>14</v>
+      </c>
+      <c r="AB90">
+        <v>2</v>
+      </c>
+      <c r="AC90">
+        <v>8</v>
+      </c>
+      <c r="AD90">
+        <v>3</v>
+      </c>
+      <c r="AE90">
+        <v>0</v>
+      </c>
+      <c r="AF90">
+        <v>0</v>
+      </c>
+      <c r="AG90">
+        <v>12</v>
+      </c>
+      <c r="AH90">
+        <v>8</v>
+      </c>
+      <c r="AI90">
+        <v>14</v>
+      </c>
+      <c r="AJ90">
+        <v>2</v>
+      </c>
+      <c r="AK90">
+        <v>1.2</v>
+      </c>
+      <c r="AL90">
+        <v>1.01</v>
+      </c>
+      <c r="AM90">
+        <v>0.32</v>
+      </c>
+      <c r="AN90">
+        <v>0</v>
+      </c>
+      <c r="AO90">
+        <v>1.51</v>
+      </c>
+      <c r="AP90">
+        <v>1.01</v>
+      </c>
+      <c r="AQ90">
+        <v>1.02</v>
+      </c>
+      <c r="AR90">
+        <v>2.54</v>
+      </c>
+      <c r="AS90">
+        <v>466</v>
+      </c>
+      <c r="AT90">
+        <v>481</v>
+      </c>
+      <c r="AU90">
+        <v>202</v>
+      </c>
+      <c r="AV90">
+        <v>238</v>
+      </c>
+      <c r="AW90">
+        <v>204</v>
+      </c>
+      <c r="AX90">
+        <v>172</v>
+      </c>
+      <c r="AY90">
+        <v>24</v>
+      </c>
+      <c r="AZ90">
+        <v>18</v>
+      </c>
+      <c r="BA90">
+        <v>5</v>
+      </c>
+      <c r="BB90">
+        <v>3</v>
+      </c>
+      <c r="BC90">
+        <v>20</v>
+      </c>
+      <c r="BD90">
+        <v>15</v>
+      </c>
+      <c r="BE90">
+        <v>39</v>
+      </c>
+      <c r="BF90">
+        <v>31</v>
+      </c>
+      <c r="BG90">
+        <v>0</v>
+      </c>
+      <c r="BH90">
+        <v>1</v>
+      </c>
+      <c r="BI90" t="s">
+        <v>90</v>
+      </c>
+      <c r="BJ90" t="s">
+        <v>90</v>
+      </c>
+      <c r="BK90">
+        <v>22</v>
+      </c>
+      <c r="BL90">
+        <v>26</v>
+      </c>
+      <c r="BM90">
+        <v>9</v>
+      </c>
+      <c r="BN90">
+        <v>10</v>
+      </c>
+      <c r="BO90">
+        <v>3</v>
+      </c>
+      <c r="BP90">
+        <v>8</v>
+      </c>
+      <c r="BQ90">
+        <v>16</v>
+      </c>
+      <c r="BR90">
+        <v>29</v>
+      </c>
+      <c r="BS90">
+        <v>3</v>
+      </c>
+      <c r="BT90">
+        <v>2</v>
+      </c>
+      <c r="BU90" t="s">
+        <v>90</v>
+      </c>
+      <c r="BV90" t="s">
+        <v>90</v>
+      </c>
+      <c r="BW90">
+        <v>50</v>
+      </c>
+      <c r="BX90">
+        <v>52</v>
+      </c>
+      <c r="BY90">
+        <v>43</v>
+      </c>
+      <c r="BZ90">
+        <v>42</v>
+      </c>
+      <c r="CA90">
+        <v>7</v>
+      </c>
+      <c r="CB90">
+        <v>10</v>
+      </c>
+      <c r="CC90">
+        <v>9</v>
+      </c>
+      <c r="CD90">
+        <v>7</v>
+      </c>
+      <c r="CE90" t="s">
+        <v>90</v>
+      </c>
+      <c r="CF90" t="s">
+        <v>90</v>
+      </c>
+      <c r="CG90">
+        <v>3</v>
+      </c>
+      <c r="CH90">
+        <v>2</v>
+      </c>
+      <c r="CI90">
+        <v>0</v>
+      </c>
+      <c r="CJ90">
         <v>0</v>
       </c>
     </row>
